--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="F14" t="n">
-        <v>5.96</v>
+        <v>6.08</v>
       </c>
       <c r="G14" t="n">
-        <v>83.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.24</v>
+        <v>-49.35</v>
       </c>
       <c r="K14" t="n">
-        <v>-27.74</v>
+        <v>63.48</v>
       </c>
       <c r="L14" t="n">
-        <v>35.56</v>
+        <v>80.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:39:55</t>
+          <t>06:39:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="F15" t="n">
-        <v>5.65</v>
+        <v>6.49</v>
       </c>
       <c r="G15" t="n">
-        <v>78.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.5</v>
+        <v>54.87</v>
       </c>
       <c r="K15" t="n">
-        <v>12.13</v>
+        <v>-0.74</v>
       </c>
       <c r="L15" t="n">
-        <v>12.23</v>
+        <v>54.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:41:15</t>
+          <t>06:40:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="F16" t="n">
-        <v>5.54</v>
+        <v>6.07</v>
       </c>
       <c r="G16" t="n">
-        <v>92.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>47.59</v>
+        <v>-26.35</v>
       </c>
       <c r="K16" t="n">
-        <v>1.31</v>
+        <v>46.52</v>
       </c>
       <c r="L16" t="n">
-        <v>47.61</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:46:38</t>
+          <t>06:45:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.59</v>
+        <v>1.08</v>
       </c>
       <c r="F17" t="n">
-        <v>5.54</v>
+        <v>6.29</v>
       </c>
       <c r="G17" t="n">
-        <v>99.2</v>
+        <v>85.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>110.58</v>
+        <v>21.98</v>
       </c>
       <c r="K17" t="n">
-        <v>58.08</v>
+        <v>5.62</v>
       </c>
       <c r="L17" t="n">
-        <v>124.9</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:48:14</t>
+          <t>06:46:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="F18" t="n">
-        <v>6.06</v>
+        <v>5.6</v>
       </c>
       <c r="G18" t="n">
-        <v>81.5</v>
+        <v>91.2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-18.44</v>
+        <v>59.33</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.97</v>
+        <v>16.68</v>
       </c>
       <c r="L18" t="n">
-        <v>25.75</v>
+        <v>61.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:50:03</t>
+          <t>06:49:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="F19" t="n">
-        <v>6.43</v>
+        <v>6.19</v>
       </c>
       <c r="G19" t="n">
-        <v>93.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>46.84</v>
+        <v>-15.27</v>
       </c>
       <c r="K19" t="n">
-        <v>0.37</v>
+        <v>33.53</v>
       </c>
       <c r="L19" t="n">
-        <v>46.84</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:54:31</t>
+          <t>06:53:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.82</v>
+        <v>1.25</v>
       </c>
       <c r="F20" t="n">
-        <v>6.67</v>
+        <v>6.82</v>
       </c>
       <c r="G20" t="n">
-        <v>107</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>13.26</v>
+        <v>251.45</v>
       </c>
       <c r="K20" t="n">
-        <v>-81.01000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="L20" t="n">
-        <v>82.09</v>
+        <v>251.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:56:43</t>
+          <t>06:55:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="F21" t="n">
-        <v>6.7</v>
+        <v>6.49</v>
       </c>
       <c r="G21" t="n">
-        <v>111.6</v>
+        <v>87.7</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>92.3</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-92.51000000000001</v>
+        <v>99.97</v>
       </c>
       <c r="L21" t="n">
-        <v>130.68</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:58:32</t>
+          <t>06:57:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="F22" t="n">
-        <v>6.32</v>
+        <v>6.09</v>
       </c>
       <c r="G22" t="n">
-        <v>91.5</v>
+        <v>89</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>39.62</v>
+        <v>195.43</v>
       </c>
       <c r="K22" t="n">
-        <v>-52.76</v>
+        <v>163.47</v>
       </c>
       <c r="L22" t="n">
-        <v>65.98</v>
+        <v>254.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:04:24</t>
+          <t>07:01:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="F23" t="n">
-        <v>6.53</v>
+        <v>5.48</v>
       </c>
       <c r="G23" t="n">
-        <v>90.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-100.86</v>
+        <v>153.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-185.81</v>
+        <v>108.13</v>
       </c>
       <c r="L23" t="n">
-        <v>211.42</v>
+        <v>187.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:06:26</t>
+          <t>07:02:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="F24" t="n">
-        <v>5.89</v>
+        <v>6.81</v>
       </c>
       <c r="G24" t="n">
-        <v>107.5</v>
+        <v>75.3</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>18.7</v>
+        <v>117.85</v>
       </c>
       <c r="K24" t="n">
-        <v>70.45999999999999</v>
+        <v>167.45</v>
       </c>
       <c r="L24" t="n">
-        <v>72.90000000000001</v>
+        <v>204.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:08:06</t>
+          <t>07:04:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.69</v>
+        <v>0.99</v>
       </c>
       <c r="F25" t="n">
-        <v>6.26</v>
+        <v>6.68</v>
       </c>
       <c r="G25" t="n">
-        <v>90.3</v>
+        <v>97.5</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>118.91</v>
+        <v>-32.84</v>
       </c>
       <c r="K25" t="n">
-        <v>44.62</v>
+        <v>84.67</v>
       </c>
       <c r="L25" t="n">
-        <v>127</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:13:20</t>
+          <t>07:09:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="F26" t="n">
-        <v>6.48</v>
+        <v>6.56</v>
       </c>
       <c r="G26" t="n">
-        <v>80.2</v>
+        <v>92.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>189.78</v>
+        <v>42.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.98</v>
+        <v>390.74</v>
       </c>
       <c r="L26" t="n">
-        <v>190.37</v>
+        <v>393.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:14:19</t>
+          <t>07:11:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="F27" t="n">
-        <v>6.02</v>
+        <v>6.24</v>
       </c>
       <c r="G27" t="n">
-        <v>85.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>15.63</v>
+        <v>-121.33</v>
       </c>
       <c r="K27" t="n">
-        <v>-467.11</v>
+        <v>32.17</v>
       </c>
       <c r="L27" t="n">
-        <v>467.37</v>
+        <v>125.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:15:13</t>
+          <t>07:14:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="F28" t="n">
-        <v>6.38</v>
+        <v>6.75</v>
       </c>
       <c r="G28" t="n">
-        <v>87.3</v>
+        <v>96.8</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>26.06</v>
+        <v>-194.67</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.779999999999999</v>
+        <v>-173.09</v>
       </c>
       <c r="L28" t="n">
-        <v>27.5</v>
+        <v>260.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:26:11</t>
+          <t>07:24:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="F29" t="n">
-        <v>5.34</v>
+        <v>6.36</v>
       </c>
       <c r="G29" t="n">
-        <v>88.8</v>
+        <v>100.2</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>35.23</v>
+        <v>9.1</v>
       </c>
       <c r="K29" t="n">
-        <v>54.93</v>
+        <v>-57.02</v>
       </c>
       <c r="L29" t="n">
-        <v>65.26000000000001</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:27:16</t>
+          <t>07:25:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="F30" t="n">
-        <v>5.73</v>
+        <v>5.96</v>
       </c>
       <c r="G30" t="n">
-        <v>87.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>-37.28</v>
+        <v>-38.15</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.3</v>
+        <v>19.79</v>
       </c>
       <c r="L30" t="n">
-        <v>37.52</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:28:30</t>
+          <t>07:27:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="F31" t="n">
-        <v>5.91</v>
+        <v>6.56</v>
       </c>
       <c r="G31" t="n">
-        <v>84.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>70.70999999999999</v>
+        <v>-66.64</v>
       </c>
       <c r="K31" t="n">
-        <v>40.92</v>
+        <v>6.67</v>
       </c>
       <c r="L31" t="n">
-        <v>81.7</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:34:45</t>
+          <t>07:31:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="F32" t="n">
-        <v>6.4</v>
+        <v>6.58</v>
       </c>
       <c r="G32" t="n">
-        <v>85.5</v>
+        <v>93</v>
       </c>
       <c r="H32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-12.21</v>
+        <v>48.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-63.98</v>
+        <v>119.13</v>
       </c>
       <c r="L32" t="n">
-        <v>65.14</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:36:06</t>
+          <t>07:32:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="F33" t="n">
-        <v>6.08</v>
+        <v>6.57</v>
       </c>
       <c r="G33" t="n">
-        <v>93.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>12.66</v>
+        <v>29.89</v>
       </c>
       <c r="K33" t="n">
-        <v>-86.54000000000001</v>
+        <v>-173.82</v>
       </c>
       <c r="L33" t="n">
-        <v>87.45999999999999</v>
+        <v>176.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:38:25</t>
+          <t>07:34:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="F34" t="n">
-        <v>6.61</v>
+        <v>6.06</v>
       </c>
       <c r="G34" t="n">
-        <v>105.8</v>
+        <v>74</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>9.289999999999999</v>
+        <v>36.34</v>
       </c>
       <c r="K34" t="n">
-        <v>-54.7</v>
+        <v>131.11</v>
       </c>
       <c r="L34" t="n">
-        <v>55.49</v>
+        <v>136.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:42:46</t>
+          <t>07:38:44</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="F35" t="n">
-        <v>6.7</v>
+        <v>6.44</v>
       </c>
       <c r="G35" t="n">
-        <v>102.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-122.26</v>
+        <v>118.22</v>
       </c>
       <c r="K35" t="n">
-        <v>-31.46</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>126.25</v>
+        <v>144.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:44:03</t>
+          <t>07:41:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="F36" t="n">
-        <v>6.39</v>
+        <v>5.94</v>
       </c>
       <c r="G36" t="n">
-        <v>82.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.84</v>
+        <v>172.15</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.36</v>
+        <v>-22.25</v>
       </c>
       <c r="L36" t="n">
-        <v>5.39</v>
+        <v>173.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:45:52</t>
+          <t>07:43:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="F37" t="n">
-        <v>5.81</v>
+        <v>5.86</v>
       </c>
       <c r="G37" t="n">
-        <v>92.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>-28.41</v>
+        <v>-22.79</v>
       </c>
       <c r="K37" t="n">
-        <v>66.38</v>
+        <v>80.87</v>
       </c>
       <c r="L37" t="n">
-        <v>72.2</v>
+        <v>84.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:49:04</t>
+          <t>07:48:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="F38" t="n">
-        <v>5.44</v>
+        <v>6.01</v>
       </c>
       <c r="G38" t="n">
-        <v>82.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>86.09</v>
+        <v>-97.75</v>
       </c>
       <c r="K38" t="n">
-        <v>27.31</v>
+        <v>34.94</v>
       </c>
       <c r="L38" t="n">
-        <v>90.31999999999999</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:50:44</t>
+          <t>07:51:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="F39" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="G39" t="n">
-        <v>98.8</v>
+        <v>97.2</v>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-12.49</v>
+        <v>75.44</v>
       </c>
       <c r="K39" t="n">
-        <v>-180.13</v>
+        <v>27.13</v>
       </c>
       <c r="L39" t="n">
-        <v>180.56</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:52:42</t>
+          <t>07:53:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="F40" t="n">
-        <v>5.32</v>
+        <v>5.29</v>
       </c>
       <c r="G40" t="n">
-        <v>85.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>122.55</v>
+        <v>-113.65</v>
       </c>
       <c r="K40" t="n">
-        <v>83.7</v>
+        <v>170.37</v>
       </c>
       <c r="L40" t="n">
-        <v>148.4</v>
+        <v>204.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:58:29</t>
+          <t>07:57:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="F41" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="G41" t="n">
-        <v>91.40000000000001</v>
+        <v>101</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-226.71</v>
+        <v>-212.6</v>
       </c>
       <c r="K41" t="n">
-        <v>26.82</v>
+        <v>-87.86</v>
       </c>
       <c r="L41" t="n">
-        <v>228.29</v>
+        <v>230.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:00:53</t>
+          <t>07:59:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="F42" t="n">
-        <v>5.97</v>
+        <v>6.02</v>
       </c>
       <c r="G42" t="n">
-        <v>95.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>66.06</v>
+        <v>140.9</v>
       </c>
       <c r="K42" t="n">
-        <v>190.1</v>
+        <v>8.84</v>
       </c>
       <c r="L42" t="n">
-        <v>201.25</v>
+        <v>141.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:02:36</t>
+          <t>08:01:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="F43" t="n">
-        <v>6.16</v>
+        <v>5.96</v>
       </c>
       <c r="G43" t="n">
-        <v>113.4</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>243.57</v>
+        <v>47.95</v>
       </c>
       <c r="K43" t="n">
-        <v>112.83</v>
+        <v>-151.84</v>
       </c>
       <c r="L43" t="n">
-        <v>268.43</v>
+        <v>159.23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:11:17</t>
+          <t>08:11:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="F44" t="n">
-        <v>6.37</v>
+        <v>5.59</v>
       </c>
       <c r="G44" t="n">
-        <v>95.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>13.76</v>
+        <v>-23.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-78.81</v>
+        <v>-41.96</v>
       </c>
       <c r="L44" t="n">
-        <v>80</v>
+        <v>48.19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:12:53</t>
+          <t>08:12:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="F45" t="n">
-        <v>5.78</v>
+        <v>6.49</v>
       </c>
       <c r="G45" t="n">
-        <v>90.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>10.41</v>
+        <v>-68.34</v>
       </c>
       <c r="K45" t="n">
-        <v>2.46</v>
+        <v>-6.59</v>
       </c>
       <c r="L45" t="n">
-        <v>10.7</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:14:22</t>
+          <t>08:14:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="F46" t="n">
-        <v>5.85</v>
+        <v>5.93</v>
       </c>
       <c r="G46" t="n">
-        <v>86.5</v>
+        <v>94.2</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.98</v>
+        <v>-34.51</v>
       </c>
       <c r="K46" t="n">
-        <v>9.109999999999999</v>
+        <v>32.57</v>
       </c>
       <c r="L46" t="n">
-        <v>16.69</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:19:22</t>
+          <t>08:18:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="F47" t="n">
-        <v>5.76</v>
+        <v>5.56</v>
       </c>
       <c r="G47" t="n">
-        <v>105.7</v>
+        <v>90.2</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>-43.31</v>
+        <v>-91.72</v>
       </c>
       <c r="K47" t="n">
-        <v>31.65</v>
+        <v>-44.71</v>
       </c>
       <c r="L47" t="n">
-        <v>53.64</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:21:30</t>
+          <t>08:19:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="F48" t="n">
-        <v>5.82</v>
+        <v>5.28</v>
       </c>
       <c r="G48" t="n">
-        <v>88.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-40.22</v>
+        <v>-146.25</v>
       </c>
       <c r="K48" t="n">
-        <v>36.37</v>
+        <v>-46.44</v>
       </c>
       <c r="L48" t="n">
-        <v>54.23</v>
+        <v>153.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:22:57</t>
+          <t>08:21:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="F49" t="n">
-        <v>6.24</v>
+        <v>6.91</v>
       </c>
       <c r="G49" t="n">
-        <v>96.8</v>
+        <v>103.3</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>55.96</v>
+        <v>-9.24</v>
       </c>
       <c r="K49" t="n">
-        <v>-45.92</v>
+        <v>-18.46</v>
       </c>
       <c r="L49" t="n">
-        <v>72.39</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:27:52</t>
+          <t>08:25:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="F50" t="n">
         <v>6.03</v>
       </c>
       <c r="G50" t="n">
-        <v>108.3</v>
+        <v>71.7</v>
       </c>
       <c r="H50" t="n">
-        <v>7.3</v>
+        <v>5.1</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>108.5</v>
+        <v>52.34</v>
       </c>
       <c r="K50" t="n">
-        <v>-108.74</v>
+        <v>52.17</v>
       </c>
       <c r="L50" t="n">
-        <v>153.61</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:29:07</t>
+          <t>08:26:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="F51" t="n">
-        <v>5.9</v>
+        <v>6.28</v>
       </c>
       <c r="G51" t="n">
-        <v>76.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-66.26000000000001</v>
+        <v>-104.6</v>
       </c>
       <c r="K51" t="n">
-        <v>9.869999999999999</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>66.98999999999999</v>
+        <v>127.98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:30:53</t>
+          <t>08:28:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="F52" t="n">
-        <v>5.59</v>
+        <v>6.18</v>
       </c>
       <c r="G52" t="n">
         <v>84.59999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-108.93</v>
+        <v>141</v>
       </c>
       <c r="K52" t="n">
-        <v>13.96</v>
+        <v>-48.99</v>
       </c>
       <c r="L52" t="n">
-        <v>109.83</v>
+        <v>149.26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:35:37</t>
+          <t>08:32:24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="F53" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="G53" t="n">
-        <v>78.8</v>
+        <v>78.2</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-102.31</v>
+        <v>-71.58</v>
       </c>
       <c r="K53" t="n">
-        <v>-31.56</v>
+        <v>135.46</v>
       </c>
       <c r="L53" t="n">
-        <v>107.06</v>
+        <v>153.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:37:32</t>
+          <t>08:33:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="F54" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="G54" t="n">
-        <v>88.7</v>
+        <v>90.7</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I54" t="n">
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>172.21</v>
+        <v>-1.27</v>
       </c>
       <c r="K54" t="n">
-        <v>152.07</v>
+        <v>-106.33</v>
       </c>
       <c r="L54" t="n">
-        <v>229.74</v>
+        <v>106.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:39:08</t>
+          <t>08:36:03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="F55" t="n">
-        <v>5.72</v>
+        <v>6.17</v>
       </c>
       <c r="G55" t="n">
-        <v>80.3</v>
+        <v>92.7</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>78.55</v>
+        <v>-145.73</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.29</v>
+        <v>61.4</v>
       </c>
       <c r="L55" t="n">
-        <v>78.55</v>
+        <v>158.14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:45:06</t>
+          <t>08:41:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="F56" t="n">
-        <v>5.79</v>
+        <v>5.92</v>
       </c>
       <c r="G56" t="n">
-        <v>106</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="I56" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-47.59</v>
+        <v>-105.12</v>
       </c>
       <c r="K56" t="n">
-        <v>208.7</v>
+        <v>56.97</v>
       </c>
       <c r="L56" t="n">
-        <v>214.06</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:46:38</t>
+          <t>08:42:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="F57" t="n">
-        <v>6.59</v>
+        <v>6.15</v>
       </c>
       <c r="G57" t="n">
-        <v>92.2</v>
+        <v>93.5</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="I57" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-197.26</v>
+        <v>-6.71</v>
       </c>
       <c r="K57" t="n">
-        <v>217.17</v>
+        <v>306.78</v>
       </c>
       <c r="L57" t="n">
-        <v>293.39</v>
+        <v>306.85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:48:28</t>
+          <t>08:44:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="F58" t="n">
-        <v>5.6</v>
+        <v>6.28</v>
       </c>
       <c r="G58" t="n">
-        <v>75.8</v>
+        <v>78.5</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>-259.53</v>
+        <v>-181.9</v>
       </c>
       <c r="K58" t="n">
-        <v>68</v>
+        <v>-79.56</v>
       </c>
       <c r="L58" t="n">
-        <v>268.29</v>
+        <v>198.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:57:51</t>
+          <t>08:56:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="F59" t="n">
-        <v>6.66</v>
+        <v>5.85</v>
       </c>
       <c r="G59" t="n">
-        <v>92.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>0.15</v>
+        <v>28.34</v>
       </c>
       <c r="K59" t="n">
-        <v>2.61</v>
+        <v>-2.53</v>
       </c>
       <c r="L59" t="n">
-        <v>2.61</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:59:29</t>
+          <t>08:58:56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="F60" t="n">
-        <v>6.62</v>
+        <v>6.27</v>
       </c>
       <c r="G60" t="n">
-        <v>85.3</v>
+        <v>85.7</v>
       </c>
       <c r="H60" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>10.23</v>
+        <v>-76.37</v>
       </c>
       <c r="K60" t="n">
-        <v>-17.97</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>20.68</v>
+        <v>108.85</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:01:19</t>
+          <t>09:00:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="F61" t="n">
-        <v>6.39</v>
+        <v>5.78</v>
       </c>
       <c r="G61" t="n">
-        <v>87.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-46.33</v>
+        <v>-36.81</v>
       </c>
       <c r="K61" t="n">
-        <v>-13.42</v>
+        <v>-20.3</v>
       </c>
       <c r="L61" t="n">
-        <v>48.24</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:06:01</t>
+          <t>09:04:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.77</v>
+        <v>1.23</v>
       </c>
       <c r="F62" t="n">
-        <v>5.87</v>
+        <v>5.85</v>
       </c>
       <c r="G62" t="n">
-        <v>97.59999999999999</v>
+        <v>108.3</v>
       </c>
       <c r="H62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>36.3</v>
+        <v>1.52</v>
       </c>
       <c r="K62" t="n">
-        <v>7.55</v>
+        <v>-44.17</v>
       </c>
       <c r="L62" t="n">
-        <v>37.08</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:07:56</t>
+          <t>09:06:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.77</v>
+        <v>1.15</v>
       </c>
       <c r="F63" t="n">
-        <v>6.06</v>
+        <v>6.36</v>
       </c>
       <c r="G63" t="n">
-        <v>101.8</v>
+        <v>108.8</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>84.92</v>
+        <v>-22.03</v>
       </c>
       <c r="K63" t="n">
-        <v>58.05</v>
+        <v>-99.52</v>
       </c>
       <c r="L63" t="n">
-        <v>102.86</v>
+        <v>101.93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:10:02</t>
+          <t>09:07:03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="F64" t="n">
-        <v>6.15</v>
+        <v>5.43</v>
       </c>
       <c r="G64" t="n">
-        <v>94.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>-81.56</v>
+        <v>-11.51</v>
       </c>
       <c r="K64" t="n">
-        <v>-83.86</v>
+        <v>-31.06</v>
       </c>
       <c r="L64" t="n">
-        <v>116.98</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:13:25</t>
+          <t>09:11:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="F65" t="n">
-        <v>5.94</v>
+        <v>5.91</v>
       </c>
       <c r="G65" t="n">
-        <v>105.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-214.88</v>
+        <v>-47.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-138.17</v>
+        <v>16.42</v>
       </c>
       <c r="L65" t="n">
-        <v>255.47</v>
+        <v>50.19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:14:43</t>
+          <t>09:13:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="F66" t="n">
-        <v>6.41</v>
+        <v>5.63</v>
       </c>
       <c r="G66" t="n">
-        <v>77.5</v>
+        <v>98.8</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-104.04</v>
+        <v>-137.12</v>
       </c>
       <c r="K66" t="n">
-        <v>114.22</v>
+        <v>-14.91</v>
       </c>
       <c r="L66" t="n">
-        <v>154.5</v>
+        <v>137.93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:15:53</t>
+          <t>09:14:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="F67" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="G67" t="n">
-        <v>76.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>-133.47</v>
+        <v>19.6</v>
       </c>
       <c r="K67" t="n">
-        <v>49.31</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>142.28</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:19:41</t>
+          <t>09:17:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="F68" t="n">
-        <v>6.07</v>
+        <v>5.76</v>
       </c>
       <c r="G68" t="n">
-        <v>90.3</v>
+        <v>94.3</v>
       </c>
       <c r="H68" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>92.73999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="K68" t="n">
-        <v>60.73</v>
+        <v>59.36</v>
       </c>
       <c r="L68" t="n">
-        <v>110.85</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:21:16</t>
+          <t>09:19:09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="F69" t="n">
-        <v>5.62</v>
+        <v>5.3</v>
       </c>
       <c r="G69" t="n">
-        <v>109.8</v>
+        <v>99.2</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-131.76</v>
+        <v>-42.2</v>
       </c>
       <c r="K69" t="n">
-        <v>237.46</v>
+        <v>157.11</v>
       </c>
       <c r="L69" t="n">
-        <v>271.56</v>
+        <v>162.68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:23:31</t>
+          <t>09:21:31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="F70" t="n">
-        <v>6.74</v>
+        <v>6.41</v>
       </c>
       <c r="G70" t="n">
-        <v>101.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-235.4</v>
+        <v>-179.63</v>
       </c>
       <c r="K70" t="n">
-        <v>-112.64</v>
+        <v>169.98</v>
       </c>
       <c r="L70" t="n">
-        <v>260.96</v>
+        <v>247.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:28:38</t>
+          <t>09:27:12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="F71" t="n">
-        <v>6.28</v>
+        <v>5.31</v>
       </c>
       <c r="G71" t="n">
-        <v>91.5</v>
+        <v>79.5</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>155.52</v>
+        <v>-117.93</v>
       </c>
       <c r="K71" t="n">
-        <v>86.44</v>
+        <v>291.21</v>
       </c>
       <c r="L71" t="n">
-        <v>177.93</v>
+        <v>314.18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:30:42</t>
+          <t>09:28:08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="F72" t="n">
-        <v>6.58</v>
+        <v>5.74</v>
       </c>
       <c r="G72" t="n">
-        <v>88.8</v>
+        <v>104.1</v>
       </c>
       <c r="H72" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>49.55</v>
+        <v>-321.55</v>
       </c>
       <c r="K72" t="n">
-        <v>32.44</v>
+        <v>170.69</v>
       </c>
       <c r="L72" t="n">
-        <v>59.23</v>
+        <v>364.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:32:05</t>
+          <t>09:30:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="F73" t="n">
-        <v>6.15</v>
+        <v>5.83</v>
       </c>
       <c r="G73" t="n">
-        <v>86.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-286.83</v>
+        <v>-85.88</v>
       </c>
       <c r="K73" t="n">
-        <v>-78.88</v>
+        <v>-114.67</v>
       </c>
       <c r="L73" t="n">
-        <v>297.48</v>
+        <v>143.27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:43:47</t>
+          <t>09:39:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="F74" t="n">
-        <v>6.52</v>
+        <v>5.66</v>
       </c>
       <c r="G74" t="n">
-        <v>84.7</v>
+        <v>87.5</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="I74" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-47.39</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-10.84</v>
+        <v>-79.8</v>
       </c>
       <c r="L74" t="n">
-        <v>48.62</v>
+        <v>122.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:45:19</t>
+          <t>09:41:34</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="F75" t="n">
-        <v>5.88</v>
+        <v>5.95</v>
       </c>
       <c r="G75" t="n">
-        <v>91.2</v>
+        <v>88.7</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I75" t="n">
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.19</v>
+        <v>-50.79</v>
       </c>
       <c r="K75" t="n">
-        <v>-31.88</v>
+        <v>81.2</v>
       </c>
       <c r="L75" t="n">
-        <v>32.04</v>
+        <v>95.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:46:41</t>
+          <t>09:42:49</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="F76" t="n">
-        <v>7.21</v>
+        <v>6.11</v>
       </c>
       <c r="G76" t="n">
-        <v>94.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>28.49</v>
+        <v>79.92</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.87</v>
+        <v>-38.71</v>
       </c>
       <c r="L76" t="n">
-        <v>40.56</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:50:16</t>
+          <t>09:48:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="F77" t="n">
-        <v>6.38</v>
+        <v>6.41</v>
       </c>
       <c r="G77" t="n">
-        <v>97.7</v>
+        <v>105.6</v>
       </c>
       <c r="H77" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-48.87</v>
+        <v>137.26</v>
       </c>
       <c r="K77" t="n">
-        <v>-37.88</v>
+        <v>33.25</v>
       </c>
       <c r="L77" t="n">
-        <v>61.83</v>
+        <v>141.23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:52:28</t>
+          <t>09:51:03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="F78" t="n">
         <v>6.43</v>
       </c>
       <c r="G78" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="H78" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.34</v>
+        <v>36.13</v>
       </c>
       <c r="K78" t="n">
-        <v>-21.84</v>
+        <v>-69.86</v>
       </c>
       <c r="L78" t="n">
-        <v>39.02</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:53:45</t>
+          <t>09:53:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="F79" t="n">
-        <v>5.84</v>
+        <v>5.17</v>
       </c>
       <c r="G79" t="n">
-        <v>103.5</v>
+        <v>98.8</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I79" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J79" t="n">
-        <v>-60.25</v>
+        <v>32.65</v>
       </c>
       <c r="K79" t="n">
-        <v>-65.97</v>
+        <v>-145.65</v>
       </c>
       <c r="L79" t="n">
-        <v>89.34</v>
+        <v>149.27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:59:26</t>
+          <t>09:58:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="F80" t="n">
-        <v>5.93</v>
+        <v>6.63</v>
       </c>
       <c r="G80" t="n">
-        <v>97.7</v>
+        <v>83.8</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>5.8</v>
+        <v>37.17</v>
       </c>
       <c r="K80" t="n">
-        <v>97.31</v>
+        <v>139.87</v>
       </c>
       <c r="L80" t="n">
-        <v>97.48</v>
+        <v>144.72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:01:45</t>
+          <t>10:00:50</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="F81" t="n">
-        <v>6.33</v>
+        <v>5.95</v>
       </c>
       <c r="G81" t="n">
-        <v>80</v>
+        <v>91.5</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-68.34999999999999</v>
+        <v>-15.36</v>
       </c>
       <c r="K81" t="n">
-        <v>-2.68</v>
+        <v>-86.97</v>
       </c>
       <c r="L81" t="n">
-        <v>68.40000000000001</v>
+        <v>88.31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:02:43</t>
+          <t>10:03:04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="F82" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="G82" t="n">
-        <v>84.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>99.20999999999999</v>
+        <v>27.98</v>
       </c>
       <c r="K82" t="n">
-        <v>-84.23</v>
+        <v>77.91</v>
       </c>
       <c r="L82" t="n">
-        <v>130.14</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:07:44</t>
+          <t>10:08:37</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.56</v>
+        <v>2.92</v>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>5.81</v>
       </c>
       <c r="G83" t="n">
-        <v>108.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="I83" t="n">
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>126.31</v>
+        <v>299.31</v>
       </c>
       <c r="K83" t="n">
-        <v>72.23999999999999</v>
+        <v>23.74</v>
       </c>
       <c r="L83" t="n">
-        <v>145.51</v>
+        <v>300.25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:09:12</t>
+          <t>10:09:54</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="F84" t="n">
-        <v>6.14</v>
+        <v>6.36</v>
       </c>
       <c r="G84" t="n">
-        <v>96.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>89.45</v>
+        <v>-75.06999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-151.36</v>
+        <v>303.5</v>
       </c>
       <c r="L84" t="n">
-        <v>175.81</v>
+        <v>312.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:11:10</t>
+          <t>10:11:13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="F85" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="G85" t="n">
-        <v>82.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>48.92</v>
+        <v>-118.52</v>
       </c>
       <c r="K85" t="n">
-        <v>74.31999999999999</v>
+        <v>-148.61</v>
       </c>
       <c r="L85" t="n">
-        <v>88.98</v>
+        <v>190.09</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:16:33</t>
+          <t>10:16:11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="F86" t="n">
-        <v>6.49</v>
+        <v>6.53</v>
       </c>
       <c r="G86" t="n">
-        <v>90.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>-96.81999999999999</v>
+        <v>64.25</v>
       </c>
       <c r="K86" t="n">
-        <v>-232.21</v>
+        <v>126.41</v>
       </c>
       <c r="L86" t="n">
-        <v>251.59</v>
+        <v>141.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:18:34</t>
+          <t>10:17:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="F87" t="n">
-        <v>5.98</v>
+        <v>5.34</v>
       </c>
       <c r="G87" t="n">
-        <v>88.5</v>
+        <v>94.3</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-116.16</v>
+        <v>35.08</v>
       </c>
       <c r="K87" t="n">
-        <v>-18.62</v>
+        <v>-272.92</v>
       </c>
       <c r="L87" t="n">
-        <v>117.64</v>
+        <v>275.16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:21:02</t>
+          <t>10:18:22</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="F88" t="n">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="G88" t="n">
-        <v>94.2</v>
+        <v>93.5</v>
       </c>
       <c r="H88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-374.18</v>
+        <v>162.62</v>
       </c>
       <c r="K88" t="n">
-        <v>-267.31</v>
+        <v>273.49</v>
       </c>
       <c r="L88" t="n">
-        <v>459.86</v>
+        <v>318.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-49.35</v>
+        <v>-38.59</v>
       </c>
       <c r="K14" t="n">
-        <v>63.48</v>
+        <v>49.64</v>
       </c>
       <c r="L14" t="n">
-        <v>80.41</v>
+        <v>62.88</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>54.87</v>
+        <v>51.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.74</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>54.88</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-26.35</v>
+        <v>-26.85</v>
       </c>
       <c r="K16" t="n">
-        <v>46.52</v>
+        <v>47.39</v>
       </c>
       <c r="L16" t="n">
-        <v>53.47</v>
+        <v>54.47</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>21.98</v>
+        <v>36.41</v>
       </c>
       <c r="K17" t="n">
-        <v>5.62</v>
+        <v>9.31</v>
       </c>
       <c r="L17" t="n">
-        <v>22.68</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>59.33</v>
+        <v>46.22</v>
       </c>
       <c r="K18" t="n">
-        <v>16.68</v>
+        <v>12.99</v>
       </c>
       <c r="L18" t="n">
-        <v>61.63</v>
+        <v>48.02</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-15.27</v>
+        <v>-20.74</v>
       </c>
       <c r="K19" t="n">
-        <v>33.53</v>
+        <v>45.56</v>
       </c>
       <c r="L19" t="n">
-        <v>36.84</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>251.45</v>
+        <v>200.51</v>
       </c>
       <c r="K20" t="n">
-        <v>7.93</v>
+        <v>6.32</v>
       </c>
       <c r="L20" t="n">
-        <v>251.57</v>
+        <v>200.61</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>96.04000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K21" t="n">
-        <v>99.97</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>138.63</v>
+        <v>123.12</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>195.43</v>
+        <v>159.01</v>
       </c>
       <c r="K22" t="n">
-        <v>163.47</v>
+        <v>133.01</v>
       </c>
       <c r="L22" t="n">
-        <v>254.79</v>
+        <v>207.31</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>153.78</v>
+        <v>171.03</v>
       </c>
       <c r="K23" t="n">
-        <v>108.13</v>
+        <v>120.26</v>
       </c>
       <c r="L23" t="n">
-        <v>187.98</v>
+        <v>209.07</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>117.85</v>
+        <v>122.08</v>
       </c>
       <c r="K24" t="n">
-        <v>167.45</v>
+        <v>173.45</v>
       </c>
       <c r="L24" t="n">
-        <v>204.76</v>
+        <v>212.11</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>-32.84</v>
+        <v>-42.89</v>
       </c>
       <c r="K25" t="n">
-        <v>84.67</v>
+        <v>110.56</v>
       </c>
       <c r="L25" t="n">
-        <v>90.81999999999999</v>
+        <v>118.59</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>42.62</v>
+        <v>43.53</v>
       </c>
       <c r="K26" t="n">
-        <v>390.74</v>
+        <v>399.11</v>
       </c>
       <c r="L26" t="n">
-        <v>393.05</v>
+        <v>401.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-121.33</v>
+        <v>-172.54</v>
       </c>
       <c r="K27" t="n">
-        <v>32.17</v>
+        <v>45.75</v>
       </c>
       <c r="L27" t="n">
-        <v>125.52</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-194.67</v>
+        <v>-191.37</v>
       </c>
       <c r="K28" t="n">
-        <v>-173.09</v>
+        <v>-170.15</v>
       </c>
       <c r="L28" t="n">
-        <v>260.49</v>
+        <v>256.08</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>9.1</v>
+        <v>7.91</v>
       </c>
       <c r="K29" t="n">
-        <v>-57.02</v>
+        <v>-49.58</v>
       </c>
       <c r="L29" t="n">
-        <v>57.74</v>
+        <v>50.21</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>-38.15</v>
+        <v>-33.62</v>
       </c>
       <c r="K30" t="n">
-        <v>19.79</v>
+        <v>17.44</v>
       </c>
       <c r="L30" t="n">
-        <v>42.98</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-66.64</v>
+        <v>-58.79</v>
       </c>
       <c r="K31" t="n">
-        <v>6.67</v>
+        <v>5.89</v>
       </c>
       <c r="L31" t="n">
-        <v>66.98</v>
+        <v>59.09</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>48.95</v>
+        <v>38.37</v>
       </c>
       <c r="K32" t="n">
-        <v>119.13</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>128.8</v>
+        <v>100.97</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>29.89</v>
+        <v>19.48</v>
       </c>
       <c r="K33" t="n">
-        <v>-173.82</v>
+        <v>-113.3</v>
       </c>
       <c r="L33" t="n">
-        <v>176.38</v>
+        <v>114.96</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>36.34</v>
+        <v>22.46</v>
       </c>
       <c r="K34" t="n">
-        <v>131.11</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>136.06</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>118.22</v>
+        <v>107.43</v>
       </c>
       <c r="K35" t="n">
-        <v>82.23999999999999</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>144.02</v>
+        <v>130.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>172.15</v>
+        <v>154.67</v>
       </c>
       <c r="K36" t="n">
-        <v>-22.25</v>
+        <v>-20</v>
       </c>
       <c r="L36" t="n">
-        <v>173.58</v>
+        <v>155.96</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>-22.79</v>
+        <v>-20.87</v>
       </c>
       <c r="K37" t="n">
-        <v>80.87</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>84.02</v>
+        <v>76.95999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>-97.75</v>
+        <v>-113.98</v>
       </c>
       <c r="K38" t="n">
-        <v>34.94</v>
+        <v>40.74</v>
       </c>
       <c r="L38" t="n">
-        <v>103.81</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>75.44</v>
+        <v>106.55</v>
       </c>
       <c r="K39" t="n">
-        <v>27.13</v>
+        <v>38.32</v>
       </c>
       <c r="L39" t="n">
-        <v>80.17</v>
+        <v>113.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-113.65</v>
+        <v>-112.81</v>
       </c>
       <c r="K40" t="n">
-        <v>170.37</v>
+        <v>169.11</v>
       </c>
       <c r="L40" t="n">
-        <v>204.8</v>
+        <v>203.29</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-212.6</v>
+        <v>-264.06</v>
       </c>
       <c r="K41" t="n">
-        <v>-87.86</v>
+        <v>-109.13</v>
       </c>
       <c r="L41" t="n">
-        <v>230.04</v>
+        <v>285.73</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>140.9</v>
+        <v>218.07</v>
       </c>
       <c r="K42" t="n">
-        <v>8.84</v>
+        <v>13.68</v>
       </c>
       <c r="L42" t="n">
-        <v>141.18</v>
+        <v>218.49</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>47.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-151.84</v>
+        <v>-221.17</v>
       </c>
       <c r="L43" t="n">
-        <v>159.23</v>
+        <v>231.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-23.7</v>
+        <v>-19.61</v>
       </c>
       <c r="K44" t="n">
-        <v>-41.96</v>
+        <v>-34.72</v>
       </c>
       <c r="L44" t="n">
-        <v>48.19</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-68.34</v>
+        <v>-54.97</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.59</v>
+        <v>-5.3</v>
       </c>
       <c r="L45" t="n">
-        <v>68.65000000000001</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.51</v>
+        <v>-28.56</v>
       </c>
       <c r="K46" t="n">
-        <v>32.57</v>
+        <v>26.95</v>
       </c>
       <c r="L46" t="n">
-        <v>47.45</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>-91.72</v>
+        <v>-65.08</v>
       </c>
       <c r="K47" t="n">
-        <v>-44.71</v>
+        <v>-31.72</v>
       </c>
       <c r="L47" t="n">
-        <v>102.04</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-146.25</v>
+        <v>-92.75</v>
       </c>
       <c r="K48" t="n">
-        <v>-46.44</v>
+        <v>-29.45</v>
       </c>
       <c r="L48" t="n">
-        <v>153.45</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.24</v>
+        <v>-14.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-18.46</v>
+        <v>-29.07</v>
       </c>
       <c r="L49" t="n">
-        <v>20.64</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>52.34</v>
+        <v>67.81</v>
       </c>
       <c r="K50" t="n">
-        <v>52.17</v>
+        <v>67.58</v>
       </c>
       <c r="L50" t="n">
-        <v>73.90000000000001</v>
+        <v>95.73</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-104.6</v>
+        <v>-84.18000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>73.73999999999999</v>
+        <v>59.35</v>
       </c>
       <c r="L51" t="n">
-        <v>127.98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>141</v>
+        <v>114.68</v>
       </c>
       <c r="K52" t="n">
-        <v>-48.99</v>
+        <v>-39.84</v>
       </c>
       <c r="L52" t="n">
-        <v>149.26</v>
+        <v>121.4</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-71.58</v>
+        <v>-87.06</v>
       </c>
       <c r="K53" t="n">
-        <v>135.46</v>
+        <v>164.76</v>
       </c>
       <c r="L53" t="n">
-        <v>153.2</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.27</v>
+        <v>-1.54</v>
       </c>
       <c r="K54" t="n">
-        <v>-106.33</v>
+        <v>-128.86</v>
       </c>
       <c r="L54" t="n">
-        <v>106.33</v>
+        <v>128.87</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>-145.73</v>
+        <v>-135.33</v>
       </c>
       <c r="K55" t="n">
-        <v>61.4</v>
+        <v>57.02</v>
       </c>
       <c r="L55" t="n">
-        <v>158.14</v>
+        <v>146.85</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-105.12</v>
+        <v>-182.42</v>
       </c>
       <c r="K56" t="n">
-        <v>56.97</v>
+        <v>98.86</v>
       </c>
       <c r="L56" t="n">
-        <v>119.57</v>
+        <v>207.48</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-6.71</v>
+        <v>-7.45</v>
       </c>
       <c r="K57" t="n">
-        <v>306.78</v>
+        <v>340.42</v>
       </c>
       <c r="L57" t="n">
-        <v>306.85</v>
+        <v>340.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>-181.9</v>
+        <v>-188.08</v>
       </c>
       <c r="K58" t="n">
-        <v>-79.56</v>
+        <v>-82.26000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>198.54</v>
+        <v>205.28</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>28.34</v>
+        <v>35.93</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.53</v>
+        <v>-3.2</v>
       </c>
       <c r="L59" t="n">
-        <v>28.45</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-76.37</v>
+        <v>-50.36</v>
       </c>
       <c r="K60" t="n">
-        <v>77.56999999999999</v>
+        <v>51.15</v>
       </c>
       <c r="L60" t="n">
-        <v>108.85</v>
+        <v>71.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-36.81</v>
+        <v>-40.72</v>
       </c>
       <c r="K61" t="n">
-        <v>-20.3</v>
+        <v>-22.47</v>
       </c>
       <c r="L61" t="n">
-        <v>42.04</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="K62" t="n">
-        <v>-44.17</v>
+        <v>-45.32</v>
       </c>
       <c r="L62" t="n">
-        <v>44.2</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.03</v>
+        <v>-18.64</v>
       </c>
       <c r="K63" t="n">
-        <v>-99.52</v>
+        <v>-84.18000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>101.93</v>
+        <v>86.22</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.51</v>
+        <v>-14.5</v>
       </c>
       <c r="K64" t="n">
-        <v>-31.06</v>
+        <v>-39.14</v>
       </c>
       <c r="L64" t="n">
-        <v>33.12</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-47.42</v>
+        <v>-73.62</v>
       </c>
       <c r="K65" t="n">
-        <v>16.42</v>
+        <v>25.48</v>
       </c>
       <c r="L65" t="n">
-        <v>50.19</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-137.12</v>
+        <v>-132.42</v>
       </c>
       <c r="K66" t="n">
-        <v>-14.91</v>
+        <v>-14.4</v>
       </c>
       <c r="L66" t="n">
-        <v>137.93</v>
+        <v>133.2</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>19.6</v>
+        <v>16.94</v>
       </c>
       <c r="K67" t="n">
-        <v>95.51000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="L67" t="n">
-        <v>97.5</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.9</v>
+        <v>-11.53</v>
       </c>
       <c r="K68" t="n">
-        <v>59.36</v>
+        <v>99.16</v>
       </c>
       <c r="L68" t="n">
-        <v>59.76</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-42.2</v>
+        <v>-41.34</v>
       </c>
       <c r="K69" t="n">
-        <v>157.11</v>
+        <v>153.91</v>
       </c>
       <c r="L69" t="n">
-        <v>162.68</v>
+        <v>159.37</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-179.63</v>
+        <v>-188.03</v>
       </c>
       <c r="K70" t="n">
-        <v>169.98</v>
+        <v>177.93</v>
       </c>
       <c r="L70" t="n">
-        <v>247.3</v>
+        <v>258.87</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-117.93</v>
+        <v>-120.91</v>
       </c>
       <c r="K71" t="n">
-        <v>291.21</v>
+        <v>298.55</v>
       </c>
       <c r="L71" t="n">
-        <v>314.18</v>
+        <v>322.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-321.55</v>
+        <v>-313.23</v>
       </c>
       <c r="K72" t="n">
-        <v>170.69</v>
+        <v>166.27</v>
       </c>
       <c r="L72" t="n">
-        <v>364.05</v>
+        <v>354.62</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-85.88</v>
+        <v>-108.61</v>
       </c>
       <c r="K73" t="n">
-        <v>-114.67</v>
+        <v>-145.02</v>
       </c>
       <c r="L73" t="n">
-        <v>143.27</v>
+        <v>181.18</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>93.54000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="K74" t="n">
-        <v>-79.8</v>
+        <v>-44.02</v>
       </c>
       <c r="L74" t="n">
-        <v>122.95</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-50.79</v>
+        <v>-40.78</v>
       </c>
       <c r="K75" t="n">
-        <v>81.2</v>
+        <v>65.19</v>
       </c>
       <c r="L75" t="n">
-        <v>95.78</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>79.92</v>
+        <v>57.38</v>
       </c>
       <c r="K76" t="n">
-        <v>-38.71</v>
+        <v>-27.79</v>
       </c>
       <c r="L76" t="n">
-        <v>88.8</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>137.26</v>
+        <v>97.7</v>
       </c>
       <c r="K77" t="n">
-        <v>33.25</v>
+        <v>23.66</v>
       </c>
       <c r="L77" t="n">
-        <v>141.23</v>
+        <v>100.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>36.13</v>
+        <v>29.79</v>
       </c>
       <c r="K78" t="n">
-        <v>-69.86</v>
+        <v>-57.59</v>
       </c>
       <c r="L78" t="n">
-        <v>78.65000000000001</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>31</v>
       </c>
       <c r="J79" t="n">
-        <v>32.65</v>
+        <v>19.73</v>
       </c>
       <c r="K79" t="n">
-        <v>-145.65</v>
+        <v>-88.01000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>149.27</v>
+        <v>90.19</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>37.17</v>
+        <v>36.7</v>
       </c>
       <c r="K80" t="n">
-        <v>139.87</v>
+        <v>138.08</v>
       </c>
       <c r="L80" t="n">
-        <v>144.72</v>
+        <v>142.87</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.36</v>
+        <v>-13.94</v>
       </c>
       <c r="K81" t="n">
-        <v>-86.97</v>
+        <v>-78.91</v>
       </c>
       <c r="L81" t="n">
-        <v>88.31</v>
+        <v>80.14</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>27.98</v>
+        <v>30.78</v>
       </c>
       <c r="K82" t="n">
-        <v>77.91</v>
+        <v>85.7</v>
       </c>
       <c r="L82" t="n">
-        <v>82.78</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>299.31</v>
+        <v>283.67</v>
       </c>
       <c r="K83" t="n">
-        <v>23.74</v>
+        <v>22.5</v>
       </c>
       <c r="L83" t="n">
-        <v>300.25</v>
+        <v>284.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-75.06999999999999</v>
+        <v>-64.39</v>
       </c>
       <c r="K84" t="n">
-        <v>303.5</v>
+        <v>260.32</v>
       </c>
       <c r="L84" t="n">
-        <v>312.65</v>
+        <v>268.17</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-118.52</v>
+        <v>-120.13</v>
       </c>
       <c r="K85" t="n">
-        <v>-148.61</v>
+        <v>-150.62</v>
       </c>
       <c r="L85" t="n">
-        <v>190.09</v>
+        <v>192.66</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>64.25</v>
+        <v>82.47</v>
       </c>
       <c r="K86" t="n">
-        <v>126.41</v>
+        <v>162.27</v>
       </c>
       <c r="L86" t="n">
-        <v>141.8</v>
+        <v>182.03</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>35.08</v>
+        <v>40.29</v>
       </c>
       <c r="K87" t="n">
-        <v>-272.92</v>
+        <v>-313.51</v>
       </c>
       <c r="L87" t="n">
-        <v>275.16</v>
+        <v>316.09</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>162.62</v>
+        <v>179.08</v>
       </c>
       <c r="K88" t="n">
-        <v>273.49</v>
+        <v>301.16</v>
       </c>
       <c r="L88" t="n">
-        <v>318.19</v>
+        <v>350.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-38.59</v>
+        <v>-37.62</v>
       </c>
       <c r="K14" t="n">
-        <v>49.64</v>
+        <v>48.4</v>
       </c>
       <c r="L14" t="n">
-        <v>62.88</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>51.09</v>
+        <v>47.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="L15" t="n">
-        <v>51.09</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-26.85</v>
+        <v>-23.12</v>
       </c>
       <c r="K16" t="n">
-        <v>47.39</v>
+        <v>40.82</v>
       </c>
       <c r="L16" t="n">
-        <v>54.47</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>36.41</v>
+        <v>34.23</v>
       </c>
       <c r="K17" t="n">
-        <v>9.31</v>
+        <v>8.75</v>
       </c>
       <c r="L17" t="n">
-        <v>37.58</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>46.22</v>
+        <v>52.98</v>
       </c>
       <c r="K18" t="n">
-        <v>12.99</v>
+        <v>14.89</v>
       </c>
       <c r="L18" t="n">
-        <v>48.02</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-20.74</v>
+        <v>-17.89</v>
       </c>
       <c r="K19" t="n">
-        <v>45.56</v>
+        <v>39.29</v>
       </c>
       <c r="L19" t="n">
-        <v>50.06</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>200.51</v>
+        <v>152.54</v>
       </c>
       <c r="K20" t="n">
-        <v>6.32</v>
+        <v>4.81</v>
       </c>
       <c r="L20" t="n">
-        <v>200.61</v>
+        <v>152.61</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>85.3</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>88.79000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>123.12</v>
+        <v>100.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>159.01</v>
+        <v>118.93</v>
       </c>
       <c r="K22" t="n">
-        <v>133.01</v>
+        <v>99.48</v>
       </c>
       <c r="L22" t="n">
-        <v>207.31</v>
+        <v>155.04</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>171.03</v>
+        <v>108.91</v>
       </c>
       <c r="K23" t="n">
-        <v>120.26</v>
+        <v>76.58</v>
       </c>
       <c r="L23" t="n">
-        <v>209.07</v>
+        <v>133.14</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>122.08</v>
+        <v>81.11</v>
       </c>
       <c r="K24" t="n">
-        <v>173.45</v>
+        <v>115.24</v>
       </c>
       <c r="L24" t="n">
-        <v>212.11</v>
+        <v>140.92</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>-42.89</v>
+        <v>-31.32</v>
       </c>
       <c r="K25" t="n">
-        <v>110.56</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>118.59</v>
+        <v>86.61</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>43.53</v>
+        <v>25.81</v>
       </c>
       <c r="K26" t="n">
-        <v>399.11</v>
+        <v>236.67</v>
       </c>
       <c r="L26" t="n">
-        <v>401.48</v>
+        <v>238.07</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-172.54</v>
+        <v>-116.8</v>
       </c>
       <c r="K27" t="n">
-        <v>45.75</v>
+        <v>30.97</v>
       </c>
       <c r="L27" t="n">
-        <v>178.5</v>
+        <v>120.83</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-191.37</v>
+        <v>-136.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-170.15</v>
+        <v>-121.37</v>
       </c>
       <c r="L28" t="n">
-        <v>256.08</v>
+        <v>182.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>7.91</v>
+        <v>7.71</v>
       </c>
       <c r="K29" t="n">
-        <v>-49.58</v>
+        <v>-48.35</v>
       </c>
       <c r="L29" t="n">
-        <v>50.21</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>-33.62</v>
+        <v>-36.34</v>
       </c>
       <c r="K30" t="n">
-        <v>17.44</v>
+        <v>18.85</v>
       </c>
       <c r="L30" t="n">
-        <v>37.87</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-58.79</v>
+        <v>-52.39</v>
       </c>
       <c r="K31" t="n">
-        <v>5.89</v>
+        <v>5.25</v>
       </c>
       <c r="L31" t="n">
-        <v>59.09</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>38.37</v>
+        <v>33.38</v>
       </c>
       <c r="K32" t="n">
-        <v>93.40000000000001</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>100.97</v>
+        <v>87.83</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>19.48</v>
+        <v>19.06</v>
       </c>
       <c r="K33" t="n">
-        <v>-113.3</v>
+        <v>-110.8</v>
       </c>
       <c r="L33" t="n">
-        <v>114.96</v>
+        <v>112.43</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>22.46</v>
+        <v>25.01</v>
       </c>
       <c r="K34" t="n">
-        <v>81.04000000000001</v>
+        <v>90.23</v>
       </c>
       <c r="L34" t="n">
-        <v>84.09999999999999</v>
+        <v>93.63</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>107.43</v>
+        <v>84.61</v>
       </c>
       <c r="K35" t="n">
-        <v>74.73999999999999</v>
+        <v>58.86</v>
       </c>
       <c r="L35" t="n">
-        <v>130.87</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>154.67</v>
+        <v>116.37</v>
       </c>
       <c r="K36" t="n">
-        <v>-20</v>
+        <v>-15.04</v>
       </c>
       <c r="L36" t="n">
-        <v>155.96</v>
+        <v>117.34</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>-20.87</v>
+        <v>-19.88</v>
       </c>
       <c r="K37" t="n">
-        <v>74.06999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="L37" t="n">
-        <v>76.95999999999999</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>-113.98</v>
+        <v>-87.48999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>40.74</v>
+        <v>31.27</v>
       </c>
       <c r="L38" t="n">
-        <v>121.04</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>106.55</v>
+        <v>74.37</v>
       </c>
       <c r="K39" t="n">
-        <v>38.32</v>
+        <v>26.75</v>
       </c>
       <c r="L39" t="n">
-        <v>113.23</v>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.81</v>
+        <v>-78.31999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>169.11</v>
+        <v>117.41</v>
       </c>
       <c r="L40" t="n">
-        <v>203.29</v>
+        <v>141.13</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-264.06</v>
+        <v>-155.5</v>
       </c>
       <c r="K41" t="n">
-        <v>-109.13</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>285.73</v>
+        <v>168.25</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>218.07</v>
+        <v>128.51</v>
       </c>
       <c r="K42" t="n">
-        <v>13.68</v>
+        <v>8.06</v>
       </c>
       <c r="L42" t="n">
-        <v>218.49</v>
+        <v>128.76</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>69.84999999999999</v>
+        <v>41.09</v>
       </c>
       <c r="K43" t="n">
-        <v>-221.17</v>
+        <v>-130.12</v>
       </c>
       <c r="L43" t="n">
-        <v>231.93</v>
+        <v>136.45</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-19.61</v>
+        <v>-21.07</v>
       </c>
       <c r="K44" t="n">
-        <v>-34.72</v>
+        <v>-37.3</v>
       </c>
       <c r="L44" t="n">
-        <v>39.87</v>
+        <v>42.83</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-54.97</v>
+        <v>-53.93</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="L45" t="n">
-        <v>55.23</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-28.56</v>
+        <v>-30.66</v>
       </c>
       <c r="K46" t="n">
-        <v>26.95</v>
+        <v>28.93</v>
       </c>
       <c r="L46" t="n">
-        <v>39.27</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>-65.08</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-31.72</v>
+        <v>-33.47</v>
       </c>
       <c r="L47" t="n">
-        <v>72.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-92.75</v>
+        <v>-97.87</v>
       </c>
       <c r="K48" t="n">
-        <v>-29.45</v>
+        <v>-31.08</v>
       </c>
       <c r="L48" t="n">
-        <v>97.31</v>
+        <v>102.69</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.56</v>
+        <v>-15.47</v>
       </c>
       <c r="K49" t="n">
-        <v>-29.07</v>
+        <v>-30.9</v>
       </c>
       <c r="L49" t="n">
-        <v>32.52</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>67.81</v>
+        <v>49.28</v>
       </c>
       <c r="K50" t="n">
-        <v>67.58</v>
+        <v>49.12</v>
       </c>
       <c r="L50" t="n">
-        <v>95.73</v>
+        <v>69.58</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-84.18000000000001</v>
+        <v>-77.38</v>
       </c>
       <c r="K51" t="n">
-        <v>59.35</v>
+        <v>54.55</v>
       </c>
       <c r="L51" t="n">
-        <v>103</v>
+        <v>94.68000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>114.68</v>
+        <v>97.84</v>
       </c>
       <c r="K52" t="n">
-        <v>-39.84</v>
+        <v>-33.99</v>
       </c>
       <c r="L52" t="n">
-        <v>121.4</v>
+        <v>103.58</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-87.06</v>
+        <v>-53.26</v>
       </c>
       <c r="K53" t="n">
-        <v>164.76</v>
+        <v>100.79</v>
       </c>
       <c r="L53" t="n">
-        <v>186.35</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.54</v>
+        <v>-1.12</v>
       </c>
       <c r="K54" t="n">
-        <v>-128.86</v>
+        <v>-93.87</v>
       </c>
       <c r="L54" t="n">
-        <v>128.87</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>-135.33</v>
+        <v>-110</v>
       </c>
       <c r="K55" t="n">
-        <v>57.02</v>
+        <v>46.34</v>
       </c>
       <c r="L55" t="n">
-        <v>146.85</v>
+        <v>119.36</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-182.42</v>
+        <v>-103.76</v>
       </c>
       <c r="K56" t="n">
-        <v>98.86</v>
+        <v>56.23</v>
       </c>
       <c r="L56" t="n">
-        <v>207.48</v>
+        <v>118.02</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-7.45</v>
+        <v>-4.38</v>
       </c>
       <c r="K57" t="n">
-        <v>340.42</v>
+        <v>200.18</v>
       </c>
       <c r="L57" t="n">
-        <v>340.5</v>
+        <v>200.23</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>-188.08</v>
+        <v>-141.54</v>
       </c>
       <c r="K58" t="n">
-        <v>-82.26000000000001</v>
+        <v>-61.9</v>
       </c>
       <c r="L58" t="n">
-        <v>205.28</v>
+        <v>154.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>35.93</v>
+        <v>33.37</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.2</v>
+        <v>-2.97</v>
       </c>
       <c r="L59" t="n">
-        <v>36.08</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-50.36</v>
+        <v>-48.66</v>
       </c>
       <c r="K60" t="n">
-        <v>51.15</v>
+        <v>49.43</v>
       </c>
       <c r="L60" t="n">
-        <v>71.78</v>
+        <v>69.36</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-40.72</v>
+        <v>-34.83</v>
       </c>
       <c r="K61" t="n">
-        <v>-22.47</v>
+        <v>-19.21</v>
       </c>
       <c r="L61" t="n">
-        <v>46.51</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="K62" t="n">
-        <v>-45.32</v>
+        <v>-46.36</v>
       </c>
       <c r="L62" t="n">
-        <v>45.35</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-18.64</v>
+        <v>-16.1</v>
       </c>
       <c r="K63" t="n">
-        <v>-84.18000000000001</v>
+        <v>-72.73999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>86.22</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>-14.5</v>
+        <v>-14.6</v>
       </c>
       <c r="K64" t="n">
-        <v>-39.14</v>
+        <v>-39.4</v>
       </c>
       <c r="L64" t="n">
-        <v>41.74</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-73.62</v>
+        <v>-55.72</v>
       </c>
       <c r="K65" t="n">
-        <v>25.48</v>
+        <v>19.29</v>
       </c>
       <c r="L65" t="n">
-        <v>77.91</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-132.42</v>
+        <v>-99.23</v>
       </c>
       <c r="K66" t="n">
-        <v>-14.4</v>
+        <v>-10.79</v>
       </c>
       <c r="L66" t="n">
-        <v>133.2</v>
+        <v>99.81999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>16.94</v>
+        <v>16.12</v>
       </c>
       <c r="K67" t="n">
-        <v>82.53</v>
+        <v>78.53</v>
       </c>
       <c r="L67" t="n">
-        <v>84.25</v>
+        <v>80.16</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-11.53</v>
+        <v>-8.4</v>
       </c>
       <c r="K68" t="n">
-        <v>99.16</v>
+        <v>72.2</v>
       </c>
       <c r="L68" t="n">
-        <v>99.83</v>
+        <v>72.69</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-41.34</v>
+        <v>-31.74</v>
       </c>
       <c r="K69" t="n">
-        <v>153.91</v>
+        <v>118.16</v>
       </c>
       <c r="L69" t="n">
-        <v>159.37</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-188.03</v>
+        <v>-115.06</v>
       </c>
       <c r="K70" t="n">
-        <v>177.93</v>
+        <v>108.88</v>
       </c>
       <c r="L70" t="n">
-        <v>258.87</v>
+        <v>158.41</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-120.91</v>
+        <v>-77.73</v>
       </c>
       <c r="K71" t="n">
-        <v>298.55</v>
+        <v>191.93</v>
       </c>
       <c r="L71" t="n">
-        <v>322.11</v>
+        <v>207.07</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-313.23</v>
+        <v>-200.78</v>
       </c>
       <c r="K72" t="n">
-        <v>166.27</v>
+        <v>106.58</v>
       </c>
       <c r="L72" t="n">
-        <v>354.62</v>
+        <v>227.31</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-108.61</v>
+        <v>-76.77</v>
       </c>
       <c r="K73" t="n">
-        <v>-145.02</v>
+        <v>-102.51</v>
       </c>
       <c r="L73" t="n">
-        <v>181.18</v>
+        <v>128.07</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>51.6</v>
+        <v>61.76</v>
       </c>
       <c r="K74" t="n">
-        <v>-44.02</v>
+        <v>-52.69</v>
       </c>
       <c r="L74" t="n">
-        <v>67.81999999999999</v>
+        <v>81.18000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-40.78</v>
+        <v>-36.39</v>
       </c>
       <c r="K75" t="n">
-        <v>65.19</v>
+        <v>58.18</v>
       </c>
       <c r="L75" t="n">
-        <v>76.89</v>
+        <v>68.62</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>57.38</v>
+        <v>55.57</v>
       </c>
       <c r="K76" t="n">
-        <v>-27.79</v>
+        <v>-26.92</v>
       </c>
       <c r="L76" t="n">
-        <v>63.75</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>97.7</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>23.66</v>
+        <v>22.6</v>
       </c>
       <c r="L77" t="n">
-        <v>100.53</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>29.79</v>
+        <v>29.61</v>
       </c>
       <c r="K78" t="n">
-        <v>-57.59</v>
+        <v>-57.25</v>
       </c>
       <c r="L78" t="n">
-        <v>64.84</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>31</v>
       </c>
       <c r="J79" t="n">
-        <v>19.73</v>
+        <v>21.95</v>
       </c>
       <c r="K79" t="n">
-        <v>-88.01000000000001</v>
+        <v>-97.89</v>
       </c>
       <c r="L79" t="n">
-        <v>90.19</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>36.7</v>
+        <v>26.48</v>
       </c>
       <c r="K80" t="n">
-        <v>138.08</v>
+        <v>99.62</v>
       </c>
       <c r="L80" t="n">
-        <v>142.87</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.94</v>
+        <v>-13.33</v>
       </c>
       <c r="K81" t="n">
-        <v>-78.91</v>
+        <v>-75.45999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>80.14</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>30.78</v>
+        <v>25.28</v>
       </c>
       <c r="K82" t="n">
-        <v>85.7</v>
+        <v>70.38</v>
       </c>
       <c r="L82" t="n">
-        <v>91.06</v>
+        <v>74.78</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>283.67</v>
+        <v>209.55</v>
       </c>
       <c r="K83" t="n">
-        <v>22.5</v>
+        <v>16.62</v>
       </c>
       <c r="L83" t="n">
-        <v>284.56</v>
+        <v>210.2</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-64.39</v>
+        <v>-42.8</v>
       </c>
       <c r="K84" t="n">
-        <v>260.32</v>
+        <v>173.04</v>
       </c>
       <c r="L84" t="n">
-        <v>268.17</v>
+        <v>178.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-120.13</v>
+        <v>-79.55</v>
       </c>
       <c r="K85" t="n">
-        <v>-150.62</v>
+        <v>-99.73999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>192.66</v>
+        <v>127.58</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>82.47</v>
+        <v>58.52</v>
       </c>
       <c r="K86" t="n">
-        <v>162.27</v>
+        <v>115.15</v>
       </c>
       <c r="L86" t="n">
-        <v>182.03</v>
+        <v>129.17</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>40.29</v>
+        <v>23.64</v>
       </c>
       <c r="K87" t="n">
-        <v>-313.51</v>
+        <v>-183.94</v>
       </c>
       <c r="L87" t="n">
-        <v>316.09</v>
+        <v>185.46</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>179.08</v>
+        <v>105.27</v>
       </c>
       <c r="K88" t="n">
-        <v>301.16</v>
+        <v>177.04</v>
       </c>
       <c r="L88" t="n">
-        <v>350.38</v>
+        <v>205.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-37.62</v>
+        <v>-33.01</v>
       </c>
       <c r="K14" t="n">
-        <v>48.4</v>
+        <v>42.47</v>
       </c>
       <c r="L14" t="n">
-        <v>61.3</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>47.67</v>
+        <v>41.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.64</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>47.68</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.12</v>
+        <v>-20.57</v>
       </c>
       <c r="K16" t="n">
-        <v>40.82</v>
+        <v>36.31</v>
       </c>
       <c r="L16" t="n">
-        <v>46.92</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>34.23</v>
+        <v>31.22</v>
       </c>
       <c r="K17" t="n">
-        <v>8.75</v>
+        <v>7.98</v>
       </c>
       <c r="L17" t="n">
-        <v>35.33</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>52.98</v>
+        <v>47.22</v>
       </c>
       <c r="K18" t="n">
-        <v>14.89</v>
+        <v>13.27</v>
       </c>
       <c r="L18" t="n">
-        <v>55.03</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.89</v>
+        <v>-16.54</v>
       </c>
       <c r="K19" t="n">
-        <v>39.29</v>
+        <v>36.33</v>
       </c>
       <c r="L19" t="n">
-        <v>43.18</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>152.54</v>
+        <v>150.61</v>
       </c>
       <c r="K20" t="n">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="L20" t="n">
-        <v>152.61</v>
+        <v>150.68</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>69.70999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>72.56999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="L21" t="n">
-        <v>100.63</v>
+        <v>97.18000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>118.93</v>
+        <v>116.14</v>
       </c>
       <c r="K22" t="n">
-        <v>99.48</v>
+        <v>97.14</v>
       </c>
       <c r="L22" t="n">
-        <v>155.04</v>
+        <v>151.41</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>108.91</v>
+        <v>110.38</v>
       </c>
       <c r="K23" t="n">
-        <v>76.58</v>
+        <v>77.61</v>
       </c>
       <c r="L23" t="n">
-        <v>133.14</v>
+        <v>134.93</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>81.11</v>
+        <v>82.16</v>
       </c>
       <c r="K24" t="n">
-        <v>115.24</v>
+        <v>116.73</v>
       </c>
       <c r="L24" t="n">
-        <v>140.92</v>
+        <v>142.74</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>-31.32</v>
+        <v>-31.22</v>
       </c>
       <c r="K25" t="n">
-        <v>80.73999999999999</v>
+        <v>80.48</v>
       </c>
       <c r="L25" t="n">
-        <v>86.61</v>
+        <v>86.33</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>25.81</v>
+        <v>26.65</v>
       </c>
       <c r="K26" t="n">
-        <v>236.67</v>
+        <v>244.35</v>
       </c>
       <c r="L26" t="n">
-        <v>238.07</v>
+        <v>245.8</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-116.8</v>
+        <v>-118.49</v>
       </c>
       <c r="K27" t="n">
-        <v>30.97</v>
+        <v>31.42</v>
       </c>
       <c r="L27" t="n">
-        <v>120.83</v>
+        <v>122.59</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-136.5</v>
+        <v>-136.92</v>
       </c>
       <c r="K28" t="n">
-        <v>-121.37</v>
+        <v>-121.74</v>
       </c>
       <c r="L28" t="n">
-        <v>182.66</v>
+        <v>183.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>7.71</v>
+        <v>6.76</v>
       </c>
       <c r="K29" t="n">
-        <v>-48.35</v>
+        <v>-42.41</v>
       </c>
       <c r="L29" t="n">
-        <v>48.96</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>-36.34</v>
+        <v>-31.51</v>
       </c>
       <c r="K30" t="n">
-        <v>18.85</v>
+        <v>16.35</v>
       </c>
       <c r="L30" t="n">
-        <v>40.94</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-52.39</v>
+        <v>-46.87</v>
       </c>
       <c r="K31" t="n">
-        <v>5.25</v>
+        <v>4.69</v>
       </c>
       <c r="L31" t="n">
-        <v>52.66</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>33.38</v>
+        <v>30.85</v>
       </c>
       <c r="K32" t="n">
-        <v>81.23999999999999</v>
+        <v>75.08</v>
       </c>
       <c r="L32" t="n">
-        <v>87.83</v>
+        <v>81.18000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>19.06</v>
+        <v>17.42</v>
       </c>
       <c r="K33" t="n">
-        <v>-110.8</v>
+        <v>-101.26</v>
       </c>
       <c r="L33" t="n">
-        <v>112.43</v>
+        <v>102.75</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>25.01</v>
+        <v>22.43</v>
       </c>
       <c r="K34" t="n">
-        <v>90.23</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>93.63</v>
+        <v>83.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>84.61</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>58.86</v>
+        <v>57.17</v>
       </c>
       <c r="L35" t="n">
-        <v>103.07</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>116.37</v>
+        <v>113.65</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.04</v>
+        <v>-14.69</v>
       </c>
       <c r="L36" t="n">
-        <v>117.34</v>
+        <v>114.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>-19.88</v>
+        <v>-18.85</v>
       </c>
       <c r="K37" t="n">
-        <v>70.56</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>73.31</v>
+        <v>69.51000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>-87.48999999999999</v>
+        <v>-86.63</v>
       </c>
       <c r="K38" t="n">
-        <v>31.27</v>
+        <v>30.97</v>
       </c>
       <c r="L38" t="n">
-        <v>92.91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>74.37</v>
+        <v>74.53</v>
       </c>
       <c r="K39" t="n">
-        <v>26.75</v>
+        <v>26.8</v>
       </c>
       <c r="L39" t="n">
-        <v>79.04000000000001</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-78.31999999999999</v>
+        <v>-78.5</v>
       </c>
       <c r="K40" t="n">
-        <v>117.41</v>
+        <v>117.67</v>
       </c>
       <c r="L40" t="n">
-        <v>141.13</v>
+        <v>141.45</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-155.5</v>
+        <v>-159.32</v>
       </c>
       <c r="K41" t="n">
-        <v>-64.26000000000001</v>
+        <v>-65.84</v>
       </c>
       <c r="L41" t="n">
-        <v>168.25</v>
+        <v>172.39</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>128.51</v>
+        <v>131.72</v>
       </c>
       <c r="K42" t="n">
-        <v>8.06</v>
+        <v>8.26</v>
       </c>
       <c r="L42" t="n">
-        <v>128.76</v>
+        <v>131.98</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>41.09</v>
+        <v>42.25</v>
       </c>
       <c r="K43" t="n">
-        <v>-130.12</v>
+        <v>-133.8</v>
       </c>
       <c r="L43" t="n">
-        <v>136.45</v>
+        <v>140.31</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-21.07</v>
+        <v>-18.44</v>
       </c>
       <c r="K44" t="n">
-        <v>-37.3</v>
+        <v>-32.65</v>
       </c>
       <c r="L44" t="n">
-        <v>42.83</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-53.93</v>
+        <v>-46.63</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.2</v>
+        <v>-4.5</v>
       </c>
       <c r="L45" t="n">
-        <v>54.18</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.66</v>
+        <v>-26.95</v>
       </c>
       <c r="K46" t="n">
-        <v>28.93</v>
+        <v>25.43</v>
       </c>
       <c r="L46" t="n">
-        <v>42.16</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>-68.68000000000001</v>
+        <v>-61.94</v>
       </c>
       <c r="K47" t="n">
-        <v>-33.47</v>
+        <v>-30.19</v>
       </c>
       <c r="L47" t="n">
-        <v>76.40000000000001</v>
+        <v>68.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-97.87</v>
+        <v>-88.27</v>
       </c>
       <c r="K48" t="n">
-        <v>-31.08</v>
+        <v>-28.03</v>
       </c>
       <c r="L48" t="n">
-        <v>102.69</v>
+        <v>92.62</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-15.47</v>
+        <v>-13.93</v>
       </c>
       <c r="K49" t="n">
-        <v>-30.9</v>
+        <v>-27.82</v>
       </c>
       <c r="L49" t="n">
-        <v>34.55</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>49.28</v>
+        <v>48.75</v>
       </c>
       <c r="K50" t="n">
-        <v>49.12</v>
+        <v>48.59</v>
       </c>
       <c r="L50" t="n">
-        <v>69.58</v>
+        <v>68.83</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-77.38</v>
+        <v>-73.93000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>54.55</v>
+        <v>52.12</v>
       </c>
       <c r="L51" t="n">
-        <v>94.68000000000001</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>97.84</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-33.99</v>
+        <v>-32.64</v>
       </c>
       <c r="L52" t="n">
-        <v>103.58</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-53.26</v>
+        <v>-54.47</v>
       </c>
       <c r="K53" t="n">
-        <v>100.79</v>
+        <v>103.08</v>
       </c>
       <c r="L53" t="n">
-        <v>114</v>
+        <v>116.58</v>
       </c>
     </row>
     <row r="54">
@@ -2323,10 +2323,10 @@
         <v>-1.12</v>
       </c>
       <c r="K54" t="n">
-        <v>-93.87</v>
+        <v>-93.79000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>93.88</v>
+        <v>93.79000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>-110</v>
+        <v>-108.22</v>
       </c>
       <c r="K55" t="n">
-        <v>46.34</v>
+        <v>45.59</v>
       </c>
       <c r="L55" t="n">
-        <v>119.36</v>
+        <v>117.43</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-103.76</v>
+        <v>-108.34</v>
       </c>
       <c r="K56" t="n">
-        <v>56.23</v>
+        <v>58.71</v>
       </c>
       <c r="L56" t="n">
-        <v>118.02</v>
+        <v>123.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.38</v>
+        <v>-4.5</v>
       </c>
       <c r="K57" t="n">
-        <v>200.18</v>
+        <v>205.44</v>
       </c>
       <c r="L57" t="n">
-        <v>200.23</v>
+        <v>205.49</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>-141.54</v>
+        <v>-141.43</v>
       </c>
       <c r="K58" t="n">
-        <v>-61.9</v>
+        <v>-61.86</v>
       </c>
       <c r="L58" t="n">
-        <v>154.48</v>
+        <v>154.36</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>33.37</v>
+        <v>29.72</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.97</v>
+        <v>-2.65</v>
       </c>
       <c r="L59" t="n">
-        <v>33.5</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.66</v>
+        <v>-43.59</v>
       </c>
       <c r="K60" t="n">
-        <v>49.43</v>
+        <v>44.28</v>
       </c>
       <c r="L60" t="n">
-        <v>69.36</v>
+        <v>62.14</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.83</v>
+        <v>-31.5</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.21</v>
+        <v>-17.38</v>
       </c>
       <c r="L61" t="n">
-        <v>39.78</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.36</v>
+        <v>-41.88</v>
       </c>
       <c r="L62" t="n">
-        <v>46.39</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-16.1</v>
+        <v>-14.89</v>
       </c>
       <c r="K63" t="n">
-        <v>-72.73999999999999</v>
+        <v>-67.25</v>
       </c>
       <c r="L63" t="n">
-        <v>74.5</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>-14.6</v>
+        <v>-13.23</v>
       </c>
       <c r="K64" t="n">
-        <v>-39.4</v>
+        <v>-35.71</v>
       </c>
       <c r="L64" t="n">
-        <v>42.01</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-55.72</v>
+        <v>-54.41</v>
       </c>
       <c r="K65" t="n">
-        <v>19.29</v>
+        <v>18.83</v>
       </c>
       <c r="L65" t="n">
-        <v>58.96</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-99.23</v>
+        <v>-96.90000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-10.79</v>
+        <v>-10.54</v>
       </c>
       <c r="L66" t="n">
-        <v>99.81999999999999</v>
+        <v>97.48</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>16.12</v>
+        <v>15.28</v>
       </c>
       <c r="K67" t="n">
-        <v>78.53</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>80.16</v>
+        <v>76.01000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.4</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>72.2</v>
+        <v>72.03</v>
       </c>
       <c r="L68" t="n">
-        <v>72.69</v>
+        <v>72.51000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-31.74</v>
+        <v>-31.57</v>
       </c>
       <c r="K69" t="n">
-        <v>118.16</v>
+        <v>117.53</v>
       </c>
       <c r="L69" t="n">
-        <v>122.35</v>
+        <v>121.7</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-115.06</v>
+        <v>-117.2</v>
       </c>
       <c r="K70" t="n">
-        <v>108.88</v>
+        <v>110.9</v>
       </c>
       <c r="L70" t="n">
-        <v>158.41</v>
+        <v>161.36</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-77.73</v>
+        <v>-79.04000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>191.93</v>
+        <v>195.18</v>
       </c>
       <c r="L71" t="n">
-        <v>207.07</v>
+        <v>210.58</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-200.78</v>
+        <v>-203.54</v>
       </c>
       <c r="K72" t="n">
-        <v>106.58</v>
+        <v>108.04</v>
       </c>
       <c r="L72" t="n">
-        <v>227.31</v>
+        <v>230.44</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-76.77</v>
+        <v>-76.69</v>
       </c>
       <c r="K73" t="n">
-        <v>-102.51</v>
+        <v>-102.4</v>
       </c>
       <c r="L73" t="n">
-        <v>128.07</v>
+        <v>127.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>61.76</v>
+        <v>55.1</v>
       </c>
       <c r="K74" t="n">
-        <v>-52.69</v>
+        <v>-47.01</v>
       </c>
       <c r="L74" t="n">
-        <v>81.18000000000001</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-36.39</v>
+        <v>-32.66</v>
       </c>
       <c r="K75" t="n">
-        <v>58.18</v>
+        <v>52.21</v>
       </c>
       <c r="L75" t="n">
-        <v>68.62</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>55.57</v>
+        <v>49.53</v>
       </c>
       <c r="K76" t="n">
-        <v>-26.92</v>
+        <v>-23.99</v>
       </c>
       <c r="L76" t="n">
-        <v>61.75</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>93.31999999999999</v>
+        <v>85.63</v>
       </c>
       <c r="K77" t="n">
-        <v>22.6</v>
+        <v>20.74</v>
       </c>
       <c r="L77" t="n">
-        <v>96.02</v>
+        <v>88.11</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>29.61</v>
+        <v>26.96</v>
       </c>
       <c r="K78" t="n">
-        <v>-57.25</v>
+        <v>-52.12</v>
       </c>
       <c r="L78" t="n">
-        <v>64.45</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>31</v>
       </c>
       <c r="J79" t="n">
-        <v>21.95</v>
+        <v>19.83</v>
       </c>
       <c r="K79" t="n">
-        <v>-97.89</v>
+        <v>-88.44</v>
       </c>
       <c r="L79" t="n">
-        <v>100.32</v>
+        <v>90.63</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>26.48</v>
+        <v>25.99</v>
       </c>
       <c r="K80" t="n">
-        <v>99.62</v>
+        <v>97.8</v>
       </c>
       <c r="L80" t="n">
-        <v>103.08</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.33</v>
+        <v>-12.64</v>
       </c>
       <c r="K81" t="n">
-        <v>-75.45999999999999</v>
+        <v>-71.55</v>
       </c>
       <c r="L81" t="n">
-        <v>76.63</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>25.28</v>
+        <v>24.47</v>
       </c>
       <c r="K82" t="n">
-        <v>70.38</v>
+        <v>68.14</v>
       </c>
       <c r="L82" t="n">
-        <v>74.78</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>209.55</v>
+        <v>206.18</v>
       </c>
       <c r="K83" t="n">
-        <v>16.62</v>
+        <v>16.35</v>
       </c>
       <c r="L83" t="n">
-        <v>210.2</v>
+        <v>206.83</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-42.8</v>
+        <v>-43.11</v>
       </c>
       <c r="K84" t="n">
-        <v>173.04</v>
+        <v>174.29</v>
       </c>
       <c r="L84" t="n">
-        <v>178.26</v>
+        <v>179.55</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-79.55</v>
+        <v>-80.14</v>
       </c>
       <c r="K85" t="n">
-        <v>-99.73999999999999</v>
+        <v>-100.49</v>
       </c>
       <c r="L85" t="n">
-        <v>127.58</v>
+        <v>128.54</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>58.52</v>
+        <v>58.57</v>
       </c>
       <c r="K86" t="n">
-        <v>115.15</v>
+        <v>115.24</v>
       </c>
       <c r="L86" t="n">
-        <v>129.17</v>
+        <v>129.26</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>23.64</v>
+        <v>24.29</v>
       </c>
       <c r="K87" t="n">
-        <v>-183.94</v>
+        <v>-189</v>
       </c>
       <c r="L87" t="n">
-        <v>185.46</v>
+        <v>190.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>105.27</v>
+        <v>107.78</v>
       </c>
       <c r="K88" t="n">
-        <v>177.04</v>
+        <v>181.26</v>
       </c>
       <c r="L88" t="n">
-        <v>205.98</v>
+        <v>210.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="F14" t="n">
-        <v>6.08</v>
+        <v>6.1</v>
       </c>
       <c r="G14" t="n">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-33.01</v>
+        <v>-16.34</v>
       </c>
       <c r="K14" t="n">
-        <v>42.47</v>
+        <v>24.59</v>
       </c>
       <c r="L14" t="n">
-        <v>53.79</v>
+        <v>29.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:39:51</t>
+          <t>06:41:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="F15" t="n">
-        <v>6.49</v>
+        <v>6.21</v>
       </c>
       <c r="G15" t="n">
-        <v>89.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>41.98</v>
+        <v>-20.78</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5600000000000001</v>
+        <v>39.29</v>
       </c>
       <c r="L15" t="n">
-        <v>41.98</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:56</t>
+          <t>06:42:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="F16" t="n">
-        <v>6.07</v>
+        <v>5.9</v>
       </c>
       <c r="G16" t="n">
-        <v>86.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.57</v>
+        <v>13.42</v>
       </c>
       <c r="K16" t="n">
-        <v>36.31</v>
+        <v>30.21</v>
       </c>
       <c r="L16" t="n">
-        <v>41.73</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:45:27</t>
+          <t>06:48:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="F17" t="n">
-        <v>6.29</v>
+        <v>6.09</v>
       </c>
       <c r="G17" t="n">
-        <v>85.5</v>
+        <v>97.5</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>31.22</v>
+        <v>27.33</v>
       </c>
       <c r="K17" t="n">
-        <v>7.98</v>
+        <v>60.96</v>
       </c>
       <c r="L17" t="n">
-        <v>32.23</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:51</t>
+          <t>06:49:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="F18" t="n">
-        <v>5.6</v>
+        <v>6.17</v>
       </c>
       <c r="G18" t="n">
-        <v>91.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>47.22</v>
+        <v>12.31</v>
       </c>
       <c r="K18" t="n">
-        <v>13.27</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>49.05</v>
+        <v>89.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:49:02</t>
+          <t>06:51:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="F19" t="n">
-        <v>6.19</v>
+        <v>5.96</v>
       </c>
       <c r="G19" t="n">
-        <v>94.8</v>
+        <v>88.7</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-16.54</v>
+        <v>-39.9</v>
       </c>
       <c r="K19" t="n">
-        <v>36.33</v>
+        <v>-26.95</v>
       </c>
       <c r="L19" t="n">
-        <v>39.92</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:53:54</t>
+          <t>06:57:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="F20" t="n">
-        <v>6.82</v>
+        <v>5.68</v>
       </c>
       <c r="G20" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>7.4</v>
+        <v>0.3</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>150.61</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>4.75</v>
+        <v>69.37</v>
       </c>
       <c r="L20" t="n">
-        <v>150.68</v>
+        <v>95.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:55:38</t>
+          <t>06:59:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6</v>
+        <v>2.66</v>
       </c>
       <c r="F21" t="n">
-        <v>6.49</v>
+        <v>5.81</v>
       </c>
       <c r="G21" t="n">
-        <v>87.7</v>
+        <v>95.8</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>67.31999999999999</v>
+        <v>-58.53</v>
       </c>
       <c r="K21" t="n">
-        <v>70.08</v>
+        <v>30.63</v>
       </c>
       <c r="L21" t="n">
-        <v>97.18000000000001</v>
+        <v>66.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:57:18</t>
+          <t>07:00:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="F22" t="n">
-        <v>6.09</v>
+        <v>6.66</v>
       </c>
       <c r="G22" t="n">
-        <v>89</v>
+        <v>91.5</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>116.14</v>
+        <v>41.88</v>
       </c>
       <c r="K22" t="n">
-        <v>97.14</v>
+        <v>39.35</v>
       </c>
       <c r="L22" t="n">
-        <v>151.41</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:01:48</t>
+          <t>07:05:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="F23" t="n">
-        <v>5.48</v>
+        <v>6.48</v>
       </c>
       <c r="G23" t="n">
-        <v>82.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>110.38</v>
+        <v>7.32</v>
       </c>
       <c r="K23" t="n">
-        <v>77.61</v>
+        <v>157.38</v>
       </c>
       <c r="L23" t="n">
-        <v>134.93</v>
+        <v>157.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:02:44</t>
+          <t>07:06:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="F24" t="n">
-        <v>6.81</v>
+        <v>6.24</v>
       </c>
       <c r="G24" t="n">
-        <v>75.3</v>
+        <v>89</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>82.16</v>
+        <v>-50.98</v>
       </c>
       <c r="K24" t="n">
-        <v>116.73</v>
+        <v>-73.14</v>
       </c>
       <c r="L24" t="n">
-        <v>142.74</v>
+        <v>89.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:04:47</t>
+          <t>07:08:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="F25" t="n">
-        <v>6.68</v>
+        <v>6.26</v>
       </c>
       <c r="G25" t="n">
-        <v>97.5</v>
+        <v>87.2</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-31.22</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>80.48</v>
+        <v>-14.73</v>
       </c>
       <c r="L25" t="n">
-        <v>86.33</v>
+        <v>82.01000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:09:46</t>
+          <t>07:13:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="F26" t="n">
-        <v>6.56</v>
+        <v>6.07</v>
       </c>
       <c r="G26" t="n">
-        <v>92.8</v>
+        <v>91.3</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>7.9</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>26.65</v>
+        <v>-94.48999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>244.35</v>
+        <v>137.64</v>
       </c>
       <c r="L26" t="n">
-        <v>245.8</v>
+        <v>166.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:11:52</t>
+          <t>07:15:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="F27" t="n">
-        <v>6.24</v>
+        <v>5.78</v>
       </c>
       <c r="G27" t="n">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-118.49</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>31.42</v>
+        <v>10.66</v>
       </c>
       <c r="L27" t="n">
-        <v>122.59</v>
+        <v>93.79000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:14:20</t>
+          <t>07:16:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="F28" t="n">
-        <v>6.75</v>
+        <v>5.54</v>
       </c>
       <c r="G28" t="n">
-        <v>96.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I28" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-136.92</v>
+        <v>74.2</v>
       </c>
       <c r="K28" t="n">
-        <v>-121.74</v>
+        <v>142.83</v>
       </c>
       <c r="L28" t="n">
-        <v>183.22</v>
+        <v>160.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:24:28</t>
+          <t>07:26:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="F29" t="n">
-        <v>6.36</v>
+        <v>5.5</v>
       </c>
       <c r="G29" t="n">
-        <v>100.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>6.76</v>
+        <v>-15.18</v>
       </c>
       <c r="K29" t="n">
-        <v>-42.41</v>
+        <v>36.31</v>
       </c>
       <c r="L29" t="n">
-        <v>42.94</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:25:45</t>
+          <t>07:27:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="F30" t="n">
-        <v>5.96</v>
+        <v>6.55</v>
       </c>
       <c r="G30" t="n">
-        <v>92.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I30" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-31.51</v>
+        <v>-24.2</v>
       </c>
       <c r="K30" t="n">
-        <v>16.35</v>
+        <v>-40.61</v>
       </c>
       <c r="L30" t="n">
-        <v>35.5</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:27:15</t>
+          <t>07:29:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="F31" t="n">
-        <v>6.56</v>
+        <v>6.59</v>
       </c>
       <c r="G31" t="n">
-        <v>97.5</v>
+        <v>89.5</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-46.87</v>
+        <v>-11.66</v>
       </c>
       <c r="K31" t="n">
-        <v>4.69</v>
+        <v>42.74</v>
       </c>
       <c r="L31" t="n">
-        <v>47.11</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:31:33</t>
+          <t>07:32:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
       <c r="F32" t="n">
-        <v>6.58</v>
+        <v>5.97</v>
       </c>
       <c r="G32" t="n">
-        <v>93</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>30.85</v>
+        <v>62.22</v>
       </c>
       <c r="K32" t="n">
-        <v>75.08</v>
+        <v>2.02</v>
       </c>
       <c r="L32" t="n">
-        <v>81.18000000000001</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:32:07</t>
+          <t>07:34:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="F33" t="n">
-        <v>6.57</v>
+        <v>5.76</v>
       </c>
       <c r="G33" t="n">
-        <v>95.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="H33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>17.42</v>
+        <v>-58.99</v>
       </c>
       <c r="K33" t="n">
-        <v>-101.26</v>
+        <v>18.88</v>
       </c>
       <c r="L33" t="n">
-        <v>102.75</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:34:28</t>
+          <t>07:36:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="F34" t="n">
-        <v>6.06</v>
+        <v>6.44</v>
       </c>
       <c r="G34" t="n">
-        <v>74</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I34" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>22.43</v>
+        <v>50.6</v>
       </c>
       <c r="K34" t="n">
-        <v>80.93000000000001</v>
+        <v>-51.65</v>
       </c>
       <c r="L34" t="n">
-        <v>83.98</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:38:44</t>
+          <t>07:41:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="F35" t="n">
-        <v>6.44</v>
+        <v>5.81</v>
       </c>
       <c r="G35" t="n">
-        <v>82.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>82.18000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="K35" t="n">
-        <v>57.17</v>
+        <v>-81.63</v>
       </c>
       <c r="L35" t="n">
-        <v>100.11</v>
+        <v>93.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:41:29</t>
+          <t>07:42:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="F36" t="n">
-        <v>5.94</v>
+        <v>6.23</v>
       </c>
       <c r="G36" t="n">
-        <v>97.3</v>
+        <v>95.5</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>113.65</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-14.69</v>
+        <v>-86.45</v>
       </c>
       <c r="L36" t="n">
-        <v>114.59</v>
+        <v>120.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:43:49</t>
+          <t>07:43:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.74</v>
+        <v>1.05</v>
       </c>
       <c r="F37" t="n">
-        <v>5.86</v>
+        <v>6.22</v>
       </c>
       <c r="G37" t="n">
-        <v>86.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-18.85</v>
+        <v>37.1</v>
       </c>
       <c r="K37" t="n">
-        <v>66.90000000000001</v>
+        <v>-38.08</v>
       </c>
       <c r="L37" t="n">
-        <v>69.51000000000001</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:48:43</t>
+          <t>07:49:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="F38" t="n">
-        <v>6.01</v>
+        <v>6.26</v>
       </c>
       <c r="G38" t="n">
-        <v>77.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-86.63</v>
+        <v>136.49</v>
       </c>
       <c r="K38" t="n">
-        <v>30.97</v>
+        <v>60.56</v>
       </c>
       <c r="L38" t="n">
-        <v>92</v>
+        <v>149.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:51:04</t>
+          <t>07:51:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="F39" t="n">
-        <v>6.22</v>
+        <v>6.29</v>
       </c>
       <c r="G39" t="n">
-        <v>97.2</v>
+        <v>99.2</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>74.53</v>
+        <v>17.92</v>
       </c>
       <c r="K39" t="n">
-        <v>26.8</v>
+        <v>-100.2</v>
       </c>
       <c r="L39" t="n">
-        <v>79.2</v>
+        <v>101.79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:53:39</t>
+          <t>07:53:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="F40" t="n">
-        <v>5.29</v>
+        <v>6.3</v>
       </c>
       <c r="G40" t="n">
-        <v>94.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I40" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-78.5</v>
+        <v>-20.29</v>
       </c>
       <c r="K40" t="n">
-        <v>117.67</v>
+        <v>-94.03</v>
       </c>
       <c r="L40" t="n">
-        <v>141.45</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:57:19</t>
+          <t>07:57:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="F41" t="n">
-        <v>6.4</v>
+        <v>5.95</v>
       </c>
       <c r="G41" t="n">
-        <v>101</v>
+        <v>99.3</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-159.32</v>
+        <v>-24.94</v>
       </c>
       <c r="K41" t="n">
-        <v>-65.84</v>
+        <v>-25.42</v>
       </c>
       <c r="L41" t="n">
-        <v>172.39</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:59:56</t>
+          <t>08:00:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="F42" t="n">
-        <v>6.02</v>
+        <v>5.78</v>
       </c>
       <c r="G42" t="n">
-        <v>86.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>131.72</v>
+        <v>67.14</v>
       </c>
       <c r="K42" t="n">
-        <v>8.26</v>
+        <v>255.06</v>
       </c>
       <c r="L42" t="n">
-        <v>131.98</v>
+        <v>263.75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:01:16</t>
+          <t>08:01:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="F43" t="n">
-        <v>5.96</v>
+        <v>6.12</v>
       </c>
       <c r="G43" t="n">
-        <v>69.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="H43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>42.25</v>
+        <v>30.11</v>
       </c>
       <c r="K43" t="n">
-        <v>-133.8</v>
+        <v>-140.4</v>
       </c>
       <c r="L43" t="n">
-        <v>140.31</v>
+        <v>143.59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:11:20</t>
+          <t>08:11:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="F44" t="n">
-        <v>5.59</v>
+        <v>5.46</v>
       </c>
       <c r="G44" t="n">
-        <v>93.40000000000001</v>
+        <v>103.4</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I44" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.44</v>
+        <v>-33.04</v>
       </c>
       <c r="K44" t="n">
-        <v>-32.65</v>
+        <v>2.6</v>
       </c>
       <c r="L44" t="n">
-        <v>37.5</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:12:36</t>
+          <t>08:13:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="F45" t="n">
-        <v>6.49</v>
+        <v>6.15</v>
       </c>
       <c r="G45" t="n">
-        <v>93.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-46.63</v>
+        <v>-5.22</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.5</v>
+        <v>-55.57</v>
       </c>
       <c r="L45" t="n">
-        <v>46.85</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:14:52</t>
+          <t>08:14:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="F46" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="G46" t="n">
-        <v>94.2</v>
+        <v>77.5</v>
       </c>
       <c r="H46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.95</v>
+        <v>-2.43</v>
       </c>
       <c r="K46" t="n">
-        <v>25.43</v>
+        <v>27.72</v>
       </c>
       <c r="L46" t="n">
-        <v>37.05</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:18:08</t>
+          <t>08:18:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="F47" t="n">
-        <v>5.56</v>
+        <v>5.65</v>
       </c>
       <c r="G47" t="n">
-        <v>90.2</v>
+        <v>102.8</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I47" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-61.94</v>
+        <v>-63.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-30.19</v>
+        <v>-26.04</v>
       </c>
       <c r="L47" t="n">
-        <v>68.91</v>
+        <v>69.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:19:22</t>
+          <t>08:19:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="F48" t="n">
-        <v>5.28</v>
+        <v>6.12</v>
       </c>
       <c r="G48" t="n">
-        <v>90.2</v>
+        <v>94.7</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I48" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-88.27</v>
+        <v>21.35</v>
       </c>
       <c r="K48" t="n">
-        <v>-28.03</v>
+        <v>59.13</v>
       </c>
       <c r="L48" t="n">
-        <v>92.62</v>
+        <v>62.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:21:27</t>
+          <t>08:21:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="F49" t="n">
-        <v>6.91</v>
+        <v>5.62</v>
       </c>
       <c r="G49" t="n">
-        <v>103.3</v>
+        <v>89.5</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-13.93</v>
+        <v>66.23</v>
       </c>
       <c r="K49" t="n">
-        <v>-27.82</v>
+        <v>-1.64</v>
       </c>
       <c r="L49" t="n">
-        <v>31.12</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:25:54</t>
+          <t>08:26:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="F50" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="G50" t="n">
-        <v>71.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>48.75</v>
+        <v>52.76</v>
       </c>
       <c r="K50" t="n">
-        <v>48.59</v>
+        <v>48.03</v>
       </c>
       <c r="L50" t="n">
-        <v>68.83</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:26:45</t>
+          <t>08:28:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="F51" t="n">
-        <v>6.28</v>
+        <v>5.8</v>
       </c>
       <c r="G51" t="n">
-        <v>86.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-73.93000000000001</v>
+        <v>-113.01</v>
       </c>
       <c r="K51" t="n">
-        <v>52.12</v>
+        <v>-14.24</v>
       </c>
       <c r="L51" t="n">
-        <v>90.45</v>
+        <v>113.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:28:06</t>
+          <t>08:29:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="F52" t="n">
-        <v>6.18</v>
+        <v>6.46</v>
       </c>
       <c r="G52" t="n">
-        <v>84.59999999999999</v>
+        <v>101.8</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>93.93000000000001</v>
+        <v>95.19</v>
       </c>
       <c r="K52" t="n">
-        <v>-32.64</v>
+        <v>-15.86</v>
       </c>
       <c r="L52" t="n">
-        <v>99.44</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:32:24</t>
+          <t>08:34:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="F53" t="n">
-        <v>5.83</v>
+        <v>5.45</v>
       </c>
       <c r="G53" t="n">
-        <v>78.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-54.47</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>103.08</v>
+        <v>211.1</v>
       </c>
       <c r="L53" t="n">
-        <v>116.58</v>
+        <v>211.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:33:39</t>
+          <t>08:36:06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="F54" t="n">
-        <v>6.4</v>
+        <v>5.46</v>
       </c>
       <c r="G54" t="n">
-        <v>90.7</v>
+        <v>80.2</v>
       </c>
       <c r="H54" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.12</v>
+        <v>31.55</v>
       </c>
       <c r="K54" t="n">
-        <v>-93.79000000000001</v>
+        <v>-99.55</v>
       </c>
       <c r="L54" t="n">
-        <v>93.79000000000001</v>
+        <v>104.43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:36:03</t>
+          <t>08:38:04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="F55" t="n">
-        <v>6.17</v>
+        <v>5.74</v>
       </c>
       <c r="G55" t="n">
-        <v>92.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-108.22</v>
+        <v>-13.72</v>
       </c>
       <c r="K55" t="n">
-        <v>45.59</v>
+        <v>-87.7</v>
       </c>
       <c r="L55" t="n">
-        <v>117.43</v>
+        <v>88.77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:41:02</t>
+          <t>08:42:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="F56" t="n">
-        <v>5.92</v>
+        <v>6.2</v>
       </c>
       <c r="G56" t="n">
-        <v>84.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="H56" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-108.34</v>
+        <v>7.16</v>
       </c>
       <c r="K56" t="n">
-        <v>58.71</v>
+        <v>-95.63</v>
       </c>
       <c r="L56" t="n">
-        <v>123.23</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:42:13</t>
+          <t>08:45:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="F57" t="n">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
       <c r="G57" t="n">
-        <v>93.5</v>
+        <v>80.7</v>
       </c>
       <c r="H57" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.5</v>
+        <v>-139.51</v>
       </c>
       <c r="K57" t="n">
-        <v>205.44</v>
+        <v>-148.34</v>
       </c>
       <c r="L57" t="n">
-        <v>205.49</v>
+        <v>203.64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:44:23</t>
+          <t>08:47:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="F58" t="n">
-        <v>6.28</v>
+        <v>6.22</v>
       </c>
       <c r="G58" t="n">
-        <v>78.5</v>
+        <v>93.3</v>
       </c>
       <c r="H58" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-141.43</v>
+        <v>154.8</v>
       </c>
       <c r="K58" t="n">
-        <v>-61.86</v>
+        <v>227.42</v>
       </c>
       <c r="L58" t="n">
-        <v>154.36</v>
+        <v>275.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:56:54</t>
+          <t>08:56:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="F59" t="n">
-        <v>5.85</v>
+        <v>6.45</v>
       </c>
       <c r="G59" t="n">
-        <v>99.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>29.72</v>
+        <v>30.85</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.65</v>
+        <v>9.33</v>
       </c>
       <c r="L59" t="n">
-        <v>29.84</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:58:56</t>
+          <t>08:56:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="F60" t="n">
-        <v>6.27</v>
+        <v>6.02</v>
       </c>
       <c r="G60" t="n">
-        <v>85.7</v>
+        <v>84.7</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.59</v>
+        <v>-30.31</v>
       </c>
       <c r="K60" t="n">
-        <v>44.28</v>
+        <v>-36.28</v>
       </c>
       <c r="L60" t="n">
-        <v>62.14</v>
+        <v>47.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:00:17</t>
+          <t>08:58:04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="F61" t="n">
-        <v>5.78</v>
+        <v>5.94</v>
       </c>
       <c r="G61" t="n">
-        <v>96.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-31.5</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.38</v>
+        <v>29.45</v>
       </c>
       <c r="L61" t="n">
-        <v>35.98</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:04:33</t>
+          <t>09:02:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
       <c r="F62" t="n">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="G62" t="n">
-        <v>108.3</v>
+        <v>103.1</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>1.44</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-41.88</v>
+        <v>30.14</v>
       </c>
       <c r="L62" t="n">
-        <v>41.9</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:06:10</t>
+          <t>09:04:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="F63" t="n">
-        <v>6.36</v>
+        <v>5.78</v>
       </c>
       <c r="G63" t="n">
-        <v>108.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.89</v>
+        <v>36.72</v>
       </c>
       <c r="K63" t="n">
-        <v>-67.25</v>
+        <v>-48.83</v>
       </c>
       <c r="L63" t="n">
-        <v>68.88</v>
+        <v>61.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:07:03</t>
+          <t>09:04:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="F64" t="n">
-        <v>5.43</v>
+        <v>5.89</v>
       </c>
       <c r="G64" t="n">
-        <v>87.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I64" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-13.23</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>-35.71</v>
+        <v>-13.97</v>
       </c>
       <c r="L64" t="n">
-        <v>38.08</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:11:21</t>
+          <t>09:10:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.37</v>
+        <v>2.19</v>
       </c>
       <c r="F65" t="n">
-        <v>5.91</v>
+        <v>6.02</v>
       </c>
       <c r="G65" t="n">
-        <v>92.90000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-54.41</v>
+        <v>151.83</v>
       </c>
       <c r="K65" t="n">
-        <v>18.83</v>
+        <v>42.07</v>
       </c>
       <c r="L65" t="n">
-        <v>57.58</v>
+        <v>157.55</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:13:26</t>
+          <t>09:11:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="F66" t="n">
-        <v>5.63</v>
+        <v>6.63</v>
       </c>
       <c r="G66" t="n">
-        <v>98.8</v>
+        <v>81.5</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-96.90000000000001</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-10.54</v>
+        <v>32.06</v>
       </c>
       <c r="L66" t="n">
-        <v>97.48</v>
+        <v>103.89</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:14:10</t>
+          <t>09:12:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="F67" t="n">
-        <v>5.82</v>
+        <v>6.33</v>
       </c>
       <c r="G67" t="n">
-        <v>98.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>15.28</v>
+        <v>-61.91</v>
       </c>
       <c r="K67" t="n">
-        <v>74.45999999999999</v>
+        <v>-23.55</v>
       </c>
       <c r="L67" t="n">
-        <v>76.01000000000001</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:17:56</t>
+          <t>09:16:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="F68" t="n">
-        <v>5.76</v>
+        <v>6.23</v>
       </c>
       <c r="G68" t="n">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="H68" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.380000000000001</v>
+        <v>119.15</v>
       </c>
       <c r="K68" t="n">
-        <v>72.03</v>
+        <v>20.66</v>
       </c>
       <c r="L68" t="n">
-        <v>72.51000000000001</v>
+        <v>120.93</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:19:09</t>
+          <t>09:18:55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="F69" t="n">
-        <v>5.3</v>
+        <v>6.27</v>
       </c>
       <c r="G69" t="n">
-        <v>99.2</v>
+        <v>84.3</v>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-31.57</v>
+        <v>-82.55</v>
       </c>
       <c r="K69" t="n">
-        <v>117.53</v>
+        <v>-114.17</v>
       </c>
       <c r="L69" t="n">
-        <v>121.7</v>
+        <v>140.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:21:31</t>
+          <t>09:20:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="F70" t="n">
-        <v>6.41</v>
+        <v>6.25</v>
       </c>
       <c r="G70" t="n">
-        <v>86.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-117.2</v>
+        <v>-72.59</v>
       </c>
       <c r="K70" t="n">
-        <v>110.9</v>
+        <v>114.21</v>
       </c>
       <c r="L70" t="n">
-        <v>161.36</v>
+        <v>135.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:27:12</t>
+          <t>09:24:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3022,31 +3022,31 @@
         <v>1.42</v>
       </c>
       <c r="F71" t="n">
-        <v>5.31</v>
+        <v>6.32</v>
       </c>
       <c r="G71" t="n">
-        <v>79.5</v>
+        <v>87.3</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-79.04000000000001</v>
+        <v>-147.57</v>
       </c>
       <c r="K71" t="n">
-        <v>195.18</v>
+        <v>-71.59</v>
       </c>
       <c r="L71" t="n">
-        <v>210.58</v>
+        <v>164.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:28:08</t>
+          <t>09:26:11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="F72" t="n">
-        <v>5.74</v>
+        <v>5.48</v>
       </c>
       <c r="G72" t="n">
-        <v>104.1</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-203.54</v>
+        <v>122.23</v>
       </c>
       <c r="K72" t="n">
-        <v>108.04</v>
+        <v>38.56</v>
       </c>
       <c r="L72" t="n">
-        <v>230.44</v>
+        <v>128.17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:30:50</t>
+          <t>09:28:03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="F73" t="n">
-        <v>5.83</v>
+        <v>6.65</v>
       </c>
       <c r="G73" t="n">
-        <v>90.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-76.69</v>
+        <v>129.58</v>
       </c>
       <c r="K73" t="n">
-        <v>-102.4</v>
+        <v>-124.61</v>
       </c>
       <c r="L73" t="n">
-        <v>127.93</v>
+        <v>179.78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:39:07</t>
+          <t>09:38:23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="F74" t="n">
-        <v>5.66</v>
+        <v>6.01</v>
       </c>
       <c r="G74" t="n">
-        <v>87.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>4.3</v>
+        <v>8.1</v>
       </c>
       <c r="I74" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>55.1</v>
+        <v>-16.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.01</v>
+        <v>26.65</v>
       </c>
       <c r="L74" t="n">
-        <v>72.43000000000001</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:41:34</t>
+          <t>09:39:39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="F75" t="n">
-        <v>5.95</v>
+        <v>6.55</v>
       </c>
       <c r="G75" t="n">
-        <v>88.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-32.66</v>
+        <v>38.61</v>
       </c>
       <c r="K75" t="n">
-        <v>52.21</v>
+        <v>29.93</v>
       </c>
       <c r="L75" t="n">
-        <v>61.58</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:42:49</t>
+          <t>09:41:12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="F76" t="n">
-        <v>6.11</v>
+        <v>4.81</v>
       </c>
       <c r="G76" t="n">
-        <v>89.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>49.53</v>
+        <v>12.81</v>
       </c>
       <c r="K76" t="n">
-        <v>-23.99</v>
+        <v>19.65</v>
       </c>
       <c r="L76" t="n">
-        <v>55.03</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:48:48</t>
+          <t>09:46:34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="F77" t="n">
-        <v>6.41</v>
+        <v>6.59</v>
       </c>
       <c r="G77" t="n">
-        <v>105.6</v>
+        <v>93.2</v>
       </c>
       <c r="H77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>85.63</v>
+        <v>17.73</v>
       </c>
       <c r="K77" t="n">
-        <v>20.74</v>
+        <v>-39.01</v>
       </c>
       <c r="L77" t="n">
-        <v>88.11</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:51:03</t>
+          <t>09:48:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="F78" t="n">
-        <v>6.43</v>
+        <v>6.12</v>
       </c>
       <c r="G78" t="n">
-        <v>90.5</v>
+        <v>95</v>
       </c>
       <c r="H78" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>26.96</v>
+        <v>10.11</v>
       </c>
       <c r="K78" t="n">
-        <v>-52.12</v>
+        <v>57.57</v>
       </c>
       <c r="L78" t="n">
-        <v>58.68</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:53:26</t>
+          <t>09:50:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="F79" t="n">
-        <v>5.17</v>
+        <v>6.4</v>
       </c>
       <c r="G79" t="n">
-        <v>98.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>19.83</v>
+        <v>-36.15</v>
       </c>
       <c r="K79" t="n">
-        <v>-88.44</v>
+        <v>38.64</v>
       </c>
       <c r="L79" t="n">
-        <v>90.63</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:58:55</t>
+          <t>09:54:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="F80" t="n">
-        <v>6.63</v>
+        <v>5.89</v>
       </c>
       <c r="G80" t="n">
-        <v>83.8</v>
+        <v>89.8</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>25.99</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>97.8</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>101.2</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:00:50</t>
+          <t>09:56:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="F81" t="n">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="G81" t="n">
-        <v>91.5</v>
+        <v>88</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I81" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.64</v>
+        <v>12.66</v>
       </c>
       <c r="K81" t="n">
-        <v>-71.55</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>72.66</v>
+        <v>71.97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:03:04</t>
+          <t>09:58:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="F82" t="n">
-        <v>5.6</v>
+        <v>6.16</v>
       </c>
       <c r="G82" t="n">
-        <v>83.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="H82" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>24.47</v>
+        <v>-58.91</v>
       </c>
       <c r="K82" t="n">
-        <v>68.14</v>
+        <v>-53.42</v>
       </c>
       <c r="L82" t="n">
-        <v>72.40000000000001</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:08:37</t>
+          <t>10:03:47</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.92</v>
+        <v>1.54</v>
       </c>
       <c r="F83" t="n">
-        <v>5.81</v>
+        <v>6.21</v>
       </c>
       <c r="G83" t="n">
-        <v>95.09999999999999</v>
+        <v>103.6</v>
       </c>
       <c r="H83" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>206.18</v>
+        <v>165.68</v>
       </c>
       <c r="K83" t="n">
-        <v>16.35</v>
+        <v>141.78</v>
       </c>
       <c r="L83" t="n">
-        <v>206.83</v>
+        <v>218.06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:09:54</t>
+          <t>10:05:46</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="F84" t="n">
-        <v>6.36</v>
+        <v>6.03</v>
       </c>
       <c r="G84" t="n">
-        <v>80.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-43.11</v>
+        <v>50.5</v>
       </c>
       <c r="K84" t="n">
-        <v>174.29</v>
+        <v>41.12</v>
       </c>
       <c r="L84" t="n">
-        <v>179.55</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:11:13</t>
+          <t>10:06:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="F85" t="n">
-        <v>5.2</v>
+        <v>6.52</v>
       </c>
       <c r="G85" t="n">
-        <v>99.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-80.14</v>
+        <v>-47.61</v>
       </c>
       <c r="K85" t="n">
-        <v>-100.49</v>
+        <v>54.45</v>
       </c>
       <c r="L85" t="n">
-        <v>128.54</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:16:11</t>
+          <t>10:11:37</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="F86" t="n">
-        <v>6.53</v>
+        <v>5.94</v>
       </c>
       <c r="G86" t="n">
-        <v>93.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I86" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>58.57</v>
+        <v>237.14</v>
       </c>
       <c r="K86" t="n">
-        <v>115.24</v>
+        <v>117.86</v>
       </c>
       <c r="L86" t="n">
-        <v>129.26</v>
+        <v>264.81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:17:21</t>
+          <t>10:13:42</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="F87" t="n">
-        <v>5.34</v>
+        <v>6.35</v>
       </c>
       <c r="G87" t="n">
-        <v>94.3</v>
+        <v>86.3</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>24.29</v>
+        <v>-22.03</v>
       </c>
       <c r="K87" t="n">
-        <v>-189</v>
+        <v>118.68</v>
       </c>
       <c r="L87" t="n">
-        <v>190.56</v>
+        <v>120.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:18:22</t>
+          <t>10:14:48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="F88" t="n">
-        <v>5.7</v>
+        <v>5.45</v>
       </c>
       <c r="G88" t="n">
-        <v>93.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>107.78</v>
+        <v>107.97</v>
       </c>
       <c r="K88" t="n">
-        <v>181.26</v>
+        <v>-40.32</v>
       </c>
       <c r="L88" t="n">
-        <v>210.89</v>
+        <v>115.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.34</v>
+        <v>-17.08</v>
       </c>
       <c r="K14" t="n">
-        <v>24.59</v>
+        <v>25.72</v>
       </c>
       <c r="L14" t="n">
-        <v>29.53</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.78</v>
+        <v>-20.51</v>
       </c>
       <c r="K15" t="n">
-        <v>39.29</v>
+        <v>38.77</v>
       </c>
       <c r="L15" t="n">
-        <v>44.45</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>13.42</v>
+        <v>13.85</v>
       </c>
       <c r="K16" t="n">
-        <v>30.21</v>
+        <v>31.18</v>
       </c>
       <c r="L16" t="n">
-        <v>33.05</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>27.33</v>
+        <v>26.77</v>
       </c>
       <c r="K17" t="n">
-        <v>60.96</v>
+        <v>59.72</v>
       </c>
       <c r="L17" t="n">
-        <v>66.8</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>12.31</v>
+        <v>11.77</v>
       </c>
       <c r="K18" t="n">
-        <v>88.98999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="L18" t="n">
-        <v>89.84</v>
+        <v>85.89</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-39.9</v>
+        <v>-40.46</v>
       </c>
       <c r="K19" t="n">
-        <v>-26.95</v>
+        <v>-27.33</v>
       </c>
       <c r="L19" t="n">
-        <v>48.15</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>64.95999999999999</v>
+        <v>63.69</v>
       </c>
       <c r="K20" t="n">
-        <v>69.37</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>95.03</v>
+        <v>93.18000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-58.53</v>
+        <v>-61.25</v>
       </c>
       <c r="K21" t="n">
-        <v>30.63</v>
+        <v>32.05</v>
       </c>
       <c r="L21" t="n">
-        <v>66.06</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>41.88</v>
+        <v>44.12</v>
       </c>
       <c r="K22" t="n">
-        <v>39.35</v>
+        <v>41.45</v>
       </c>
       <c r="L22" t="n">
-        <v>57.47</v>
+        <v>60.54</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>7.32</v>
+        <v>7.04</v>
       </c>
       <c r="K23" t="n">
-        <v>157.38</v>
+        <v>151.43</v>
       </c>
       <c r="L23" t="n">
-        <v>157.55</v>
+        <v>151.59</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-50.98</v>
+        <v>-52.99</v>
       </c>
       <c r="K24" t="n">
-        <v>-73.14</v>
+        <v>-76.02</v>
       </c>
       <c r="L24" t="n">
-        <v>89.16</v>
+        <v>92.66</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>80.68000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K25" t="n">
-        <v>-14.73</v>
+        <v>-15.28</v>
       </c>
       <c r="L25" t="n">
-        <v>82.01000000000001</v>
+        <v>85.08</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-94.48999999999999</v>
+        <v>-93.88</v>
       </c>
       <c r="K26" t="n">
-        <v>137.64</v>
+        <v>136.76</v>
       </c>
       <c r="L26" t="n">
-        <v>166.95</v>
+        <v>165.88</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>93.18000000000001</v>
+        <v>100.96</v>
       </c>
       <c r="K27" t="n">
-        <v>10.66</v>
+        <v>11.54</v>
       </c>
       <c r="L27" t="n">
-        <v>93.79000000000001</v>
+        <v>101.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>74.2</v>
+        <v>75.05</v>
       </c>
       <c r="K28" t="n">
-        <v>142.83</v>
+        <v>144.46</v>
       </c>
       <c r="L28" t="n">
-        <v>160.95</v>
+        <v>162.79</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.18</v>
+        <v>-15.25</v>
       </c>
       <c r="K29" t="n">
-        <v>36.31</v>
+        <v>36.48</v>
       </c>
       <c r="L29" t="n">
-        <v>39.36</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-24.2</v>
+        <v>-24.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.61</v>
+        <v>-40.44</v>
       </c>
       <c r="L30" t="n">
-        <v>47.28</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.66</v>
+        <v>-11.59</v>
       </c>
       <c r="K31" t="n">
-        <v>42.74</v>
+        <v>42.48</v>
       </c>
       <c r="L31" t="n">
-        <v>44.3</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>62.22</v>
+        <v>61.54</v>
       </c>
       <c r="K32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>62.26</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-58.99</v>
+        <v>-58.68</v>
       </c>
       <c r="K33" t="n">
-        <v>18.88</v>
+        <v>18.78</v>
       </c>
       <c r="L33" t="n">
-        <v>61.94</v>
+        <v>61.61</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>50.6</v>
+        <v>49.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-51.65</v>
+        <v>-50.32</v>
       </c>
       <c r="L34" t="n">
-        <v>72.3</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>45.04</v>
+        <v>44.74</v>
       </c>
       <c r="K35" t="n">
-        <v>-81.63</v>
+        <v>-81.08</v>
       </c>
       <c r="L35" t="n">
-        <v>93.23</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>83.43000000000001</v>
+        <v>80.06</v>
       </c>
       <c r="K36" t="n">
-        <v>-86.45</v>
+        <v>-82.95</v>
       </c>
       <c r="L36" t="n">
-        <v>120.14</v>
+        <v>115.28</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>37.1</v>
+        <v>39.17</v>
       </c>
       <c r="K37" t="n">
-        <v>-38.08</v>
+        <v>-40.2</v>
       </c>
       <c r="L37" t="n">
-        <v>53.17</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>136.49</v>
+        <v>133.32</v>
       </c>
       <c r="K38" t="n">
-        <v>60.56</v>
+        <v>59.15</v>
       </c>
       <c r="L38" t="n">
-        <v>149.32</v>
+        <v>145.85</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>17.92</v>
+        <v>18.31</v>
       </c>
       <c r="K39" t="n">
-        <v>-100.2</v>
+        <v>-102.38</v>
       </c>
       <c r="L39" t="n">
-        <v>101.79</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-20.29</v>
+        <v>-20.7</v>
       </c>
       <c r="K40" t="n">
-        <v>-94.03</v>
+        <v>-95.97</v>
       </c>
       <c r="L40" t="n">
-        <v>96.2</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-24.94</v>
+        <v>-24.47</v>
       </c>
       <c r="K41" t="n">
-        <v>-25.42</v>
+        <v>-24.93</v>
       </c>
       <c r="L41" t="n">
-        <v>35.61</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>67.14</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>255.06</v>
+        <v>245.73</v>
       </c>
       <c r="L42" t="n">
-        <v>263.75</v>
+        <v>254.1</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>30.11</v>
+        <v>30.88</v>
       </c>
       <c r="K43" t="n">
-        <v>-140.4</v>
+        <v>-144.01</v>
       </c>
       <c r="L43" t="n">
-        <v>143.59</v>
+        <v>147.28</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-33.04</v>
+        <v>-34.19</v>
       </c>
       <c r="K44" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="L44" t="n">
-        <v>33.15</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.22</v>
+        <v>-5.09</v>
       </c>
       <c r="K45" t="n">
-        <v>-55.57</v>
+        <v>-54.12</v>
       </c>
       <c r="L45" t="n">
-        <v>55.81</v>
+        <v>54.36</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.43</v>
+        <v>-2.55</v>
       </c>
       <c r="K46" t="n">
-        <v>27.72</v>
+        <v>29.1</v>
       </c>
       <c r="L46" t="n">
-        <v>27.83</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-63.95</v>
+        <v>-63.13</v>
       </c>
       <c r="K47" t="n">
-        <v>-26.04</v>
+        <v>-25.7</v>
       </c>
       <c r="L47" t="n">
-        <v>69.05</v>
+        <v>68.16</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>21.35</v>
+        <v>21.2</v>
       </c>
       <c r="K48" t="n">
-        <v>59.13</v>
+        <v>58.73</v>
       </c>
       <c r="L48" t="n">
-        <v>62.87</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>66.23</v>
+        <v>65.39</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.64</v>
+        <v>-1.62</v>
       </c>
       <c r="L49" t="n">
-        <v>66.25</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>52.76</v>
+        <v>54.65</v>
       </c>
       <c r="K50" t="n">
-        <v>48.03</v>
+        <v>49.75</v>
       </c>
       <c r="L50" t="n">
-        <v>71.34999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-113.01</v>
+        <v>-110.6</v>
       </c>
       <c r="K51" t="n">
-        <v>-14.24</v>
+        <v>-13.94</v>
       </c>
       <c r="L51" t="n">
-        <v>113.91</v>
+        <v>111.48</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>95.19</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-15.86</v>
+        <v>-15.67</v>
       </c>
       <c r="L52" t="n">
-        <v>96.5</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>9.619999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="K53" t="n">
-        <v>211.1</v>
+        <v>199.76</v>
       </c>
       <c r="L53" t="n">
-        <v>211.32</v>
+        <v>199.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>31.55</v>
+        <v>31.81</v>
       </c>
       <c r="K54" t="n">
-        <v>-99.55</v>
+        <v>-100.37</v>
       </c>
       <c r="L54" t="n">
-        <v>104.43</v>
+        <v>105.29</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-13.72</v>
+        <v>-14.15</v>
       </c>
       <c r="K55" t="n">
-        <v>-87.7</v>
+        <v>-90.43000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>88.77</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>7.16</v>
+        <v>7.01</v>
       </c>
       <c r="K56" t="n">
-        <v>-95.63</v>
+        <v>-93.67</v>
       </c>
       <c r="L56" t="n">
-        <v>95.90000000000001</v>
+        <v>93.93000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-139.51</v>
+        <v>-136.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-148.34</v>
+        <v>-145.65</v>
       </c>
       <c r="L57" t="n">
-        <v>203.64</v>
+        <v>199.95</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>154.8</v>
+        <v>147.41</v>
       </c>
       <c r="K58" t="n">
-        <v>227.42</v>
+        <v>216.56</v>
       </c>
       <c r="L58" t="n">
-        <v>275.1</v>
+        <v>261.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>30.85</v>
+        <v>31.88</v>
       </c>
       <c r="K59" t="n">
-        <v>9.33</v>
+        <v>9.65</v>
       </c>
       <c r="L59" t="n">
-        <v>32.23</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.31</v>
+        <v>-30.21</v>
       </c>
       <c r="K60" t="n">
-        <v>-36.28</v>
+        <v>-36.16</v>
       </c>
       <c r="L60" t="n">
-        <v>47.27</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>9.109999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="K61" t="n">
-        <v>29.45</v>
+        <v>31.28</v>
       </c>
       <c r="L61" t="n">
-        <v>30.82</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-70.68000000000001</v>
+        <v>-69.56</v>
       </c>
       <c r="K62" t="n">
-        <v>30.14</v>
+        <v>29.66</v>
       </c>
       <c r="L62" t="n">
-        <v>76.84</v>
+        <v>75.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>36.72</v>
+        <v>36.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.83</v>
+        <v>-48.6</v>
       </c>
       <c r="L63" t="n">
-        <v>61.09</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>83.04000000000001</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.97</v>
+        <v>-13.64</v>
       </c>
       <c r="L64" t="n">
-        <v>84.20999999999999</v>
+        <v>82.20999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>151.83</v>
+        <v>145.21</v>
       </c>
       <c r="K65" t="n">
-        <v>42.07</v>
+        <v>40.23</v>
       </c>
       <c r="L65" t="n">
-        <v>157.55</v>
+        <v>150.68</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>98.81999999999999</v>
+        <v>96.91</v>
       </c>
       <c r="K66" t="n">
-        <v>32.06</v>
+        <v>31.44</v>
       </c>
       <c r="L66" t="n">
-        <v>103.89</v>
+        <v>101.88</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-61.91</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-23.55</v>
+        <v>-24.92</v>
       </c>
       <c r="L67" t="n">
-        <v>66.23999999999999</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>119.15</v>
+        <v>118.32</v>
       </c>
       <c r="K68" t="n">
-        <v>20.66</v>
+        <v>20.51</v>
       </c>
       <c r="L68" t="n">
-        <v>120.93</v>
+        <v>120.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-82.55</v>
+        <v>-81</v>
       </c>
       <c r="K69" t="n">
-        <v>-114.17</v>
+        <v>-112.03</v>
       </c>
       <c r="L69" t="n">
-        <v>140.89</v>
+        <v>138.25</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-72.59</v>
+        <v>-71.13</v>
       </c>
       <c r="K70" t="n">
-        <v>114.21</v>
+        <v>111.91</v>
       </c>
       <c r="L70" t="n">
-        <v>135.33</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-147.57</v>
+        <v>-148.9</v>
       </c>
       <c r="K71" t="n">
-        <v>-71.59</v>
+        <v>-72.23</v>
       </c>
       <c r="L71" t="n">
-        <v>164.01</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>122.23</v>
+        <v>128.07</v>
       </c>
       <c r="K72" t="n">
-        <v>38.56</v>
+        <v>40.4</v>
       </c>
       <c r="L72" t="n">
-        <v>128.17</v>
+        <v>134.29</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>129.58</v>
+        <v>129.84</v>
       </c>
       <c r="K73" t="n">
-        <v>-124.61</v>
+        <v>-124.86</v>
       </c>
       <c r="L73" t="n">
-        <v>179.78</v>
+        <v>180.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-16.47</v>
+        <v>-17.24</v>
       </c>
       <c r="K74" t="n">
-        <v>26.65</v>
+        <v>27.89</v>
       </c>
       <c r="L74" t="n">
-        <v>31.33</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>38.61</v>
+        <v>37.79</v>
       </c>
       <c r="K75" t="n">
-        <v>29.93</v>
+        <v>29.3</v>
       </c>
       <c r="L75" t="n">
-        <v>48.85</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>12.81</v>
+        <v>13.94</v>
       </c>
       <c r="K76" t="n">
-        <v>19.65</v>
+        <v>21.39</v>
       </c>
       <c r="L76" t="n">
-        <v>23.45</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>17.73</v>
+        <v>18.77</v>
       </c>
       <c r="K77" t="n">
-        <v>-39.01</v>
+        <v>-41.29</v>
       </c>
       <c r="L77" t="n">
-        <v>42.85</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>10.11</v>
+        <v>10.09</v>
       </c>
       <c r="K78" t="n">
-        <v>57.57</v>
+        <v>57.44</v>
       </c>
       <c r="L78" t="n">
-        <v>58.45</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-36.15</v>
+        <v>-36.56</v>
       </c>
       <c r="K79" t="n">
-        <v>38.64</v>
+        <v>39.08</v>
       </c>
       <c r="L79" t="n">
-        <v>52.92</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>8.880000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="K80" t="n">
-        <v>-77.09999999999999</v>
+        <v>-78.05</v>
       </c>
       <c r="L80" t="n">
-        <v>77.61</v>
+        <v>78.56999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>12.66</v>
+        <v>12.91</v>
       </c>
       <c r="K81" t="n">
-        <v>70.84999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="L81" t="n">
-        <v>71.97</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-58.91</v>
+        <v>-59.57</v>
       </c>
       <c r="K82" t="n">
-        <v>-53.42</v>
+        <v>-54.02</v>
       </c>
       <c r="L82" t="n">
-        <v>79.53</v>
+        <v>80.42</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>165.68</v>
+        <v>147.84</v>
       </c>
       <c r="K83" t="n">
-        <v>141.78</v>
+        <v>126.52</v>
       </c>
       <c r="L83" t="n">
-        <v>218.06</v>
+        <v>194.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>50.5</v>
+        <v>54.87</v>
       </c>
       <c r="K84" t="n">
-        <v>41.12</v>
+        <v>44.68</v>
       </c>
       <c r="L84" t="n">
-        <v>65.12</v>
+        <v>70.76000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-47.61</v>
+        <v>-51.52</v>
       </c>
       <c r="K85" t="n">
-        <v>54.45</v>
+        <v>58.92</v>
       </c>
       <c r="L85" t="n">
-        <v>72.33</v>
+        <v>78.27</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>237.14</v>
+        <v>227.03</v>
       </c>
       <c r="K86" t="n">
-        <v>117.86</v>
+        <v>112.84</v>
       </c>
       <c r="L86" t="n">
-        <v>264.81</v>
+        <v>253.52</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-22.03</v>
+        <v>-23.09</v>
       </c>
       <c r="K87" t="n">
-        <v>118.68</v>
+        <v>124.37</v>
       </c>
       <c r="L87" t="n">
-        <v>120.71</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>107.97</v>
+        <v>114.97</v>
       </c>
       <c r="K88" t="n">
-        <v>-40.32</v>
+        <v>-42.93</v>
       </c>
       <c r="L88" t="n">
-        <v>115.26</v>
+        <v>122.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.08</v>
+        <v>-17.94</v>
       </c>
       <c r="K14" t="n">
-        <v>25.72</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
-        <v>30.88</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.51</v>
+        <v>-20.2</v>
       </c>
       <c r="K15" t="n">
-        <v>38.77</v>
+        <v>38.18</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>13.85</v>
+        <v>14.35</v>
       </c>
       <c r="K16" t="n">
-        <v>31.18</v>
+        <v>32.29</v>
       </c>
       <c r="L16" t="n">
-        <v>34.12</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>26.77</v>
+        <v>26.14</v>
       </c>
       <c r="K17" t="n">
-        <v>59.72</v>
+        <v>58.31</v>
       </c>
       <c r="L17" t="n">
-        <v>65.45</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>11.77</v>
+        <v>11.15</v>
       </c>
       <c r="K18" t="n">
-        <v>85.08</v>
+        <v>80.61</v>
       </c>
       <c r="L18" t="n">
-        <v>85.89</v>
+        <v>81.38</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-40.46</v>
+        <v>-41.1</v>
       </c>
       <c r="K19" t="n">
-        <v>-27.33</v>
+        <v>-27.76</v>
       </c>
       <c r="L19" t="n">
-        <v>48.83</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>63.69</v>
+        <v>62.24</v>
       </c>
       <c r="K20" t="n">
-        <v>68.01000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>93.18000000000001</v>
+        <v>91.05</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-61.25</v>
+        <v>-64.36</v>
       </c>
       <c r="K21" t="n">
-        <v>32.05</v>
+        <v>33.68</v>
       </c>
       <c r="L21" t="n">
-        <v>69.13</v>
+        <v>72.64</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>44.12</v>
+        <v>46.67</v>
       </c>
       <c r="K22" t="n">
-        <v>41.45</v>
+        <v>43.86</v>
       </c>
       <c r="L22" t="n">
-        <v>60.54</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>7.04</v>
+        <v>6.72</v>
       </c>
       <c r="K23" t="n">
-        <v>151.43</v>
+        <v>144.63</v>
       </c>
       <c r="L23" t="n">
-        <v>151.59</v>
+        <v>144.79</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-52.99</v>
+        <v>-55.28</v>
       </c>
       <c r="K24" t="n">
-        <v>-76.02</v>
+        <v>-79.3</v>
       </c>
       <c r="L24" t="n">
-        <v>92.66</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>83.69</v>
+        <v>87.14</v>
       </c>
       <c r="K25" t="n">
-        <v>-15.28</v>
+        <v>-15.91</v>
       </c>
       <c r="L25" t="n">
-        <v>85.08</v>
+        <v>88.58</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-93.88</v>
+        <v>-93.19</v>
       </c>
       <c r="K26" t="n">
-        <v>136.76</v>
+        <v>135.76</v>
       </c>
       <c r="L26" t="n">
-        <v>165.88</v>
+        <v>164.66</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>100.96</v>
+        <v>109.85</v>
       </c>
       <c r="K27" t="n">
-        <v>11.54</v>
+        <v>12.56</v>
       </c>
       <c r="L27" t="n">
-        <v>101.62</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>75.05</v>
+        <v>76.02</v>
       </c>
       <c r="K28" t="n">
-        <v>144.46</v>
+        <v>146.32</v>
       </c>
       <c r="L28" t="n">
-        <v>162.79</v>
+        <v>164.89</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.25</v>
+        <v>-15.33</v>
       </c>
       <c r="K29" t="n">
-        <v>36.48</v>
+        <v>36.67</v>
       </c>
       <c r="L29" t="n">
-        <v>39.54</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-24.1</v>
+        <v>-23.98</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.44</v>
+        <v>-40.24</v>
       </c>
       <c r="L30" t="n">
-        <v>47.08</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.59</v>
+        <v>-11.51</v>
       </c>
       <c r="K31" t="n">
-        <v>42.48</v>
+        <v>42.2</v>
       </c>
       <c r="L31" t="n">
-        <v>44.04</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>61.54</v>
+        <v>60.76</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="L32" t="n">
-        <v>61.58</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-58.68</v>
+        <v>-58.33</v>
       </c>
       <c r="K33" t="n">
-        <v>18.78</v>
+        <v>18.67</v>
       </c>
       <c r="L33" t="n">
-        <v>61.61</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>49.3</v>
+        <v>47.81</v>
       </c>
       <c r="K34" t="n">
-        <v>-50.32</v>
+        <v>-48.8</v>
       </c>
       <c r="L34" t="n">
-        <v>70.44</v>
+        <v>68.31999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>44.74</v>
+        <v>44.39</v>
       </c>
       <c r="K35" t="n">
-        <v>-81.08</v>
+        <v>-80.44</v>
       </c>
       <c r="L35" t="n">
-        <v>92.59999999999999</v>
+        <v>91.88</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>80.06</v>
+        <v>76.2</v>
       </c>
       <c r="K36" t="n">
-        <v>-82.95</v>
+        <v>-78.95999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>115.28</v>
+        <v>109.73</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>39.17</v>
+        <v>41.52</v>
       </c>
       <c r="K37" t="n">
-        <v>-40.2</v>
+        <v>-42.62</v>
       </c>
       <c r="L37" t="n">
-        <v>56.12</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>133.32</v>
+        <v>129.68</v>
       </c>
       <c r="K38" t="n">
-        <v>59.15</v>
+        <v>57.54</v>
       </c>
       <c r="L38" t="n">
-        <v>145.85</v>
+        <v>141.88</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>18.31</v>
+        <v>18.75</v>
       </c>
       <c r="K39" t="n">
-        <v>-102.38</v>
+        <v>-104.86</v>
       </c>
       <c r="L39" t="n">
-        <v>104</v>
+        <v>106.53</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-20.7</v>
+        <v>-21.18</v>
       </c>
       <c r="K40" t="n">
-        <v>-95.97</v>
+        <v>-98.19</v>
       </c>
       <c r="L40" t="n">
-        <v>98.18000000000001</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-24.47</v>
+        <v>-26.35</v>
       </c>
       <c r="K41" t="n">
-        <v>-24.93</v>
+        <v>-26.85</v>
       </c>
       <c r="L41" t="n">
-        <v>34.93</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>64.68000000000001</v>
+        <v>61.88</v>
       </c>
       <c r="K42" t="n">
-        <v>245.73</v>
+        <v>235.07</v>
       </c>
       <c r="L42" t="n">
-        <v>254.1</v>
+        <v>243.07</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>30.88</v>
+        <v>31.77</v>
       </c>
       <c r="K43" t="n">
-        <v>-144.01</v>
+        <v>-148.13</v>
       </c>
       <c r="L43" t="n">
-        <v>147.28</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-34.19</v>
+        <v>-35.49</v>
       </c>
       <c r="K44" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="L44" t="n">
-        <v>34.29</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.09</v>
+        <v>-4.93</v>
       </c>
       <c r="K45" t="n">
-        <v>-54.12</v>
+        <v>-52.47</v>
       </c>
       <c r="L45" t="n">
-        <v>54.36</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.55</v>
+        <v>-2.69</v>
       </c>
       <c r="K46" t="n">
-        <v>29.1</v>
+        <v>30.68</v>
       </c>
       <c r="L46" t="n">
-        <v>29.21</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-63.13</v>
+        <v>-62.19</v>
       </c>
       <c r="K47" t="n">
-        <v>-25.7</v>
+        <v>-25.32</v>
       </c>
       <c r="L47" t="n">
-        <v>68.16</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>21.2</v>
+        <v>21.04</v>
       </c>
       <c r="K48" t="n">
-        <v>58.73</v>
+        <v>58.26</v>
       </c>
       <c r="L48" t="n">
-        <v>62.44</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>65.39</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.62</v>
+        <v>-1.59</v>
       </c>
       <c r="L49" t="n">
-        <v>65.41</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>54.65</v>
+        <v>56.8</v>
       </c>
       <c r="K50" t="n">
-        <v>49.75</v>
+        <v>51.71</v>
       </c>
       <c r="L50" t="n">
-        <v>73.90000000000001</v>
+        <v>76.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-110.6</v>
+        <v>-107.85</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.94</v>
+        <v>-13.59</v>
       </c>
       <c r="L51" t="n">
-        <v>111.48</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>94.04000000000001</v>
+        <v>92.72</v>
       </c>
       <c r="K52" t="n">
-        <v>-15.67</v>
+        <v>-15.45</v>
       </c>
       <c r="L52" t="n">
-        <v>95.34</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>9.1</v>
+        <v>8.51</v>
       </c>
       <c r="K53" t="n">
-        <v>199.76</v>
+        <v>186.8</v>
       </c>
       <c r="L53" t="n">
-        <v>199.97</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>31.81</v>
+        <v>32.11</v>
       </c>
       <c r="K54" t="n">
-        <v>-100.37</v>
+        <v>-101.31</v>
       </c>
       <c r="L54" t="n">
-        <v>105.29</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.15</v>
+        <v>-14.64</v>
       </c>
       <c r="K55" t="n">
-        <v>-90.43000000000001</v>
+        <v>-93.54000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>91.53</v>
+        <v>94.68000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>7.01</v>
+        <v>7.71</v>
       </c>
       <c r="K56" t="n">
-        <v>-93.67</v>
+        <v>-103.02</v>
       </c>
       <c r="L56" t="n">
-        <v>93.93000000000001</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-136.98</v>
+        <v>-134.1</v>
       </c>
       <c r="K57" t="n">
-        <v>-145.65</v>
+        <v>-142.58</v>
       </c>
       <c r="L57" t="n">
-        <v>199.95</v>
+        <v>195.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>147.41</v>
+        <v>138.97</v>
       </c>
       <c r="K58" t="n">
-        <v>216.56</v>
+        <v>204.15</v>
       </c>
       <c r="L58" t="n">
-        <v>261.97</v>
+        <v>246.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>31.88</v>
+        <v>33.07</v>
       </c>
       <c r="K59" t="n">
-        <v>9.65</v>
+        <v>10</v>
       </c>
       <c r="L59" t="n">
-        <v>33.31</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.21</v>
+        <v>-30.11</v>
       </c>
       <c r="K60" t="n">
-        <v>-36.16</v>
+        <v>-36.03</v>
       </c>
       <c r="L60" t="n">
-        <v>47.12</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>9.68</v>
+        <v>10.33</v>
       </c>
       <c r="K61" t="n">
-        <v>31.28</v>
+        <v>33.39</v>
       </c>
       <c r="L61" t="n">
-        <v>32.75</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-69.56</v>
+        <v>-68.28</v>
       </c>
       <c r="K62" t="n">
-        <v>29.66</v>
+        <v>29.12</v>
       </c>
       <c r="L62" t="n">
-        <v>75.62</v>
+        <v>74.23</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>36.55</v>
+        <v>36.35</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.6</v>
+        <v>-48.34</v>
       </c>
       <c r="L63" t="n">
-        <v>60.81</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>81.06999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.64</v>
+        <v>-13.26</v>
       </c>
       <c r="L64" t="n">
-        <v>82.20999999999999</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>145.21</v>
+        <v>137.64</v>
       </c>
       <c r="K65" t="n">
-        <v>40.23</v>
+        <v>38.14</v>
       </c>
       <c r="L65" t="n">
-        <v>150.68</v>
+        <v>142.82</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>96.91</v>
+        <v>94.73</v>
       </c>
       <c r="K66" t="n">
-        <v>31.44</v>
+        <v>30.73</v>
       </c>
       <c r="L66" t="n">
-        <v>101.88</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-65.48999999999999</v>
+        <v>-69.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-24.92</v>
+        <v>-26.48</v>
       </c>
       <c r="L67" t="n">
-        <v>70.06999999999999</v>
+        <v>74.45999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>118.32</v>
+        <v>117.37</v>
       </c>
       <c r="K68" t="n">
-        <v>20.51</v>
+        <v>20.35</v>
       </c>
       <c r="L68" t="n">
-        <v>120.09</v>
+        <v>119.12</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-81</v>
+        <v>-79.23</v>
       </c>
       <c r="K69" t="n">
-        <v>-112.03</v>
+        <v>-109.59</v>
       </c>
       <c r="L69" t="n">
-        <v>138.25</v>
+        <v>135.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-71.13</v>
+        <v>-69.45999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>111.91</v>
+        <v>109.28</v>
       </c>
       <c r="L70" t="n">
-        <v>132.6</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-148.9</v>
+        <v>-150.43</v>
       </c>
       <c r="K71" t="n">
-        <v>-72.23</v>
+        <v>-72.97</v>
       </c>
       <c r="L71" t="n">
-        <v>165.5</v>
+        <v>167.19</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>128.07</v>
+        <v>134.74</v>
       </c>
       <c r="K72" t="n">
-        <v>40.4</v>
+        <v>42.5</v>
       </c>
       <c r="L72" t="n">
-        <v>134.29</v>
+        <v>141.28</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>129.84</v>
+        <v>130.14</v>
       </c>
       <c r="K73" t="n">
-        <v>-124.86</v>
+        <v>-125.14</v>
       </c>
       <c r="L73" t="n">
-        <v>180.14</v>
+        <v>180.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-17.24</v>
+        <v>-18.12</v>
       </c>
       <c r="K74" t="n">
-        <v>27.89</v>
+        <v>29.31</v>
       </c>
       <c r="L74" t="n">
-        <v>32.79</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>37.79</v>
+        <v>36.86</v>
       </c>
       <c r="K75" t="n">
-        <v>29.3</v>
+        <v>28.57</v>
       </c>
       <c r="L75" t="n">
-        <v>47.82</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>13.94</v>
+        <v>15.24</v>
       </c>
       <c r="K76" t="n">
-        <v>21.39</v>
+        <v>23.38</v>
       </c>
       <c r="L76" t="n">
-        <v>25.53</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>18.77</v>
+        <v>19.95</v>
       </c>
       <c r="K77" t="n">
-        <v>-41.29</v>
+        <v>-43.9</v>
       </c>
       <c r="L77" t="n">
-        <v>45.36</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>10.09</v>
+        <v>10.06</v>
       </c>
       <c r="K78" t="n">
-        <v>57.44</v>
+        <v>57.29</v>
       </c>
       <c r="L78" t="n">
-        <v>58.32</v>
+        <v>58.17</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-36.56</v>
+        <v>-37.03</v>
       </c>
       <c r="K79" t="n">
-        <v>39.08</v>
+        <v>39.58</v>
       </c>
       <c r="L79" t="n">
-        <v>53.52</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>8.99</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-78.05</v>
+        <v>-79.13</v>
       </c>
       <c r="L80" t="n">
-        <v>78.56999999999999</v>
+        <v>79.66</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>12.91</v>
+        <v>13.19</v>
       </c>
       <c r="K81" t="n">
-        <v>72.23</v>
+        <v>73.8</v>
       </c>
       <c r="L81" t="n">
-        <v>73.37</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-59.57</v>
+        <v>-60.33</v>
       </c>
       <c r="K82" t="n">
-        <v>-54.02</v>
+        <v>-54.7</v>
       </c>
       <c r="L82" t="n">
-        <v>80.42</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>147.84</v>
+        <v>140.08</v>
       </c>
       <c r="K83" t="n">
-        <v>126.52</v>
+        <v>119.88</v>
       </c>
       <c r="L83" t="n">
-        <v>194.59</v>
+        <v>184.38</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>54.87</v>
+        <v>59.88</v>
       </c>
       <c r="K84" t="n">
-        <v>44.68</v>
+        <v>48.75</v>
       </c>
       <c r="L84" t="n">
-        <v>70.76000000000001</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-51.52</v>
+        <v>-55.99</v>
       </c>
       <c r="K85" t="n">
-        <v>58.92</v>
+        <v>64.02</v>
       </c>
       <c r="L85" t="n">
-        <v>78.27</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>227.03</v>
+        <v>215.47</v>
       </c>
       <c r="K86" t="n">
-        <v>112.84</v>
+        <v>107.1</v>
       </c>
       <c r="L86" t="n">
-        <v>253.52</v>
+        <v>240.62</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-23.09</v>
+        <v>-24.3</v>
       </c>
       <c r="K87" t="n">
-        <v>124.37</v>
+        <v>130.87</v>
       </c>
       <c r="L87" t="n">
-        <v>126.5</v>
+        <v>133.11</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>114.97</v>
+        <v>122.97</v>
       </c>
       <c r="K88" t="n">
-        <v>-42.93</v>
+        <v>-45.92</v>
       </c>
       <c r="L88" t="n">
-        <v>122.73</v>
+        <v>131.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -628,25 +628,25 @@
         <v>1.29</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1</v>
+        <v>7.01</v>
       </c>
       <c r="G14" t="n">
-        <v>90</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.94</v>
+        <v>-25.22</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>38.69</v>
       </c>
       <c r="L14" t="n">
-        <v>32.42</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>1.45</v>
       </c>
       <c r="F15" t="n">
-        <v>6.21</v>
+        <v>4.31</v>
       </c>
       <c r="G15" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.2</v>
+        <v>-24.88</v>
       </c>
       <c r="K15" t="n">
-        <v>38.18</v>
+        <v>47.52</v>
       </c>
       <c r="L15" t="n">
-        <v>43.2</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>1.35</v>
       </c>
       <c r="F16" t="n">
-        <v>5.9</v>
+        <v>7.01</v>
       </c>
       <c r="G16" t="n">
-        <v>83.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="H16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>14.35</v>
+        <v>20.67</v>
       </c>
       <c r="K16" t="n">
-        <v>32.29</v>
+        <v>45.44</v>
       </c>
       <c r="L16" t="n">
-        <v>35.34</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>1.39</v>
       </c>
       <c r="F17" t="n">
-        <v>6.09</v>
+        <v>7.01</v>
       </c>
       <c r="G17" t="n">
-        <v>97.5</v>
+        <v>91.3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>26.14</v>
+        <v>35.16</v>
       </c>
       <c r="K17" t="n">
-        <v>58.31</v>
+        <v>76.53</v>
       </c>
       <c r="L17" t="n">
-        <v>63.9</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>1.43</v>
       </c>
       <c r="F18" t="n">
-        <v>6.17</v>
+        <v>7.01</v>
       </c>
       <c r="G18" t="n">
-        <v>95.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="H18" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>11.15</v>
+        <v>15.11</v>
       </c>
       <c r="K18" t="n">
-        <v>80.61</v>
+        <v>103.64</v>
       </c>
       <c r="L18" t="n">
-        <v>81.38</v>
+        <v>104.73</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>1.37</v>
       </c>
       <c r="F19" t="n">
-        <v>5.96</v>
+        <v>6.33</v>
       </c>
       <c r="G19" t="n">
         <v>88.7</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.1</v>
+        <v>-54.74</v>
       </c>
       <c r="K19" t="n">
-        <v>-27.76</v>
+        <v>-37.73</v>
       </c>
       <c r="L19" t="n">
-        <v>49.6</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>1.38</v>
       </c>
       <c r="F20" t="n">
-        <v>5.68</v>
+        <v>5.51</v>
       </c>
       <c r="G20" t="n">
-        <v>92.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>0.3</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>62.24</v>
+        <v>80.36</v>
       </c>
       <c r="K20" t="n">
-        <v>66.45999999999999</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>91.05</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>2.66</v>
       </c>
       <c r="F21" t="n">
-        <v>5.81</v>
+        <v>7.01</v>
       </c>
       <c r="G21" t="n">
-        <v>95.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-64.36</v>
+        <v>-68.76000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>33.68</v>
+        <v>46.01</v>
       </c>
       <c r="L21" t="n">
-        <v>72.64</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>1.34</v>
       </c>
       <c r="F22" t="n">
-        <v>6.66</v>
+        <v>2.67</v>
       </c>
       <c r="G22" t="n">
-        <v>91.5</v>
+        <v>102.8</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>46.67</v>
+        <v>56.49</v>
       </c>
       <c r="K22" t="n">
-        <v>43.86</v>
+        <v>45.71</v>
       </c>
       <c r="L22" t="n">
-        <v>64.04000000000001</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>1.29</v>
       </c>
       <c r="F23" t="n">
-        <v>6.48</v>
+        <v>5.87</v>
       </c>
       <c r="G23" t="n">
-        <v>97.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>6.72</v>
+        <v>15.91</v>
       </c>
       <c r="K23" t="n">
-        <v>144.63</v>
+        <v>186.26</v>
       </c>
       <c r="L23" t="n">
-        <v>144.79</v>
+        <v>186.94</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>1.72</v>
       </c>
       <c r="F24" t="n">
-        <v>6.24</v>
+        <v>7.01</v>
       </c>
       <c r="G24" t="n">
-        <v>89</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-55.28</v>
+        <v>-49.01</v>
       </c>
       <c r="K24" t="n">
-        <v>-79.3</v>
+        <v>-100.11</v>
       </c>
       <c r="L24" t="n">
-        <v>96.67</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>1.73</v>
       </c>
       <c r="F25" t="n">
-        <v>6.26</v>
+        <v>7.01</v>
       </c>
       <c r="G25" t="n">
-        <v>87.2</v>
+        <v>94.7</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>87.14</v>
+        <v>121.22</v>
       </c>
       <c r="K25" t="n">
-        <v>-15.91</v>
+        <v>-21.66</v>
       </c>
       <c r="L25" t="n">
-        <v>88.58</v>
+        <v>123.14</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>1.3</v>
       </c>
       <c r="F26" t="n">
-        <v>6.07</v>
+        <v>7.01</v>
       </c>
       <c r="G26" t="n">
-        <v>91.3</v>
+        <v>91</v>
       </c>
       <c r="H26" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>-93.19</v>
+        <v>-119.65</v>
       </c>
       <c r="K26" t="n">
-        <v>135.76</v>
+        <v>209.87</v>
       </c>
       <c r="L26" t="n">
-        <v>164.66</v>
+        <v>241.58</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>1.4</v>
       </c>
       <c r="F27" t="n">
-        <v>5.78</v>
+        <v>4.17</v>
       </c>
       <c r="G27" t="n">
-        <v>92.2</v>
+        <v>85.3</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>109.85</v>
+        <v>145.44</v>
       </c>
       <c r="K27" t="n">
-        <v>12.56</v>
+        <v>17.71</v>
       </c>
       <c r="L27" t="n">
-        <v>110.57</v>
+        <v>146.51</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>1.65</v>
       </c>
       <c r="F28" t="n">
-        <v>5.54</v>
+        <v>6.6</v>
       </c>
       <c r="G28" t="n">
-        <v>95.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>76.02</v>
+        <v>112.99</v>
       </c>
       <c r="K28" t="n">
-        <v>146.32</v>
+        <v>171.29</v>
       </c>
       <c r="L28" t="n">
-        <v>164.89</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>1.37</v>
       </c>
       <c r="F29" t="n">
-        <v>5.5</v>
+        <v>4.68</v>
       </c>
       <c r="G29" t="n">
-        <v>93.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.33</v>
+        <v>-19.59</v>
       </c>
       <c r="K29" t="n">
-        <v>36.67</v>
+        <v>47.79</v>
       </c>
       <c r="L29" t="n">
-        <v>39.74</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>1.54</v>
       </c>
       <c r="F30" t="n">
-        <v>6.55</v>
+        <v>7.01</v>
       </c>
       <c r="G30" t="n">
-        <v>99.09999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-23.98</v>
+        <v>-29.78</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.24</v>
+        <v>-50.66</v>
       </c>
       <c r="L30" t="n">
-        <v>46.84</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>1.27</v>
       </c>
       <c r="F31" t="n">
-        <v>6.59</v>
+        <v>1.57</v>
       </c>
       <c r="G31" t="n">
-        <v>89.5</v>
+        <v>101.4</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.51</v>
+        <v>-10.47</v>
       </c>
       <c r="K31" t="n">
-        <v>42.2</v>
+        <v>39</v>
       </c>
       <c r="L31" t="n">
-        <v>43.74</v>
+        <v>40.38</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>1.42</v>
       </c>
       <c r="F32" t="n">
-        <v>5.97</v>
+        <v>4.43</v>
       </c>
       <c r="G32" t="n">
-        <v>93.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>60.76</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="L32" t="n">
-        <v>60.8</v>
+        <v>69.22</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>1.36</v>
       </c>
       <c r="F33" t="n">
-        <v>5.76</v>
+        <v>5.88</v>
       </c>
       <c r="G33" t="n">
-        <v>88.7</v>
+        <v>84.8</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-58.33</v>
+        <v>-71.40000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>18.67</v>
+        <v>23.32</v>
       </c>
       <c r="L33" t="n">
-        <v>61.25</v>
+        <v>75.11</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>1.34</v>
       </c>
       <c r="F34" t="n">
-        <v>6.44</v>
+        <v>6.51</v>
       </c>
       <c r="G34" t="n">
-        <v>92.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>47.81</v>
+        <v>67.69</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.8</v>
+        <v>-68.42</v>
       </c>
       <c r="L34" t="n">
-        <v>68.31999999999999</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>1.34</v>
       </c>
       <c r="F35" t="n">
-        <v>5.81</v>
+        <v>6.9</v>
       </c>
       <c r="G35" t="n">
-        <v>87.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>44.39</v>
+        <v>63.04</v>
       </c>
       <c r="K35" t="n">
-        <v>-80.44</v>
+        <v>-105.99</v>
       </c>
       <c r="L35" t="n">
-        <v>91.88</v>
+        <v>123.32</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>1.36</v>
       </c>
       <c r="F36" t="n">
-        <v>6.23</v>
+        <v>1.66</v>
       </c>
       <c r="G36" t="n">
-        <v>95.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>76.2</v>
+        <v>78.63</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.95999999999999</v>
+        <v>-79.16</v>
       </c>
       <c r="L36" t="n">
-        <v>109.73</v>
+        <v>111.58</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>1.05</v>
       </c>
       <c r="F37" t="n">
-        <v>6.22</v>
+        <v>1.35</v>
       </c>
       <c r="G37" t="n">
-        <v>96.3</v>
+        <v>94</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>41.52</v>
+        <v>46.43</v>
       </c>
       <c r="K37" t="n">
-        <v>-42.62</v>
+        <v>-43.59</v>
       </c>
       <c r="L37" t="n">
-        <v>59.5</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>1.37</v>
       </c>
       <c r="F38" t="n">
-        <v>6.26</v>
+        <v>1.76</v>
       </c>
       <c r="G38" t="n">
-        <v>66.2</v>
+        <v>94.7</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>129.68</v>
+        <v>125.12</v>
       </c>
       <c r="K38" t="n">
-        <v>57.54</v>
+        <v>50.05</v>
       </c>
       <c r="L38" t="n">
-        <v>141.88</v>
+        <v>134.76</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>1.53</v>
       </c>
       <c r="F39" t="n">
-        <v>6.29</v>
+        <v>4.16</v>
       </c>
       <c r="G39" t="n">
-        <v>99.2</v>
+        <v>95.3</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>18.75</v>
+        <v>33.14</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.86</v>
+        <v>-114.1</v>
       </c>
       <c r="L39" t="n">
-        <v>106.53</v>
+        <v>118.81</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>1.7</v>
       </c>
       <c r="F40" t="n">
-        <v>6.3</v>
+        <v>7.01</v>
       </c>
       <c r="G40" t="n">
-        <v>96</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="I40" t="n">
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-21.18</v>
+        <v>-11.57</v>
       </c>
       <c r="K40" t="n">
-        <v>-98.19</v>
+        <v>-128.08</v>
       </c>
       <c r="L40" t="n">
-        <v>100.44</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>1.43</v>
       </c>
       <c r="F41" t="n">
-        <v>5.95</v>
+        <v>7.01</v>
       </c>
       <c r="G41" t="n">
-        <v>99.3</v>
+        <v>88.7</v>
       </c>
       <c r="H41" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.35</v>
+        <v>21.83</v>
       </c>
       <c r="K41" t="n">
-        <v>-26.85</v>
+        <v>-26.59</v>
       </c>
       <c r="L41" t="n">
-        <v>37.62</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>1.62</v>
       </c>
       <c r="F42" t="n">
-        <v>5.78</v>
+        <v>7.01</v>
       </c>
       <c r="G42" t="n">
-        <v>75.5</v>
+        <v>85.2</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>61.88</v>
+        <v>93.53</v>
       </c>
       <c r="K42" t="n">
-        <v>235.07</v>
+        <v>273.24</v>
       </c>
       <c r="L42" t="n">
-        <v>243.07</v>
+        <v>288.81</v>
       </c>
     </row>
     <row r="43">
@@ -1846,10 +1846,10 @@
         <v>1.3</v>
       </c>
       <c r="F43" t="n">
-        <v>6.12</v>
+        <v>4.22</v>
       </c>
       <c r="G43" t="n">
-        <v>84.5</v>
+        <v>92</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>31.77</v>
+        <v>63.08</v>
       </c>
       <c r="K43" t="n">
-        <v>-148.13</v>
+        <v>-172.88</v>
       </c>
       <c r="L43" t="n">
-        <v>151.5</v>
+        <v>184.03</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>1.46</v>
       </c>
       <c r="F44" t="n">
-        <v>5.46</v>
+        <v>7.01</v>
       </c>
       <c r="G44" t="n">
-        <v>103.4</v>
+        <v>78.8</v>
       </c>
       <c r="H44" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="I44" t="n">
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-35.49</v>
+        <v>-48.28</v>
       </c>
       <c r="K44" t="n">
-        <v>2.79</v>
+        <v>4.23</v>
       </c>
       <c r="L44" t="n">
-        <v>35.6</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>1.49</v>
       </c>
       <c r="F45" t="n">
-        <v>6.15</v>
+        <v>7.01</v>
       </c>
       <c r="G45" t="n">
-        <v>87.8</v>
+        <v>92.5</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.93</v>
+        <v>-5.65</v>
       </c>
       <c r="K45" t="n">
-        <v>-52.47</v>
+        <v>-63.1</v>
       </c>
       <c r="L45" t="n">
-        <v>52.7</v>
+        <v>63.35</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>1.05</v>
       </c>
       <c r="F46" t="n">
-        <v>5.9</v>
+        <v>2.99</v>
       </c>
       <c r="G46" t="n">
-        <v>77.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.69</v>
+        <v>-3.02</v>
       </c>
       <c r="K46" t="n">
-        <v>30.68</v>
+        <v>38.66</v>
       </c>
       <c r="L46" t="n">
-        <v>30.8</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>1.85</v>
       </c>
       <c r="F47" t="n">
-        <v>5.65</v>
+        <v>5.17</v>
       </c>
       <c r="G47" t="n">
-        <v>102.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-62.19</v>
+        <v>-75.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-25.32</v>
+        <v>-30.85</v>
       </c>
       <c r="L47" t="n">
-        <v>67.14</v>
+        <v>81.97</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>1.59</v>
       </c>
       <c r="F48" t="n">
-        <v>6.12</v>
+        <v>7.01</v>
       </c>
       <c r="G48" t="n">
-        <v>94.7</v>
+        <v>92</v>
       </c>
       <c r="H48" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>21.04</v>
+        <v>28.53</v>
       </c>
       <c r="K48" t="n">
-        <v>58.26</v>
+        <v>75.78</v>
       </c>
       <c r="L48" t="n">
-        <v>61.94</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>1.51</v>
       </c>
       <c r="F49" t="n">
-        <v>5.62</v>
+        <v>5.19</v>
       </c>
       <c r="G49" t="n">
-        <v>89.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>64.43000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.59</v>
+        <v>-1.74</v>
       </c>
       <c r="L49" t="n">
-        <v>64.45</v>
+        <v>82.20999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>1.59</v>
       </c>
       <c r="F50" t="n">
-        <v>6.01</v>
+        <v>6.19</v>
       </c>
       <c r="G50" t="n">
-        <v>93.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I50" t="n">
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>56.8</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>51.71</v>
+        <v>63.19</v>
       </c>
       <c r="L50" t="n">
-        <v>76.81</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>1.71</v>
       </c>
       <c r="F51" t="n">
-        <v>5.8</v>
+        <v>4.12</v>
       </c>
       <c r="G51" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-107.85</v>
+        <v>-111.13</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.59</v>
+        <v>-14.21</v>
       </c>
       <c r="L51" t="n">
-        <v>108.7</v>
+        <v>112.03</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>1.65</v>
       </c>
       <c r="F52" t="n">
-        <v>6.46</v>
+        <v>7.01</v>
       </c>
       <c r="G52" t="n">
-        <v>101.8</v>
+        <v>98.7</v>
       </c>
       <c r="H52" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>92.72</v>
+        <v>121.36</v>
       </c>
       <c r="K52" t="n">
-        <v>-15.45</v>
+        <v>-19.98</v>
       </c>
       <c r="L52" t="n">
-        <v>94</v>
+        <v>122.99</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>1.86</v>
       </c>
       <c r="F53" t="n">
-        <v>5.45</v>
+        <v>7.01</v>
       </c>
       <c r="G53" t="n">
-        <v>84.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>8.51</v>
+        <v>17.87</v>
       </c>
       <c r="K53" t="n">
-        <v>186.8</v>
+        <v>208.21</v>
       </c>
       <c r="L53" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>1.21</v>
       </c>
       <c r="F54" t="n">
-        <v>5.46</v>
+        <v>6.4</v>
       </c>
       <c r="G54" t="n">
-        <v>80.2</v>
+        <v>78.7</v>
       </c>
       <c r="H54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>32.11</v>
+        <v>58.66</v>
       </c>
       <c r="K54" t="n">
-        <v>-101.31</v>
+        <v>-147.25</v>
       </c>
       <c r="L54" t="n">
-        <v>106.28</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="55">
@@ -2350,10 +2350,10 @@
         <v>1.67</v>
       </c>
       <c r="F55" t="n">
-        <v>5.74</v>
+        <v>7.01</v>
       </c>
       <c r="G55" t="n">
-        <v>89.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.64</v>
+        <v>-2.09</v>
       </c>
       <c r="K55" t="n">
-        <v>-93.54000000000001</v>
+        <v>-121.63</v>
       </c>
       <c r="L55" t="n">
-        <v>94.68000000000001</v>
+        <v>121.64</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>1.34</v>
       </c>
       <c r="F56" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="G56" t="n">
-        <v>73.5</v>
+        <v>93.7</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>7.71</v>
+        <v>69.16</v>
       </c>
       <c r="K56" t="n">
-        <v>-103.02</v>
+        <v>-123.61</v>
       </c>
       <c r="L56" t="n">
-        <v>103.31</v>
+        <v>141.64</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>1.84</v>
       </c>
       <c r="F57" t="n">
-        <v>6.18</v>
+        <v>7.01</v>
       </c>
       <c r="G57" t="n">
-        <v>80.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-134.1</v>
+        <v>-145.02</v>
       </c>
       <c r="K57" t="n">
-        <v>-142.58</v>
+        <v>-190.15</v>
       </c>
       <c r="L57" t="n">
-        <v>195.73</v>
+        <v>239.14</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>1.72</v>
       </c>
       <c r="F58" t="n">
-        <v>6.22</v>
+        <v>5.2</v>
       </c>
       <c r="G58" t="n">
-        <v>93.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>138.97</v>
+        <v>173.09</v>
       </c>
       <c r="K58" t="n">
-        <v>204.15</v>
+        <v>226.11</v>
       </c>
       <c r="L58" t="n">
-        <v>246.96</v>
+        <v>284.76</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>1.45</v>
       </c>
       <c r="F59" t="n">
-        <v>6.45</v>
+        <v>4.74</v>
       </c>
       <c r="G59" t="n">
-        <v>90.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>33.07</v>
+        <v>42.25</v>
       </c>
       <c r="K59" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="L59" t="n">
-        <v>34.55</v>
+        <v>44.06</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>1.83</v>
       </c>
       <c r="F60" t="n">
-        <v>6.02</v>
+        <v>7.01</v>
       </c>
       <c r="G60" t="n">
-        <v>84.7</v>
+        <v>90</v>
       </c>
       <c r="H60" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.11</v>
+        <v>-38.34</v>
       </c>
       <c r="K60" t="n">
-        <v>-36.03</v>
+        <v>-46.5</v>
       </c>
       <c r="L60" t="n">
-        <v>46.96</v>
+        <v>60.27</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>1.65</v>
       </c>
       <c r="F61" t="n">
-        <v>5.94</v>
+        <v>7.01</v>
       </c>
       <c r="G61" t="n">
-        <v>82.8</v>
+        <v>88.5</v>
       </c>
       <c r="H61" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>10.33</v>
+        <v>13.37</v>
       </c>
       <c r="K61" t="n">
-        <v>33.39</v>
+        <v>40.67</v>
       </c>
       <c r="L61" t="n">
-        <v>34.95</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>1.84</v>
       </c>
       <c r="F62" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="G62" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="H62" t="n">
         <v>5.7</v>
       </c>
-      <c r="G62" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1.5</v>
-      </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-68.28</v>
+        <v>-81.31</v>
       </c>
       <c r="K62" t="n">
-        <v>29.12</v>
+        <v>35.83</v>
       </c>
       <c r="L62" t="n">
-        <v>74.23</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>1.44</v>
       </c>
       <c r="F63" t="n">
-        <v>5.78</v>
+        <v>5.53</v>
       </c>
       <c r="G63" t="n">
-        <v>97.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="H63" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>36.35</v>
+        <v>47.88</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.34</v>
+        <v>-61.93</v>
       </c>
       <c r="L63" t="n">
-        <v>60.48</v>
+        <v>78.28</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>1.81</v>
       </c>
       <c r="F64" t="n">
-        <v>5.89</v>
+        <v>7.01</v>
       </c>
       <c r="G64" t="n">
-        <v>90</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>78.81999999999999</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.26</v>
+        <v>-15</v>
       </c>
       <c r="L64" t="n">
-        <v>79.93000000000001</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>2.19</v>
       </c>
       <c r="F65" t="n">
-        <v>6.02</v>
+        <v>7.01</v>
       </c>
       <c r="G65" t="n">
-        <v>101.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>137.64</v>
+        <v>145.88</v>
       </c>
       <c r="K65" t="n">
-        <v>38.14</v>
+        <v>39.7</v>
       </c>
       <c r="L65" t="n">
-        <v>142.82</v>
+        <v>151.19</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>1.65</v>
       </c>
       <c r="F66" t="n">
-        <v>6.63</v>
+        <v>7.01</v>
       </c>
       <c r="G66" t="n">
-        <v>81.5</v>
+        <v>102.3</v>
       </c>
       <c r="H66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>94.73</v>
+        <v>125.51</v>
       </c>
       <c r="K66" t="n">
-        <v>30.73</v>
+        <v>37.14</v>
       </c>
       <c r="L66" t="n">
-        <v>99.59</v>
+        <v>130.89</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>1.82</v>
       </c>
       <c r="F67" t="n">
-        <v>6.33</v>
+        <v>6.41</v>
       </c>
       <c r="G67" t="n">
-        <v>79.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-69.59</v>
+        <v>-79.06</v>
       </c>
       <c r="K67" t="n">
-        <v>-26.48</v>
+        <v>-38.19</v>
       </c>
       <c r="L67" t="n">
-        <v>74.45999999999999</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>1.16</v>
       </c>
       <c r="F68" t="n">
-        <v>6.23</v>
+        <v>1.87</v>
       </c>
       <c r="G68" t="n">
-        <v>95.7</v>
+        <v>94.3</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>117.37</v>
+        <v>116.78</v>
       </c>
       <c r="K68" t="n">
-        <v>20.35</v>
+        <v>18.76</v>
       </c>
       <c r="L68" t="n">
-        <v>119.12</v>
+        <v>118.28</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>1.64</v>
       </c>
       <c r="F69" t="n">
-        <v>6.27</v>
+        <v>5.54</v>
       </c>
       <c r="G69" t="n">
-        <v>84.3</v>
+        <v>95</v>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-79.23</v>
+        <v>-86.03</v>
       </c>
       <c r="K69" t="n">
-        <v>-109.59</v>
+        <v>-136.39</v>
       </c>
       <c r="L69" t="n">
-        <v>135.23</v>
+        <v>161.26</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>1.4</v>
       </c>
       <c r="F70" t="n">
-        <v>6.25</v>
+        <v>4.46</v>
       </c>
       <c r="G70" t="n">
-        <v>82</v>
+        <v>94.5</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-69.45999999999999</v>
+        <v>-75.97</v>
       </c>
       <c r="K70" t="n">
-        <v>109.28</v>
+        <v>131.71</v>
       </c>
       <c r="L70" t="n">
-        <v>129.49</v>
+        <v>152.05</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>1.42</v>
       </c>
       <c r="F71" t="n">
-        <v>6.32</v>
+        <v>6.76</v>
       </c>
       <c r="G71" t="n">
-        <v>87.3</v>
+        <v>96</v>
       </c>
       <c r="H71" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-150.43</v>
+        <v>-184.37</v>
       </c>
       <c r="K71" t="n">
-        <v>-72.97</v>
+        <v>-110.26</v>
       </c>
       <c r="L71" t="n">
-        <v>167.19</v>
+        <v>214.82</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>1.59</v>
       </c>
       <c r="F72" t="n">
-        <v>5.48</v>
+        <v>6.85</v>
       </c>
       <c r="G72" t="n">
-        <v>90.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>134.74</v>
+        <v>185.32</v>
       </c>
       <c r="K72" t="n">
-        <v>42.5</v>
+        <v>57.49</v>
       </c>
       <c r="L72" t="n">
-        <v>141.28</v>
+        <v>194.03</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>1.51</v>
       </c>
       <c r="F73" t="n">
-        <v>6.65</v>
+        <v>6.29</v>
       </c>
       <c r="G73" t="n">
-        <v>87.59999999999999</v>
+        <v>102.7</v>
       </c>
       <c r="H73" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>130.14</v>
+        <v>183.75</v>
       </c>
       <c r="K73" t="n">
-        <v>-125.14</v>
+        <v>-160.63</v>
       </c>
       <c r="L73" t="n">
-        <v>180.55</v>
+        <v>244.06</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>1.65</v>
       </c>
       <c r="F74" t="n">
-        <v>6.01</v>
+        <v>7.01</v>
       </c>
       <c r="G74" t="n">
-        <v>94.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>8.1</v>
+        <v>1.6</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-18.12</v>
+        <v>-23.87</v>
       </c>
       <c r="K74" t="n">
-        <v>29.31</v>
+        <v>39.75</v>
       </c>
       <c r="L74" t="n">
-        <v>34.46</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>1.76</v>
       </c>
       <c r="F75" t="n">
-        <v>6.55</v>
+        <v>7.01</v>
       </c>
       <c r="G75" t="n">
-        <v>86.59999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="H75" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>36.86</v>
+        <v>47.05</v>
       </c>
       <c r="K75" t="n">
-        <v>28.57</v>
+        <v>36.05</v>
       </c>
       <c r="L75" t="n">
-        <v>46.64</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>1.73</v>
       </c>
       <c r="F76" t="n">
-        <v>4.81</v>
+        <v>7.01</v>
       </c>
       <c r="G76" t="n">
-        <v>96.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>15.24</v>
+        <v>20.63</v>
       </c>
       <c r="K76" t="n">
-        <v>23.38</v>
+        <v>31.52</v>
       </c>
       <c r="L76" t="n">
-        <v>27.9</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>1.77</v>
       </c>
       <c r="F77" t="n">
-        <v>6.59</v>
+        <v>7.01</v>
       </c>
       <c r="G77" t="n">
-        <v>93.2</v>
+        <v>101.3</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>19.95</v>
+        <v>25.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-43.9</v>
+        <v>-51.48</v>
       </c>
       <c r="L77" t="n">
-        <v>48.22</v>
+        <v>57.35</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>1.82</v>
       </c>
       <c r="F78" t="n">
-        <v>6.12</v>
+        <v>7.01</v>
       </c>
       <c r="G78" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H78" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="I78" t="n">
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>10.06</v>
+        <v>13.65</v>
       </c>
       <c r="K78" t="n">
-        <v>57.29</v>
+        <v>70.44</v>
       </c>
       <c r="L78" t="n">
-        <v>58.17</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>1.77</v>
       </c>
       <c r="F79" t="n">
-        <v>6.4</v>
+        <v>5.77</v>
       </c>
       <c r="G79" t="n">
-        <v>92.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-37.03</v>
+        <v>-42.27</v>
       </c>
       <c r="K79" t="n">
-        <v>39.58</v>
+        <v>46.3</v>
       </c>
       <c r="L79" t="n">
-        <v>54.2</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>1.52</v>
       </c>
       <c r="F80" t="n">
-        <v>5.89</v>
+        <v>7.01</v>
       </c>
       <c r="G80" t="n">
-        <v>89.8</v>
+        <v>87.3</v>
       </c>
       <c r="H80" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>9.109999999999999</v>
+        <v>18.21</v>
       </c>
       <c r="K80" t="n">
-        <v>-79.13</v>
+        <v>-107.52</v>
       </c>
       <c r="L80" t="n">
-        <v>79.66</v>
+        <v>109.05</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>1.76</v>
       </c>
       <c r="F81" t="n">
-        <v>6.15</v>
+        <v>7.01</v>
       </c>
       <c r="G81" t="n">
-        <v>88</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>13.19</v>
+        <v>22.54</v>
       </c>
       <c r="K81" t="n">
-        <v>73.8</v>
+        <v>90.31</v>
       </c>
       <c r="L81" t="n">
-        <v>74.97</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>1.62</v>
       </c>
       <c r="F82" t="n">
-        <v>6.16</v>
+        <v>7.01</v>
       </c>
       <c r="G82" t="n">
-        <v>94.8</v>
+        <v>92.8</v>
       </c>
       <c r="H82" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-60.33</v>
+        <v>-69.94</v>
       </c>
       <c r="K82" t="n">
-        <v>-54.7</v>
+        <v>-68.75</v>
       </c>
       <c r="L82" t="n">
-        <v>81.43000000000001</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>1.54</v>
       </c>
       <c r="F83" t="n">
-        <v>6.21</v>
+        <v>3.79</v>
       </c>
       <c r="G83" t="n">
-        <v>103.6</v>
+        <v>93.8</v>
       </c>
       <c r="H83" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>140.08</v>
+        <v>156.27</v>
       </c>
       <c r="K83" t="n">
-        <v>119.88</v>
+        <v>126.88</v>
       </c>
       <c r="L83" t="n">
-        <v>184.38</v>
+        <v>201.29</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>1.51</v>
       </c>
       <c r="F84" t="n">
-        <v>6.03</v>
+        <v>6.11</v>
       </c>
       <c r="G84" t="n">
-        <v>89.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>59.88</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>48.75</v>
+        <v>51.3</v>
       </c>
       <c r="L84" t="n">
-        <v>77.20999999999999</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>1.93</v>
       </c>
       <c r="F85" t="n">
-        <v>6.52</v>
+        <v>7.01</v>
       </c>
       <c r="G85" t="n">
-        <v>93.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-55.99</v>
+        <v>-39.95</v>
       </c>
       <c r="K85" t="n">
-        <v>64.02</v>
+        <v>84.58</v>
       </c>
       <c r="L85" t="n">
-        <v>85.05</v>
+        <v>93.54000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>1.98</v>
       </c>
       <c r="F86" t="n">
-        <v>5.94</v>
+        <v>7.01</v>
       </c>
       <c r="G86" t="n">
-        <v>99.3</v>
+        <v>88.5</v>
       </c>
       <c r="H86" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>215.47</v>
+        <v>250.93</v>
       </c>
       <c r="K86" t="n">
-        <v>107.1</v>
+        <v>116.51</v>
       </c>
       <c r="L86" t="n">
-        <v>240.62</v>
+        <v>276.65</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>1.87</v>
       </c>
       <c r="F87" t="n">
-        <v>6.35</v>
+        <v>4.92</v>
       </c>
       <c r="G87" t="n">
-        <v>86.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-24.3</v>
+        <v>20.06</v>
       </c>
       <c r="K87" t="n">
-        <v>130.87</v>
+        <v>160.19</v>
       </c>
       <c r="L87" t="n">
-        <v>133.11</v>
+        <v>161.44</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>1.63</v>
       </c>
       <c r="F88" t="n">
-        <v>5.45</v>
+        <v>7.01</v>
       </c>
       <c r="G88" t="n">
-        <v>89.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="H88" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>122.97</v>
+        <v>181.88</v>
       </c>
       <c r="K88" t="n">
-        <v>-45.92</v>
+        <v>-36.57</v>
       </c>
       <c r="L88" t="n">
-        <v>131.27</v>
+        <v>185.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.22</v>
+        <v>-27.52</v>
       </c>
       <c r="K14" t="n">
-        <v>38.69</v>
+        <v>42.21</v>
       </c>
       <c r="L14" t="n">
-        <v>46.19</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.88</v>
+        <v>-28.31</v>
       </c>
       <c r="K15" t="n">
-        <v>47.52</v>
+        <v>54.07</v>
       </c>
       <c r="L15" t="n">
-        <v>53.64</v>
+        <v>61.04</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>20.67</v>
+        <v>23.2</v>
       </c>
       <c r="K16" t="n">
-        <v>45.44</v>
+        <v>51.02</v>
       </c>
       <c r="L16" t="n">
-        <v>49.92</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>35.16</v>
+        <v>37.15</v>
       </c>
       <c r="K17" t="n">
-        <v>76.53</v>
+        <v>80.86</v>
       </c>
       <c r="L17" t="n">
-        <v>84.20999999999999</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>15.11</v>
+        <v>16.48</v>
       </c>
       <c r="K18" t="n">
-        <v>103.64</v>
+        <v>113.06</v>
       </c>
       <c r="L18" t="n">
-        <v>104.73</v>
+        <v>114.25</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-54.74</v>
+        <v>-57.84</v>
       </c>
       <c r="K19" t="n">
-        <v>-37.73</v>
+        <v>-39.86</v>
       </c>
       <c r="L19" t="n">
-        <v>66.48999999999999</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>80.36</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>82.95999999999999</v>
+        <v>89.11</v>
       </c>
       <c r="L20" t="n">
-        <v>115.5</v>
+        <v>124.06</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.76000000000001</v>
+        <v>-72.65000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>46.01</v>
+        <v>48.62</v>
       </c>
       <c r="L21" t="n">
-        <v>82.73999999999999</v>
+        <v>87.42</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>56.49</v>
+        <v>63.43</v>
       </c>
       <c r="K22" t="n">
-        <v>45.71</v>
+        <v>51.33</v>
       </c>
       <c r="L22" t="n">
-        <v>72.67</v>
+        <v>81.59</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>15.91</v>
+        <v>17.36</v>
       </c>
       <c r="K23" t="n">
-        <v>186.26</v>
+        <v>203.19</v>
       </c>
       <c r="L23" t="n">
-        <v>186.94</v>
+        <v>203.93</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-49.01</v>
+        <v>-50.9</v>
       </c>
       <c r="K24" t="n">
-        <v>-100.11</v>
+        <v>-103.96</v>
       </c>
       <c r="L24" t="n">
-        <v>111.46</v>
+        <v>115.75</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>121.22</v>
+        <v>130.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-21.66</v>
+        <v>-23.27</v>
       </c>
       <c r="L25" t="n">
-        <v>123.14</v>
+        <v>132.26</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>-119.65</v>
+        <v>-134.34</v>
       </c>
       <c r="K26" t="n">
-        <v>209.87</v>
+        <v>235.65</v>
       </c>
       <c r="L26" t="n">
-        <v>241.58</v>
+        <v>271.25</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>145.44</v>
+        <v>156.21</v>
       </c>
       <c r="K27" t="n">
-        <v>17.71</v>
+        <v>19.02</v>
       </c>
       <c r="L27" t="n">
-        <v>146.51</v>
+        <v>157.37</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>112.99</v>
+        <v>121.36</v>
       </c>
       <c r="K28" t="n">
-        <v>171.29</v>
+        <v>183.98</v>
       </c>
       <c r="L28" t="n">
-        <v>205.2</v>
+        <v>220.4</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-19.59</v>
+        <v>-22.3</v>
       </c>
       <c r="K29" t="n">
-        <v>47.79</v>
+        <v>54.38</v>
       </c>
       <c r="L29" t="n">
-        <v>51.65</v>
+        <v>58.78</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-29.78</v>
+        <v>-32.97</v>
       </c>
       <c r="K30" t="n">
-        <v>-50.66</v>
+        <v>-56.08</v>
       </c>
       <c r="L30" t="n">
-        <v>58.76</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.47</v>
+        <v>-10.88</v>
       </c>
       <c r="K31" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
       <c r="L31" t="n">
-        <v>40.38</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>69.18000000000001</v>
+        <v>71.84</v>
       </c>
       <c r="K32" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="L32" t="n">
-        <v>69.22</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-71.40000000000001</v>
+        <v>-76.69</v>
       </c>
       <c r="K33" t="n">
-        <v>23.32</v>
+        <v>25.04</v>
       </c>
       <c r="L33" t="n">
-        <v>75.11</v>
+        <v>80.68000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>67.69</v>
+        <v>77.03</v>
       </c>
       <c r="K34" t="n">
-        <v>-68.42</v>
+        <v>-77.86</v>
       </c>
       <c r="L34" t="n">
-        <v>96.25</v>
+        <v>109.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>63.04</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-105.99</v>
+        <v>-117.35</v>
       </c>
       <c r="L35" t="n">
-        <v>123.32</v>
+        <v>136.53</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>78.63</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-79.16</v>
+        <v>-85.03</v>
       </c>
       <c r="L36" t="n">
-        <v>111.58</v>
+        <v>119.84</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>46.43</v>
+        <v>49.06</v>
       </c>
       <c r="K37" t="n">
-        <v>-43.59</v>
+        <v>-46.05</v>
       </c>
       <c r="L37" t="n">
-        <v>63.69</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>125.12</v>
+        <v>136.5</v>
       </c>
       <c r="K38" t="n">
-        <v>50.05</v>
+        <v>54.6</v>
       </c>
       <c r="L38" t="n">
-        <v>134.76</v>
+        <v>147.01</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>33.14</v>
+        <v>36.15</v>
       </c>
       <c r="K39" t="n">
-        <v>-114.1</v>
+        <v>-124.47</v>
       </c>
       <c r="L39" t="n">
-        <v>118.81</v>
+        <v>129.62</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.57</v>
+        <v>-12.22</v>
       </c>
       <c r="K40" t="n">
-        <v>-128.08</v>
+        <v>-135.33</v>
       </c>
       <c r="L40" t="n">
-        <v>128.6</v>
+        <v>135.88</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>21.83</v>
+        <v>24.51</v>
       </c>
       <c r="K41" t="n">
-        <v>-26.59</v>
+        <v>-29.86</v>
       </c>
       <c r="L41" t="n">
-        <v>34.41</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>93.53</v>
+        <v>102.04</v>
       </c>
       <c r="K42" t="n">
-        <v>273.24</v>
+        <v>298.08</v>
       </c>
       <c r="L42" t="n">
-        <v>288.81</v>
+        <v>315.06</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>63.08</v>
+        <v>69.84</v>
       </c>
       <c r="K43" t="n">
-        <v>-172.88</v>
+        <v>-191.4</v>
       </c>
       <c r="L43" t="n">
-        <v>184.03</v>
+        <v>203.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.28</v>
+        <v>-51.86</v>
       </c>
       <c r="K44" t="n">
-        <v>4.23</v>
+        <v>4.54</v>
       </c>
       <c r="L44" t="n">
-        <v>48.47</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.65</v>
+        <v>-5.86</v>
       </c>
       <c r="K45" t="n">
-        <v>-63.1</v>
+        <v>-65.53</v>
       </c>
       <c r="L45" t="n">
-        <v>63.35</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.02</v>
+        <v>-3.39</v>
       </c>
       <c r="K46" t="n">
-        <v>38.66</v>
+        <v>43.41</v>
       </c>
       <c r="L46" t="n">
-        <v>38.78</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-75.95</v>
+        <v>-86.42</v>
       </c>
       <c r="K47" t="n">
-        <v>-30.85</v>
+        <v>-35.1</v>
       </c>
       <c r="L47" t="n">
-        <v>81.97</v>
+        <v>93.28</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>28.53</v>
+        <v>30.65</v>
       </c>
       <c r="K48" t="n">
-        <v>75.78</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>80.98</v>
+        <v>86.97</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>82.2</v>
+        <v>93.53</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.74</v>
+        <v>-1.98</v>
       </c>
       <c r="L49" t="n">
-        <v>82.20999999999999</v>
+        <v>93.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>76.34999999999999</v>
+        <v>85.73</v>
       </c>
       <c r="K50" t="n">
-        <v>63.19</v>
+        <v>70.95</v>
       </c>
       <c r="L50" t="n">
-        <v>99.11</v>
+        <v>111.28</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-111.13</v>
+        <v>-123.03</v>
       </c>
       <c r="K51" t="n">
-        <v>-14.21</v>
+        <v>-15.73</v>
       </c>
       <c r="L51" t="n">
-        <v>112.03</v>
+        <v>124.04</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>121.36</v>
+        <v>130.35</v>
       </c>
       <c r="K52" t="n">
-        <v>-19.98</v>
+        <v>-21.46</v>
       </c>
       <c r="L52" t="n">
-        <v>122.99</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>17.87</v>
+        <v>18.55</v>
       </c>
       <c r="K53" t="n">
-        <v>208.21</v>
+        <v>216.22</v>
       </c>
       <c r="L53" t="n">
-        <v>208.97</v>
+        <v>217.01</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>58.66</v>
+        <v>65.86</v>
       </c>
       <c r="K54" t="n">
-        <v>-147.25</v>
+        <v>-165.34</v>
       </c>
       <c r="L54" t="n">
-        <v>158.51</v>
+        <v>177.97</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.09</v>
+        <v>-2.17</v>
       </c>
       <c r="K55" t="n">
-        <v>-121.63</v>
+        <v>-126.3</v>
       </c>
       <c r="L55" t="n">
-        <v>121.64</v>
+        <v>126.32</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>69.16</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>-123.61</v>
+        <v>-128.36</v>
       </c>
       <c r="L56" t="n">
-        <v>141.64</v>
+        <v>147.08</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-145.02</v>
+        <v>-158.2</v>
       </c>
       <c r="K57" t="n">
-        <v>-190.15</v>
+        <v>-207.44</v>
       </c>
       <c r="L57" t="n">
-        <v>239.14</v>
+        <v>260.88</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>173.09</v>
+        <v>182.89</v>
       </c>
       <c r="K58" t="n">
-        <v>226.11</v>
+        <v>238.91</v>
       </c>
       <c r="L58" t="n">
-        <v>284.76</v>
+        <v>300.87</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>42.25</v>
+        <v>46.09</v>
       </c>
       <c r="K59" t="n">
-        <v>12.5</v>
+        <v>13.64</v>
       </c>
       <c r="L59" t="n">
-        <v>44.06</v>
+        <v>48.07</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-38.34</v>
+        <v>-43.63</v>
       </c>
       <c r="K60" t="n">
-        <v>-46.5</v>
+        <v>-52.92</v>
       </c>
       <c r="L60" t="n">
-        <v>60.27</v>
+        <v>68.58</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>13.37</v>
+        <v>14.13</v>
       </c>
       <c r="K61" t="n">
-        <v>40.67</v>
+        <v>42.98</v>
       </c>
       <c r="L61" t="n">
-        <v>42.82</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-81.31</v>
+        <v>-90.03</v>
       </c>
       <c r="K62" t="n">
-        <v>35.83</v>
+        <v>39.67</v>
       </c>
       <c r="L62" t="n">
-        <v>88.86</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>47.88</v>
+        <v>53</v>
       </c>
       <c r="K63" t="n">
-        <v>-61.93</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>78.28</v>
+        <v>86.67</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>90.95999999999999</v>
+        <v>99.23</v>
       </c>
       <c r="K64" t="n">
-        <v>-15</v>
+        <v>-16.36</v>
       </c>
       <c r="L64" t="n">
-        <v>92.19</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>145.88</v>
+        <v>154.14</v>
       </c>
       <c r="K65" t="n">
-        <v>39.7</v>
+        <v>41.94</v>
       </c>
       <c r="L65" t="n">
-        <v>151.19</v>
+        <v>159.75</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>125.51</v>
+        <v>136.92</v>
       </c>
       <c r="K66" t="n">
-        <v>37.14</v>
+        <v>40.51</v>
       </c>
       <c r="L66" t="n">
-        <v>130.89</v>
+        <v>142.79</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-79.06</v>
+        <v>-87.53</v>
       </c>
       <c r="K67" t="n">
-        <v>-38.19</v>
+        <v>-42.28</v>
       </c>
       <c r="L67" t="n">
-        <v>87.8</v>
+        <v>97.20999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>116.78</v>
+        <v>121.27</v>
       </c>
       <c r="K68" t="n">
-        <v>18.76</v>
+        <v>19.49</v>
       </c>
       <c r="L68" t="n">
-        <v>118.28</v>
+        <v>122.83</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-86.03</v>
+        <v>-96.59999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-136.39</v>
+        <v>-153.14</v>
       </c>
       <c r="L69" t="n">
-        <v>161.26</v>
+        <v>181.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-75.97</v>
+        <v>-82.88</v>
       </c>
       <c r="K70" t="n">
-        <v>131.71</v>
+        <v>143.68</v>
       </c>
       <c r="L70" t="n">
-        <v>152.05</v>
+        <v>165.87</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-184.37</v>
+        <v>-201.13</v>
       </c>
       <c r="K71" t="n">
-        <v>-110.26</v>
+        <v>-120.28</v>
       </c>
       <c r="L71" t="n">
-        <v>214.82</v>
+        <v>234.35</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>185.32</v>
+        <v>199.04</v>
       </c>
       <c r="K72" t="n">
-        <v>57.49</v>
+        <v>61.75</v>
       </c>
       <c r="L72" t="n">
-        <v>194.03</v>
+        <v>208.4</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>183.75</v>
+        <v>209.09</v>
       </c>
       <c r="K73" t="n">
-        <v>-160.63</v>
+        <v>-182.78</v>
       </c>
       <c r="L73" t="n">
-        <v>244.06</v>
+        <v>277.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-23.87</v>
+        <v>-27.16</v>
       </c>
       <c r="K74" t="n">
-        <v>39.75</v>
+        <v>45.23</v>
       </c>
       <c r="L74" t="n">
-        <v>46.37</v>
+        <v>52.76</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>47.05</v>
+        <v>50.53</v>
       </c>
       <c r="K75" t="n">
-        <v>36.05</v>
+        <v>38.72</v>
       </c>
       <c r="L75" t="n">
-        <v>59.27</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>20.63</v>
+        <v>21.8</v>
       </c>
       <c r="K76" t="n">
-        <v>31.52</v>
+        <v>33.31</v>
       </c>
       <c r="L76" t="n">
-        <v>37.67</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>25.27</v>
+        <v>26.7</v>
       </c>
       <c r="K77" t="n">
-        <v>-51.48</v>
+        <v>-54.4</v>
       </c>
       <c r="L77" t="n">
-        <v>57.35</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>13.65</v>
+        <v>14.17</v>
       </c>
       <c r="K78" t="n">
-        <v>70.44</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>71.75</v>
+        <v>74.51000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-42.27</v>
+        <v>-43.9</v>
       </c>
       <c r="K79" t="n">
-        <v>46.3</v>
+        <v>48.08</v>
       </c>
       <c r="L79" t="n">
-        <v>62.69</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>18.21</v>
+        <v>20.72</v>
       </c>
       <c r="K80" t="n">
-        <v>-107.52</v>
+        <v>-122.34</v>
       </c>
       <c r="L80" t="n">
-        <v>109.05</v>
+        <v>124.09</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>22.54</v>
+        <v>23.41</v>
       </c>
       <c r="K81" t="n">
-        <v>90.31</v>
+        <v>93.78</v>
       </c>
       <c r="L81" t="n">
-        <v>93.08</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-69.94</v>
+        <v>-73.90000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-68.75</v>
+        <v>-72.64</v>
       </c>
       <c r="L82" t="n">
-        <v>98.08</v>
+        <v>103.63</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>156.27</v>
+        <v>177.82</v>
       </c>
       <c r="K83" t="n">
-        <v>126.88</v>
+        <v>144.38</v>
       </c>
       <c r="L83" t="n">
-        <v>201.29</v>
+        <v>229.05</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>87.59999999999999</v>
+        <v>92.56</v>
       </c>
       <c r="K84" t="n">
-        <v>51.3</v>
+        <v>54.2</v>
       </c>
       <c r="L84" t="n">
-        <v>101.52</v>
+        <v>107.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-39.95</v>
+        <v>-41.48</v>
       </c>
       <c r="K85" t="n">
-        <v>84.58</v>
+        <v>87.83</v>
       </c>
       <c r="L85" t="n">
-        <v>93.54000000000001</v>
+        <v>97.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>250.93</v>
+        <v>260.58</v>
       </c>
       <c r="K86" t="n">
-        <v>116.51</v>
+        <v>120.99</v>
       </c>
       <c r="L86" t="n">
-        <v>276.65</v>
+        <v>287.29</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>20.06</v>
+        <v>22.83</v>
       </c>
       <c r="K87" t="n">
-        <v>160.19</v>
+        <v>182.28</v>
       </c>
       <c r="L87" t="n">
-        <v>161.44</v>
+        <v>183.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>181.88</v>
+        <v>206.96</v>
       </c>
       <c r="K88" t="n">
-        <v>-36.57</v>
+        <v>-41.61</v>
       </c>
       <c r="L88" t="n">
-        <v>185.52</v>
+        <v>211.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="F14" t="n">
-        <v>7.01</v>
+        <v>4.06</v>
       </c>
       <c r="G14" t="n">
-        <v>91.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>51.1</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-27.52</v>
+        <v>-3.99</v>
       </c>
       <c r="K14" t="n">
-        <v>42.21</v>
+        <v>-24.84</v>
       </c>
       <c r="L14" t="n">
-        <v>50.39</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:41:04</t>
+          <t>06:40:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F15" t="n">
-        <v>4.31</v>
+        <v>4.69</v>
       </c>
       <c r="G15" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-28.31</v>
+        <v>8.6</v>
       </c>
       <c r="K15" t="n">
-        <v>54.07</v>
+        <v>-22.24</v>
       </c>
       <c r="L15" t="n">
-        <v>61.04</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:42:07</t>
+          <t>06:42:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="F16" t="n">
-        <v>7.01</v>
+        <v>6.41</v>
       </c>
       <c r="G16" t="n">
-        <v>87.7</v>
+        <v>101.6</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>23.2</v>
+        <v>18.97</v>
       </c>
       <c r="K16" t="n">
-        <v>51.02</v>
+        <v>12.74</v>
       </c>
       <c r="L16" t="n">
-        <v>56.05</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:48:38</t>
+          <t>06:45:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="F17" t="n">
-        <v>7.01</v>
+        <v>6.72</v>
       </c>
       <c r="G17" t="n">
-        <v>91.3</v>
+        <v>81.3</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>20.1</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>37.15</v>
+        <v>-5.82</v>
       </c>
       <c r="K17" t="n">
-        <v>80.86</v>
+        <v>33.68</v>
       </c>
       <c r="L17" t="n">
-        <v>88.98</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:49:38</t>
+          <t>06:46:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="F18" t="n">
-        <v>7.01</v>
+        <v>5.1</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>93.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>62.6</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>16.48</v>
+        <v>40.86</v>
       </c>
       <c r="K18" t="n">
-        <v>113.06</v>
+        <v>14.34</v>
       </c>
       <c r="L18" t="n">
-        <v>114.25</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:51:29</t>
+          <t>06:49:10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="F19" t="n">
-        <v>6.33</v>
+        <v>4.65</v>
       </c>
       <c r="G19" t="n">
-        <v>88.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>34.9</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-57.84</v>
+        <v>-46.67</v>
       </c>
       <c r="K19" t="n">
-        <v>-39.86</v>
+        <v>-13.06</v>
       </c>
       <c r="L19" t="n">
-        <v>70.25</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:57:51</t>
+          <t>06:53:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="F20" t="n">
-        <v>5.51</v>
+        <v>4.81</v>
       </c>
       <c r="G20" t="n">
-        <v>83.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3</v>
+        <v>46.5</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>86.31999999999999</v>
+        <v>-31.71</v>
       </c>
       <c r="K20" t="n">
-        <v>89.11</v>
+        <v>-24.6</v>
       </c>
       <c r="L20" t="n">
-        <v>124.06</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:59:07</t>
+          <t>06:55:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.66</v>
+        <v>1.34</v>
       </c>
       <c r="F21" t="n">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="G21" t="n">
-        <v>85.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1</v>
+        <v>29.2</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-72.65000000000001</v>
+        <v>22.7</v>
       </c>
       <c r="K21" t="n">
-        <v>48.62</v>
+        <v>-63.39</v>
       </c>
       <c r="L21" t="n">
-        <v>87.42</v>
+        <v>67.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:00:44</t>
+          <t>06:56:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.67</v>
+        <v>5.91</v>
       </c>
       <c r="G22" t="n">
-        <v>102.8</v>
+        <v>93.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>42.6</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>63.43</v>
+        <v>68.92</v>
       </c>
       <c r="K22" t="n">
-        <v>51.33</v>
+        <v>-16.6</v>
       </c>
       <c r="L22" t="n">
-        <v>81.59</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:05:32</t>
+          <t>07:01:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="F23" t="n">
-        <v>5.87</v>
+        <v>2.05</v>
       </c>
       <c r="G23" t="n">
-        <v>99.09999999999999</v>
+        <v>106</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7</v>
+        <v>24.8</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>17.36</v>
+        <v>76.41</v>
       </c>
       <c r="K23" t="n">
-        <v>203.19</v>
+        <v>-76.73</v>
       </c>
       <c r="L23" t="n">
-        <v>203.93</v>
+        <v>108.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:06:55</t>
+          <t>07:02:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="F24" t="n">
         <v>7.01</v>
       </c>
       <c r="G24" t="n">
-        <v>94.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>-50.9</v>
+        <v>-34.53</v>
       </c>
       <c r="K24" t="n">
-        <v>-103.96</v>
+        <v>23.6</v>
       </c>
       <c r="L24" t="n">
-        <v>115.75</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:08:52</t>
+          <t>07:03:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="F25" t="n">
         <v>7.01</v>
       </c>
       <c r="G25" t="n">
-        <v>94.7</v>
+        <v>84.5</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>130.2</v>
+        <v>85.62</v>
       </c>
       <c r="K25" t="n">
-        <v>-23.27</v>
+        <v>18.31</v>
       </c>
       <c r="L25" t="n">
-        <v>132.26</v>
+        <v>87.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:13:10</t>
+          <t>07:09:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="F26" t="n">
-        <v>7.01</v>
+        <v>4.44</v>
       </c>
       <c r="G26" t="n">
-        <v>91</v>
+        <v>98.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>34.2</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>-134.34</v>
+        <v>110.95</v>
       </c>
       <c r="K26" t="n">
-        <v>235.65</v>
+        <v>-109.37</v>
       </c>
       <c r="L26" t="n">
-        <v>271.25</v>
+        <v>155.79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:15:11</t>
+          <t>07:10:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="F27" t="n">
-        <v>4.17</v>
+        <v>4.4</v>
       </c>
       <c r="G27" t="n">
-        <v>85.3</v>
+        <v>89.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3</v>
+        <v>60.3</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>156.21</v>
+        <v>-111.11</v>
       </c>
       <c r="K27" t="n">
-        <v>19.02</v>
+        <v>6.33</v>
       </c>
       <c r="L27" t="n">
-        <v>157.37</v>
+        <v>111.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:16:45</t>
+          <t>07:12:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.65</v>
+        <v>1.06</v>
       </c>
       <c r="F28" t="n">
-        <v>6.6</v>
+        <v>3.82</v>
       </c>
       <c r="G28" t="n">
-        <v>80.3</v>
+        <v>70.5</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>121.36</v>
+        <v>-33.53</v>
       </c>
       <c r="K28" t="n">
-        <v>183.98</v>
+        <v>132.29</v>
       </c>
       <c r="L28" t="n">
-        <v>220.4</v>
+        <v>136.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:26:09</t>
+          <t>07:19:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="F29" t="n">
-        <v>4.68</v>
+        <v>4.38</v>
       </c>
       <c r="G29" t="n">
-        <v>79.59999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1</v>
+        <v>63.7</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-22.3</v>
+        <v>7.08</v>
       </c>
       <c r="K29" t="n">
-        <v>54.38</v>
+        <v>40.1</v>
       </c>
       <c r="L29" t="n">
-        <v>58.78</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:27:52</t>
+          <t>07:20:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="F30" t="n">
         <v>7.01</v>
       </c>
       <c r="G30" t="n">
-        <v>100.7</v>
+        <v>86.7</v>
       </c>
       <c r="H30" t="n">
-        <v>3.7</v>
+        <v>20.7</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.97</v>
+        <v>-4.31</v>
       </c>
       <c r="K30" t="n">
-        <v>-56.08</v>
+        <v>-33.95</v>
       </c>
       <c r="L30" t="n">
-        <v>65.05</v>
+        <v>34.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:29:10</t>
+          <t>07:21:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="F31" t="n">
-        <v>1.57</v>
+        <v>4.72</v>
       </c>
       <c r="G31" t="n">
-        <v>101.4</v>
+        <v>92.5</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>40.1</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.88</v>
+        <v>-27.43</v>
       </c>
       <c r="K31" t="n">
-        <v>40.5</v>
+        <v>24.44</v>
       </c>
       <c r="L31" t="n">
-        <v>41.94</v>
+        <v>36.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:32:43</t>
+          <t>07:25:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="F32" t="n">
-        <v>4.43</v>
+        <v>7.01</v>
       </c>
       <c r="G32" t="n">
-        <v>88.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1</v>
+        <v>45</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>71.84</v>
+        <v>50.01</v>
       </c>
       <c r="K32" t="n">
-        <v>2.4</v>
+        <v>16.11</v>
       </c>
       <c r="L32" t="n">
-        <v>71.88</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:34:54</t>
+          <t>07:26:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="F33" t="n">
-        <v>5.88</v>
+        <v>3.12</v>
       </c>
       <c r="G33" t="n">
-        <v>84.8</v>
+        <v>93.3</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.69</v>
+        <v>38.93</v>
       </c>
       <c r="K33" t="n">
-        <v>25.04</v>
+        <v>-30.73</v>
       </c>
       <c r="L33" t="n">
-        <v>80.68000000000001</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:36:52</t>
+          <t>07:28:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="F34" t="n">
-        <v>6.51</v>
+        <v>1.69</v>
       </c>
       <c r="G34" t="n">
-        <v>98.40000000000001</v>
+        <v>104.6</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4</v>
+        <v>26.5</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>77.03</v>
+        <v>-33.96</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.86</v>
+        <v>38.87</v>
       </c>
       <c r="L34" t="n">
-        <v>109.52</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:41:33</t>
+          <t>07:32:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="F35" t="n">
-        <v>6.9</v>
+        <v>4.41</v>
       </c>
       <c r="G35" t="n">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>35.2</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>69.79000000000001</v>
+        <v>-42.94</v>
       </c>
       <c r="K35" t="n">
-        <v>-117.35</v>
+        <v>-58.85</v>
       </c>
       <c r="L35" t="n">
-        <v>136.53</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:42:26</t>
+          <t>07:34:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1.66</v>
+        <v>2.51</v>
       </c>
       <c r="G36" t="n">
-        <v>94.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="H36" t="n">
-        <v>1.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>84.45999999999999</v>
+        <v>30.11</v>
       </c>
       <c r="K36" t="n">
-        <v>-85.03</v>
+        <v>-48.49</v>
       </c>
       <c r="L36" t="n">
-        <v>119.84</v>
+        <v>57.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:43:36</t>
+          <t>07:36:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="F37" t="n">
-        <v>1.35</v>
+        <v>5.26</v>
       </c>
       <c r="G37" t="n">
-        <v>94</v>
+        <v>96.8</v>
       </c>
       <c r="H37" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>49.06</v>
+        <v>-5.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-46.05</v>
+        <v>63.55</v>
       </c>
       <c r="L37" t="n">
-        <v>67.29000000000001</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:49:52</t>
+          <t>07:41:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="F38" t="n">
-        <v>1.76</v>
+        <v>6.1</v>
       </c>
       <c r="G38" t="n">
-        <v>94.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>136.5</v>
+        <v>-11.97</v>
       </c>
       <c r="K38" t="n">
-        <v>54.6</v>
+        <v>-109.18</v>
       </c>
       <c r="L38" t="n">
-        <v>147.01</v>
+        <v>109.83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:51:53</t>
+          <t>07:42:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="F39" t="n">
-        <v>4.16</v>
+        <v>7.01</v>
       </c>
       <c r="G39" t="n">
-        <v>95.3</v>
+        <v>89.8</v>
       </c>
       <c r="H39" t="n">
-        <v>3.8</v>
+        <v>50.8</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>36.15</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-124.47</v>
+        <v>-47.92</v>
       </c>
       <c r="L39" t="n">
-        <v>129.62</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:53:24</t>
+          <t>07:45:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="F40" t="n">
-        <v>7.01</v>
+        <v>2.76</v>
       </c>
       <c r="G40" t="n">
-        <v>95.59999999999999</v>
+        <v>104.9</v>
       </c>
       <c r="H40" t="n">
-        <v>2.2</v>
+        <v>35.2</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.22</v>
+        <v>120.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-135.33</v>
+        <v>23.17</v>
       </c>
       <c r="L40" t="n">
-        <v>135.88</v>
+        <v>122.31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:57:28</t>
+          <t>07:49:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="F41" t="n">
-        <v>7.01</v>
+        <v>5.96</v>
       </c>
       <c r="G41" t="n">
-        <v>88.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>3.8</v>
+        <v>31.6</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>24.51</v>
+        <v>118.79</v>
       </c>
       <c r="K41" t="n">
-        <v>-29.86</v>
+        <v>33.81</v>
       </c>
       <c r="L41" t="n">
-        <v>38.63</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:00:06</t>
+          <t>07:51:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="F42" t="n">
-        <v>7.01</v>
+        <v>3.96</v>
       </c>
       <c r="G42" t="n">
-        <v>85.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>102.04</v>
+        <v>-79.25</v>
       </c>
       <c r="K42" t="n">
-        <v>298.08</v>
+        <v>-141.51</v>
       </c>
       <c r="L42" t="n">
-        <v>315.06</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:01:00</t>
+          <t>07:53:49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="F43" t="n">
-        <v>4.22</v>
+        <v>4.8</v>
       </c>
       <c r="G43" t="n">
-        <v>92</v>
+        <v>101.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>69.84</v>
+        <v>163.96</v>
       </c>
       <c r="K43" t="n">
-        <v>-191.4</v>
+        <v>17.41</v>
       </c>
       <c r="L43" t="n">
-        <v>203.74</v>
+        <v>164.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:11:40</t>
+          <t>08:05:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="F44" t="n">
-        <v>7.01</v>
+        <v>4.54</v>
       </c>
       <c r="G44" t="n">
-        <v>78.8</v>
+        <v>95.2</v>
       </c>
       <c r="H44" t="n">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>-51.86</v>
+        <v>19.9</v>
       </c>
       <c r="K44" t="n">
-        <v>4.54</v>
+        <v>-31.26</v>
       </c>
       <c r="L44" t="n">
-        <v>52.06</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:13:04</t>
+          <t>08:06:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="F45" t="n">
         <v>7.01</v>
       </c>
       <c r="G45" t="n">
-        <v>92.5</v>
+        <v>95.5</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.86</v>
+        <v>24.19</v>
       </c>
       <c r="K45" t="n">
-        <v>-65.53</v>
+        <v>-28.99</v>
       </c>
       <c r="L45" t="n">
-        <v>65.79000000000001</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:14:59</t>
+          <t>08:08:03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="F46" t="n">
-        <v>2.99</v>
+        <v>6.12</v>
       </c>
       <c r="G46" t="n">
-        <v>87.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.39</v>
+        <v>95.73</v>
       </c>
       <c r="K46" t="n">
-        <v>43.41</v>
+        <v>5.14</v>
       </c>
       <c r="L46" t="n">
-        <v>43.54</v>
+        <v>95.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:18:39</t>
+          <t>08:12:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="F47" t="n">
-        <v>5.17</v>
+        <v>2.04</v>
       </c>
       <c r="G47" t="n">
-        <v>82.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="H47" t="n">
-        <v>5.6</v>
+        <v>51.7</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>-86.42</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.1</v>
+        <v>36.21</v>
       </c>
       <c r="L47" t="n">
-        <v>93.28</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:19:41</t>
+          <t>08:13:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="F48" t="n">
-        <v>7.01</v>
+        <v>2.07</v>
       </c>
       <c r="G48" t="n">
-        <v>92</v>
+        <v>83.3</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5</v>
+        <v>21.9</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>30.65</v>
+        <v>44.14</v>
       </c>
       <c r="K48" t="n">
-        <v>81.40000000000001</v>
+        <v>-9.98</v>
       </c>
       <c r="L48" t="n">
-        <v>86.97</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:21:07</t>
+          <t>08:15:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="F49" t="n">
-        <v>5.19</v>
+        <v>7.01</v>
       </c>
       <c r="G49" t="n">
-        <v>82.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>93.53</v>
+        <v>35.49</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.98</v>
+        <v>19.14</v>
       </c>
       <c r="L49" t="n">
-        <v>93.55</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:26:30</t>
+          <t>08:19:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="F50" t="n">
-        <v>6.19</v>
+        <v>3.81</v>
       </c>
       <c r="G50" t="n">
-        <v>89.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8</v>
+        <v>36.7</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>85.73</v>
+        <v>65.94</v>
       </c>
       <c r="K50" t="n">
-        <v>70.95</v>
+        <v>29.87</v>
       </c>
       <c r="L50" t="n">
-        <v>111.28</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:28:48</t>
+          <t>08:21:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="F51" t="n">
-        <v>4.12</v>
+        <v>7.01</v>
       </c>
       <c r="G51" t="n">
-        <v>85.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>46.3</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-123.03</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-15.73</v>
+        <v>-55.22</v>
       </c>
       <c r="L51" t="n">
-        <v>124.04</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:29:42</t>
+          <t>08:23:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="F52" t="n">
-        <v>7.01</v>
+        <v>2.68</v>
       </c>
       <c r="G52" t="n">
-        <v>98.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>5.1</v>
+        <v>43.2</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>130.35</v>
+        <v>52.56</v>
       </c>
       <c r="K52" t="n">
-        <v>-21.46</v>
+        <v>-67.2</v>
       </c>
       <c r="L52" t="n">
-        <v>132.1</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:34:10</t>
+          <t>08:28:09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="F53" t="n">
-        <v>7.01</v>
+        <v>4.86</v>
       </c>
       <c r="G53" t="n">
-        <v>78.59999999999999</v>
+        <v>114.2</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>18.55</v>
+        <v>112.97</v>
       </c>
       <c r="K53" t="n">
-        <v>216.22</v>
+        <v>-7.01</v>
       </c>
       <c r="L53" t="n">
-        <v>217.01</v>
+        <v>113.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:36:06</t>
+          <t>08:28:45</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="F54" t="n">
-        <v>6.4</v>
+        <v>5.76</v>
       </c>
       <c r="G54" t="n">
-        <v>78.7</v>
+        <v>86.3</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>65.86</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-165.34</v>
+        <v>17.57</v>
       </c>
       <c r="L54" t="n">
-        <v>177.97</v>
+        <v>95.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:38:04</t>
+          <t>08:31:23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="F55" t="n">
-        <v>7.01</v>
+        <v>3.88</v>
       </c>
       <c r="G55" t="n">
-        <v>84.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>60.9</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.17</v>
+        <v>112.75</v>
       </c>
       <c r="K55" t="n">
-        <v>-126.3</v>
+        <v>26.73</v>
       </c>
       <c r="L55" t="n">
-        <v>126.32</v>
+        <v>115.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:42:50</t>
+          <t>08:35:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2392,31 +2392,31 @@
         <v>1.34</v>
       </c>
       <c r="F56" t="n">
-        <v>4.6</v>
+        <v>2.23</v>
       </c>
       <c r="G56" t="n">
-        <v>93.7</v>
+        <v>95.3</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>37.2</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>71.81999999999999</v>
+        <v>31.09</v>
       </c>
       <c r="K56" t="n">
-        <v>-128.36</v>
+        <v>170.13</v>
       </c>
       <c r="L56" t="n">
-        <v>147.08</v>
+        <v>172.95</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:45:22</t>
+          <t>08:36:56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="F57" t="n">
         <v>7.01</v>
       </c>
       <c r="G57" t="n">
-        <v>93.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-158.2</v>
+        <v>-141.6</v>
       </c>
       <c r="K57" t="n">
-        <v>-207.44</v>
+        <v>64.63</v>
       </c>
       <c r="L57" t="n">
-        <v>260.88</v>
+        <v>155.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:47:23</t>
+          <t>08:37:36</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="F58" t="n">
-        <v>5.2</v>
+        <v>7.01</v>
       </c>
       <c r="G58" t="n">
-        <v>94.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9</v>
+        <v>27.1</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>182.89</v>
+        <v>-55.71</v>
       </c>
       <c r="K58" t="n">
-        <v>238.91</v>
+        <v>28.04</v>
       </c>
       <c r="L58" t="n">
-        <v>300.87</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:56:06</t>
+          <t>08:49:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="F59" t="n">
-        <v>4.74</v>
+        <v>7.01</v>
       </c>
       <c r="G59" t="n">
-        <v>98.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>46.09</v>
+        <v>26.25</v>
       </c>
       <c r="K59" t="n">
-        <v>13.64</v>
+        <v>-8.15</v>
       </c>
       <c r="L59" t="n">
-        <v>48.07</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:56:48</t>
+          <t>08:51:38</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="F60" t="n">
         <v>7.01</v>
       </c>
       <c r="G60" t="n">
-        <v>90</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>54.8</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.63</v>
+        <v>-24.96</v>
       </c>
       <c r="K60" t="n">
-        <v>-52.92</v>
+        <v>-4.15</v>
       </c>
       <c r="L60" t="n">
-        <v>68.58</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:58:04</t>
+          <t>08:53:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="F61" t="n">
-        <v>7.01</v>
+        <v>6.77</v>
       </c>
       <c r="G61" t="n">
-        <v>88.5</v>
+        <v>84.7</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>40.9</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>14.13</v>
+        <v>6.32</v>
       </c>
       <c r="K61" t="n">
-        <v>42.98</v>
+        <v>-14.94</v>
       </c>
       <c r="L61" t="n">
-        <v>45.24</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:02:16</t>
+          <t>08:57:40</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="F62" t="n">
         <v>7.01</v>
       </c>
       <c r="G62" t="n">
-        <v>83.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="H62" t="n">
-        <v>5.7</v>
+        <v>18.7</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>-90.03</v>
+        <v>27.48</v>
       </c>
       <c r="K62" t="n">
-        <v>39.67</v>
+        <v>21.27</v>
       </c>
       <c r="L62" t="n">
-        <v>98.38</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:04:00</t>
+          <t>08:58:34</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="F63" t="n">
-        <v>5.53</v>
+        <v>7.01</v>
       </c>
       <c r="G63" t="n">
-        <v>85.2</v>
+        <v>84.8</v>
       </c>
       <c r="H63" t="n">
-        <v>3.2</v>
+        <v>40.3</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>53</v>
+        <v>23.77</v>
       </c>
       <c r="K63" t="n">
-        <v>-68.56999999999999</v>
+        <v>-43.89</v>
       </c>
       <c r="L63" t="n">
-        <v>86.67</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:04:52</t>
+          <t>08:59:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="F64" t="n">
-        <v>7.01</v>
+        <v>1.92</v>
       </c>
       <c r="G64" t="n">
-        <v>87.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>51.1</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>99.23</v>
+        <v>-31.33</v>
       </c>
       <c r="K64" t="n">
-        <v>-16.36</v>
+        <v>-63.56</v>
       </c>
       <c r="L64" t="n">
-        <v>100.57</v>
+        <v>70.86</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:10:22</t>
+          <t>09:04:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="F65" t="n">
-        <v>7.01</v>
+        <v>4.2</v>
       </c>
       <c r="G65" t="n">
-        <v>90.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H65" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>154.14</v>
+        <v>62.93</v>
       </c>
       <c r="K65" t="n">
-        <v>41.94</v>
+        <v>36.62</v>
       </c>
       <c r="L65" t="n">
-        <v>159.75</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:11:15</t>
+          <t>09:06:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="F66" t="n">
-        <v>7.01</v>
+        <v>6.64</v>
       </c>
       <c r="G66" t="n">
-        <v>102.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>44.5</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>136.92</v>
+        <v>38.61</v>
       </c>
       <c r="K66" t="n">
-        <v>40.51</v>
+        <v>19.91</v>
       </c>
       <c r="L66" t="n">
-        <v>142.79</v>
+        <v>43.44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:12:30</t>
+          <t>09:07:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="F67" t="n">
-        <v>6.41</v>
+        <v>7.01</v>
       </c>
       <c r="G67" t="n">
-        <v>96.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-87.53</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-42.28</v>
+        <v>9.4</v>
       </c>
       <c r="L67" t="n">
-        <v>97.20999999999999</v>
+        <v>96.36</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:16:55</t>
+          <t>09:13:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="F68" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="G68" t="n">
-        <v>94.3</v>
+        <v>102.4</v>
       </c>
       <c r="H68" t="n">
-        <v>2.1</v>
+        <v>51.5</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>121.27</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>19.49</v>
+        <v>-77.45</v>
       </c>
       <c r="L68" t="n">
-        <v>122.83</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:18:55</t>
+          <t>09:15:15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="F69" t="n">
-        <v>5.54</v>
+        <v>3.75</v>
       </c>
       <c r="G69" t="n">
-        <v>95</v>
+        <v>103.9</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>60.3</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-96.59999999999999</v>
+        <v>88.39</v>
       </c>
       <c r="K69" t="n">
-        <v>-153.14</v>
+        <v>4.96</v>
       </c>
       <c r="L69" t="n">
-        <v>181.06</v>
+        <v>88.53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:20:40</t>
+          <t>09:16:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="F70" t="n">
-        <v>4.46</v>
+        <v>5.52</v>
       </c>
       <c r="G70" t="n">
-        <v>94.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-82.88</v>
+        <v>31.97</v>
       </c>
       <c r="K70" t="n">
-        <v>143.68</v>
+        <v>-83.15000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>165.87</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:24:41</t>
+          <t>09:20:42</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.42</v>
+        <v>1.86</v>
       </c>
       <c r="F71" t="n">
-        <v>6.76</v>
+        <v>7.01</v>
       </c>
       <c r="G71" t="n">
-        <v>96</v>
+        <v>84.8</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-201.13</v>
+        <v>146.22</v>
       </c>
       <c r="K71" t="n">
-        <v>-120.28</v>
+        <v>112.31</v>
       </c>
       <c r="L71" t="n">
-        <v>234.35</v>
+        <v>184.37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:26:11</t>
+          <t>09:22:02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="F72" t="n">
-        <v>6.85</v>
+        <v>7.01</v>
       </c>
       <c r="G72" t="n">
-        <v>79.2</v>
+        <v>98</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>53.4</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>199.04</v>
+        <v>11.91</v>
       </c>
       <c r="K72" t="n">
-        <v>61.75</v>
+        <v>-119.92</v>
       </c>
       <c r="L72" t="n">
-        <v>208.4</v>
+        <v>120.51</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:28:03</t>
+          <t>09:23:51</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="F73" t="n">
-        <v>6.29</v>
+        <v>1.65</v>
       </c>
       <c r="G73" t="n">
-        <v>102.7</v>
+        <v>104.4</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>209.09</v>
+        <v>-27.05</v>
       </c>
       <c r="K73" t="n">
-        <v>-182.78</v>
+        <v>110.06</v>
       </c>
       <c r="L73" t="n">
-        <v>277.72</v>
+        <v>113.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:38:23</t>
+          <t>09:37:36</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="F74" t="n">
         <v>7.01</v>
       </c>
       <c r="G74" t="n">
-        <v>89.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="H74" t="n">
-        <v>1.6</v>
+        <v>16.5</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.16</v>
+        <v>-2.01</v>
       </c>
       <c r="K74" t="n">
-        <v>45.23</v>
+        <v>-26.47</v>
       </c>
       <c r="L74" t="n">
-        <v>52.76</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:39:39</t>
+          <t>09:39:34</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="F75" t="n">
-        <v>7.01</v>
+        <v>6.86</v>
       </c>
       <c r="G75" t="n">
-        <v>100.5</v>
+        <v>92.5</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>50.53</v>
+        <v>-2.69</v>
       </c>
       <c r="K75" t="n">
-        <v>38.72</v>
+        <v>-28.83</v>
       </c>
       <c r="L75" t="n">
-        <v>63.66</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:41:12</t>
+          <t>09:40:58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="F76" t="n">
-        <v>7.01</v>
+        <v>6.18</v>
       </c>
       <c r="G76" t="n">
-        <v>65.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="H76" t="n">
-        <v>2.3</v>
+        <v>30.1</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>21.8</v>
+        <v>27.37</v>
       </c>
       <c r="K76" t="n">
-        <v>33.31</v>
+        <v>25.93</v>
       </c>
       <c r="L76" t="n">
-        <v>39.81</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:46:34</t>
+          <t>09:43:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="F77" t="n">
-        <v>7.01</v>
+        <v>6.08</v>
       </c>
       <c r="G77" t="n">
-        <v>101.3</v>
+        <v>81.3</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8</v>
+        <v>86.5</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>26.7</v>
+        <v>-9.17</v>
       </c>
       <c r="K77" t="n">
-        <v>-54.4</v>
+        <v>-44.31</v>
       </c>
       <c r="L77" t="n">
-        <v>60.6</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:48:16</t>
+          <t>09:45:35</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="F78" t="n">
         <v>7.01</v>
       </c>
       <c r="G78" t="n">
-        <v>92</v>
+        <v>98.2</v>
       </c>
       <c r="H78" t="n">
-        <v>1.7</v>
+        <v>72.2</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>14.17</v>
+        <v>-88.26000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>73.15000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="L78" t="n">
-        <v>74.51000000000001</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:50:45</t>
+          <t>09:47:55</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="F79" t="n">
-        <v>5.77</v>
+        <v>7.01</v>
       </c>
       <c r="G79" t="n">
-        <v>97.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3</v>
+        <v>38.1</v>
       </c>
       <c r="I79" t="n">
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-43.9</v>
+        <v>11.74</v>
       </c>
       <c r="K79" t="n">
-        <v>48.08</v>
+        <v>-37.3</v>
       </c>
       <c r="L79" t="n">
-        <v>65.09999999999999</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:54:55</t>
+          <t>09:53:26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="F80" t="n">
         <v>7.01</v>
       </c>
       <c r="G80" t="n">
-        <v>87.3</v>
+        <v>93.3</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>20.72</v>
+        <v>-15.09</v>
       </c>
       <c r="K80" t="n">
-        <v>-122.34</v>
+        <v>-97.70999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>124.09</v>
+        <v>98.86</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:56:32</t>
+          <t>09:54:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="F81" t="n">
         <v>7.01</v>
       </c>
       <c r="G81" t="n">
-        <v>92.59999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>23.41</v>
+        <v>39.68</v>
       </c>
       <c r="K81" t="n">
-        <v>93.78</v>
+        <v>-46.2</v>
       </c>
       <c r="L81" t="n">
-        <v>96.66</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:58:49</t>
+          <t>09:57:08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="F82" t="n">
-        <v>7.01</v>
+        <v>1.68</v>
       </c>
       <c r="G82" t="n">
-        <v>92.8</v>
+        <v>95</v>
       </c>
       <c r="H82" t="n">
-        <v>1.6</v>
+        <v>59.2</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-73.90000000000001</v>
+        <v>48.06</v>
       </c>
       <c r="K82" t="n">
-        <v>-72.64</v>
+        <v>-35.43</v>
       </c>
       <c r="L82" t="n">
-        <v>103.63</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:03:47</t>
+          <t>10:01:57</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="F83" t="n">
-        <v>3.79</v>
+        <v>7.01</v>
       </c>
       <c r="G83" t="n">
-        <v>93.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>6</v>
+        <v>34.6</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>177.82</v>
+        <v>-61.41</v>
       </c>
       <c r="K83" t="n">
-        <v>144.38</v>
+        <v>-85.17</v>
       </c>
       <c r="L83" t="n">
-        <v>229.05</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:05:46</t>
+          <t>10:03:09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="F84" t="n">
-        <v>6.11</v>
+        <v>7.01</v>
       </c>
       <c r="G84" t="n">
-        <v>90.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>92.56</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>54.2</v>
+        <v>-106.02</v>
       </c>
       <c r="L84" t="n">
-        <v>107.26</v>
+        <v>106.37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:06:55</t>
+          <t>10:03:56</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="F85" t="n">
-        <v>7.01</v>
+        <v>5.94</v>
       </c>
       <c r="G85" t="n">
-        <v>99.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="H85" t="n">
-        <v>0.9</v>
+        <v>29.9</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.48</v>
+        <v>-59.18</v>
       </c>
       <c r="K85" t="n">
-        <v>87.83</v>
+        <v>46.63</v>
       </c>
       <c r="L85" t="n">
-        <v>97.13</v>
+        <v>75.34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:11:37</t>
+          <t>10:06:59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="F86" t="n">
-        <v>7.01</v>
+        <v>5.3</v>
       </c>
       <c r="G86" t="n">
-        <v>88.5</v>
+        <v>96.3</v>
       </c>
       <c r="H86" t="n">
-        <v>3.9</v>
+        <v>33</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>260.58</v>
+        <v>-54.69</v>
       </c>
       <c r="K86" t="n">
-        <v>120.99</v>
+        <v>-123.28</v>
       </c>
       <c r="L86" t="n">
-        <v>287.29</v>
+        <v>134.87</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:13:42</t>
+          <t>10:09:26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="F87" t="n">
-        <v>4.92</v>
+        <v>7.01</v>
       </c>
       <c r="G87" t="n">
-        <v>96.59999999999999</v>
+        <v>101.7</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>22.83</v>
+        <v>132.64</v>
       </c>
       <c r="K87" t="n">
-        <v>182.28</v>
+        <v>-149.46</v>
       </c>
       <c r="L87" t="n">
-        <v>183.71</v>
+        <v>199.83</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:14:48</t>
+          <t>10:10:41</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="F88" t="n">
-        <v>7.01</v>
+        <v>5.98</v>
       </c>
       <c r="G88" t="n">
-        <v>78.7</v>
+        <v>102.6</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>39.5</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>206.96</v>
+        <v>-104.59</v>
       </c>
       <c r="K88" t="n">
-        <v>-41.61</v>
+        <v>104</v>
       </c>
       <c r="L88" t="n">
-        <v>211.1</v>
+        <v>147.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="F14" t="n">
-        <v>4.06</v>
+        <v>7.01</v>
       </c>
       <c r="G14" t="n">
-        <v>96.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>51.1</v>
+        <v>41.3</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.99</v>
+        <v>17.08</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.84</v>
+        <v>-30.37</v>
       </c>
       <c r="L14" t="n">
-        <v>25.16</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:40:40</t>
+          <t>06:40:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="F15" t="n">
-        <v>4.69</v>
+        <v>5.8</v>
       </c>
       <c r="G15" t="n">
-        <v>93.90000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="H15" t="n">
-        <v>28.4</v>
+        <v>41.1</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>8.6</v>
+        <v>27.57</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.24</v>
+        <v>19.03</v>
       </c>
       <c r="L15" t="n">
-        <v>23.84</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:42:21</t>
+          <t>06:41:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="F16" t="n">
-        <v>6.41</v>
+        <v>5.94</v>
       </c>
       <c r="G16" t="n">
-        <v>101.6</v>
+        <v>90.7</v>
       </c>
       <c r="H16" t="n">
-        <v>76.90000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>18.97</v>
+        <v>6.65</v>
       </c>
       <c r="K16" t="n">
-        <v>12.74</v>
+        <v>-26.3</v>
       </c>
       <c r="L16" t="n">
-        <v>22.85</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:45:47</t>
+          <t>06:47:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="n">
-        <v>6.72</v>
+        <v>7.01</v>
       </c>
       <c r="G17" t="n">
-        <v>81.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>20.1</v>
+        <v>56.2</v>
       </c>
       <c r="I17" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.82</v>
+        <v>16.86</v>
       </c>
       <c r="K17" t="n">
-        <v>33.68</v>
+        <v>45</v>
       </c>
       <c r="L17" t="n">
-        <v>34.17</v>
+        <v>48.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:59</t>
+          <t>06:47:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="F18" t="n">
-        <v>5.1</v>
+        <v>7.01</v>
       </c>
       <c r="G18" t="n">
-        <v>93.2</v>
+        <v>84.5</v>
       </c>
       <c r="H18" t="n">
-        <v>62.6</v>
+        <v>51.5</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>40.86</v>
+        <v>-29.56</v>
       </c>
       <c r="K18" t="n">
-        <v>14.34</v>
+        <v>35.78</v>
       </c>
       <c r="L18" t="n">
-        <v>43.31</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:49:10</t>
+          <t>06:50:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="F19" t="n">
-        <v>4.65</v>
+        <v>7.01</v>
       </c>
       <c r="G19" t="n">
-        <v>84.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="H19" t="n">
-        <v>34.9</v>
+        <v>30.6</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-46.67</v>
+        <v>4.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-13.06</v>
+        <v>-50.01</v>
       </c>
       <c r="L19" t="n">
-        <v>48.46</v>
+        <v>50.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:53:59</t>
+          <t>06:55:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="F20" t="n">
-        <v>4.81</v>
+        <v>6.59</v>
       </c>
       <c r="G20" t="n">
-        <v>91</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>46.5</v>
+        <v>28.1</v>
       </c>
       <c r="I20" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-31.71</v>
+        <v>-4.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-24.6</v>
+        <v>83</v>
       </c>
       <c r="L20" t="n">
-        <v>40.14</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:55:17</t>
+          <t>06:57:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="F21" t="n">
-        <v>6.05</v>
+        <v>2.13</v>
       </c>
       <c r="G21" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="H21" t="n">
-        <v>29.2</v>
+        <v>35.9</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>22.7</v>
+        <v>-36.47</v>
       </c>
       <c r="K21" t="n">
-        <v>-63.39</v>
+        <v>65.73</v>
       </c>
       <c r="L21" t="n">
-        <v>67.33</v>
+        <v>75.18000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:56:24</t>
+          <t>06:58:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="F22" t="n">
-        <v>5.91</v>
+        <v>7.01</v>
       </c>
       <c r="G22" t="n">
-        <v>93.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>42.6</v>
+        <v>2.2</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>68.92</v>
+        <v>-46.94</v>
       </c>
       <c r="K22" t="n">
-        <v>-16.6</v>
+        <v>3.11</v>
       </c>
       <c r="L22" t="n">
-        <v>70.89</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:01:23</t>
+          <t>07:02:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="F23" t="n">
-        <v>2.05</v>
+        <v>5.34</v>
       </c>
       <c r="G23" t="n">
-        <v>106</v>
+        <v>87.5</v>
       </c>
       <c r="H23" t="n">
-        <v>24.8</v>
+        <v>26.7</v>
       </c>
       <c r="I23" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>76.41</v>
+        <v>-16.27</v>
       </c>
       <c r="K23" t="n">
-        <v>-76.73</v>
+        <v>-107.52</v>
       </c>
       <c r="L23" t="n">
-        <v>108.29</v>
+        <v>108.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:02:35</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="F24" t="n">
         <v>7.01</v>
       </c>
       <c r="G24" t="n">
-        <v>86.8</v>
+        <v>91.2</v>
       </c>
       <c r="H24" t="n">
-        <v>12.9</v>
+        <v>32.2</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-34.53</v>
+        <v>54.25</v>
       </c>
       <c r="K24" t="n">
-        <v>23.6</v>
+        <v>-100.26</v>
       </c>
       <c r="L24" t="n">
-        <v>41.82</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:03:38</t>
+          <t>07:06:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="F25" t="n">
-        <v>7.01</v>
+        <v>6.3</v>
       </c>
       <c r="G25" t="n">
-        <v>84.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>24.4</v>
+        <v>19.9</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>85.62</v>
+        <v>100.53</v>
       </c>
       <c r="K25" t="n">
-        <v>18.31</v>
+        <v>47.97</v>
       </c>
       <c r="L25" t="n">
-        <v>87.56</v>
+        <v>111.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:09:13</t>
+          <t>07:09:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="F26" t="n">
-        <v>4.44</v>
+        <v>6.78</v>
       </c>
       <c r="G26" t="n">
-        <v>98.8</v>
+        <v>93</v>
       </c>
       <c r="H26" t="n">
-        <v>34.2</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>110.95</v>
+        <v>97.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-109.37</v>
+        <v>128.03</v>
       </c>
       <c r="L26" t="n">
-        <v>155.79</v>
+        <v>160.79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:10:01</t>
+          <t>07:11:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="F27" t="n">
-        <v>4.4</v>
+        <v>7.01</v>
       </c>
       <c r="G27" t="n">
-        <v>89.5</v>
+        <v>91.2</v>
       </c>
       <c r="H27" t="n">
-        <v>60.3</v>
+        <v>34.2</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-111.11</v>
+        <v>-116</v>
       </c>
       <c r="K27" t="n">
-        <v>6.33</v>
+        <v>51.69</v>
       </c>
       <c r="L27" t="n">
-        <v>111.29</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:12:27</t>
+          <t>07:13:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="F28" t="n">
-        <v>3.82</v>
+        <v>7.01</v>
       </c>
       <c r="G28" t="n">
-        <v>70.5</v>
+        <v>97.2</v>
       </c>
       <c r="H28" t="n">
-        <v>53</v>
+        <v>19.2</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-33.53</v>
+        <v>-113.78</v>
       </c>
       <c r="K28" t="n">
-        <v>132.29</v>
+        <v>18.43</v>
       </c>
       <c r="L28" t="n">
-        <v>136.48</v>
+        <v>115.26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:19:12</t>
+          <t>07:25:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="F29" t="n">
-        <v>4.38</v>
+        <v>2.5</v>
       </c>
       <c r="G29" t="n">
-        <v>100.5</v>
+        <v>90</v>
       </c>
       <c r="H29" t="n">
-        <v>63.7</v>
+        <v>61.6</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>7.08</v>
+        <v>-16.66</v>
       </c>
       <c r="K29" t="n">
-        <v>40.1</v>
+        <v>-20.11</v>
       </c>
       <c r="L29" t="n">
-        <v>40.72</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:20:26</t>
+          <t>07:27:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="F30" t="n">
-        <v>7.01</v>
+        <v>2.99</v>
       </c>
       <c r="G30" t="n">
-        <v>86.7</v>
+        <v>93.5</v>
       </c>
       <c r="H30" t="n">
-        <v>20.7</v>
+        <v>38.8</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.31</v>
+        <v>-6.49</v>
       </c>
       <c r="K30" t="n">
-        <v>-33.95</v>
+        <v>25.17</v>
       </c>
       <c r="L30" t="n">
-        <v>34.23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:21:25</t>
+          <t>07:28:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="F31" t="n">
-        <v>4.72</v>
+        <v>5.37</v>
       </c>
       <c r="G31" t="n">
-        <v>92.5</v>
+        <v>88.7</v>
       </c>
       <c r="H31" t="n">
-        <v>40.1</v>
+        <v>38.9</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-27.43</v>
+        <v>7.47</v>
       </c>
       <c r="K31" t="n">
-        <v>24.44</v>
+        <v>28.6</v>
       </c>
       <c r="L31" t="n">
-        <v>36.74</v>
+        <v>29.56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:25:51</t>
+          <t>07:33:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>7.01</v>
+        <v>6.99</v>
       </c>
       <c r="G32" t="n">
-        <v>83.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="H32" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>50.01</v>
+        <v>-5.48</v>
       </c>
       <c r="K32" t="n">
-        <v>16.11</v>
+        <v>32.48</v>
       </c>
       <c r="L32" t="n">
-        <v>52.54</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:26:47</t>
+          <t>07:34:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="F33" t="n">
-        <v>3.12</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>93.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>38.1</v>
+        <v>39.4</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>38.93</v>
+        <v>19.08</v>
       </c>
       <c r="K33" t="n">
-        <v>-30.73</v>
+        <v>-29.77</v>
       </c>
       <c r="L33" t="n">
-        <v>49.6</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:28:30</t>
+          <t>07:36:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="F34" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G34" t="n">
-        <v>104.6</v>
+        <v>85</v>
       </c>
       <c r="H34" t="n">
-        <v>26.5</v>
+        <v>32.1</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-33.96</v>
+        <v>6.03</v>
       </c>
       <c r="K34" t="n">
-        <v>38.87</v>
+        <v>40.24</v>
       </c>
       <c r="L34" t="n">
-        <v>51.62</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:32:59</t>
+          <t>07:40:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="F35" t="n">
-        <v>4.41</v>
+        <v>7.01</v>
       </c>
       <c r="G35" t="n">
-        <v>82.8</v>
+        <v>95.8</v>
       </c>
       <c r="H35" t="n">
-        <v>35.2</v>
+        <v>34</v>
       </c>
       <c r="I35" t="n">
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-42.94</v>
+        <v>37.45</v>
       </c>
       <c r="K35" t="n">
-        <v>-58.85</v>
+        <v>-28.56</v>
       </c>
       <c r="L35" t="n">
-        <v>72.84999999999999</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:34:59</t>
+          <t>07:42:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="F36" t="n">
-        <v>2.51</v>
+        <v>7.01</v>
       </c>
       <c r="G36" t="n">
-        <v>91</v>
+        <v>85.2</v>
       </c>
       <c r="H36" t="n">
-        <v>9.300000000000001</v>
+        <v>43.3</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>30.11</v>
+        <v>58.62</v>
       </c>
       <c r="K36" t="n">
-        <v>-48.49</v>
+        <v>27.69</v>
       </c>
       <c r="L36" t="n">
-        <v>57.08</v>
+        <v>64.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:36:15</t>
+          <t>07:44:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F37" t="n">
-        <v>5.26</v>
+        <v>6.57</v>
       </c>
       <c r="G37" t="n">
-        <v>96.8</v>
+        <v>100.2</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>15.1</v>
       </c>
       <c r="I37" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.22</v>
+        <v>19.4</v>
       </c>
       <c r="K37" t="n">
-        <v>63.55</v>
+        <v>51.87</v>
       </c>
       <c r="L37" t="n">
-        <v>63.77</v>
+        <v>55.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:41:06</t>
+          <t>07:49:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="F38" t="n">
-        <v>6.1</v>
+        <v>6.99</v>
       </c>
       <c r="G38" t="n">
-        <v>95.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="H38" t="n">
-        <v>63.6</v>
+        <v>45.8</v>
       </c>
       <c r="I38" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-11.97</v>
+        <v>16.65</v>
       </c>
       <c r="K38" t="n">
-        <v>-109.18</v>
+        <v>-89.58</v>
       </c>
       <c r="L38" t="n">
-        <v>109.83</v>
+        <v>91.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:42:50</t>
+          <t>07:50:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="F39" t="n">
-        <v>7.01</v>
+        <v>6.75</v>
       </c>
       <c r="G39" t="n">
-        <v>89.8</v>
+        <v>103.5</v>
       </c>
       <c r="H39" t="n">
-        <v>50.8</v>
+        <v>47.7</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-86.43000000000001</v>
+        <v>-53.28</v>
       </c>
       <c r="K39" t="n">
-        <v>-47.92</v>
+        <v>85.62</v>
       </c>
       <c r="L39" t="n">
-        <v>98.81999999999999</v>
+        <v>100.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:45:17</t>
+          <t>07:52:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="F40" t="n">
-        <v>2.76</v>
+        <v>7.01</v>
       </c>
       <c r="G40" t="n">
-        <v>104.9</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>35.2</v>
+        <v>28.9</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>120.1</v>
+        <v>-128.79</v>
       </c>
       <c r="K40" t="n">
-        <v>23.17</v>
+        <v>43.44</v>
       </c>
       <c r="L40" t="n">
-        <v>122.31</v>
+        <v>135.92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:49:53</t>
+          <t>07:57:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="F41" t="n">
-        <v>5.96</v>
+        <v>3.28</v>
       </c>
       <c r="G41" t="n">
-        <v>82.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>31.6</v>
+        <v>16.6</v>
       </c>
       <c r="I41" t="n">
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>118.79</v>
+        <v>93.67</v>
       </c>
       <c r="K41" t="n">
-        <v>33.81</v>
+        <v>-22.82</v>
       </c>
       <c r="L41" t="n">
-        <v>123.5</v>
+        <v>96.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:51:28</t>
+          <t>07:59:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="F42" t="n">
-        <v>3.96</v>
+        <v>7.01</v>
       </c>
       <c r="G42" t="n">
-        <v>91.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>30.8</v>
+        <v>43.7</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-79.25</v>
+        <v>89.75</v>
       </c>
       <c r="K42" t="n">
-        <v>-141.51</v>
+        <v>100.38</v>
       </c>
       <c r="L42" t="n">
-        <v>162.2</v>
+        <v>134.65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:53:49</t>
+          <t>08:00:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="F43" t="n">
-        <v>4.8</v>
+        <v>4.02</v>
       </c>
       <c r="G43" t="n">
-        <v>101.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>77</v>
+        <v>57.1</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>163.96</v>
+        <v>-110.5</v>
       </c>
       <c r="K43" t="n">
-        <v>17.41</v>
+        <v>99.89</v>
       </c>
       <c r="L43" t="n">
-        <v>164.88</v>
+        <v>148.96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:05:27</t>
+          <t>08:14:06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="F44" t="n">
-        <v>4.54</v>
+        <v>6.92</v>
       </c>
       <c r="G44" t="n">
-        <v>95.2</v>
+        <v>82.8</v>
       </c>
       <c r="H44" t="n">
-        <v>29</v>
+        <v>68.8</v>
       </c>
       <c r="I44" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>19.9</v>
+        <v>24.47</v>
       </c>
       <c r="K44" t="n">
-        <v>-31.26</v>
+        <v>-12.42</v>
       </c>
       <c r="L44" t="n">
-        <v>37.05</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:06:26</t>
+          <t>08:16:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="F45" t="n">
-        <v>7.01</v>
+        <v>6.97</v>
       </c>
       <c r="G45" t="n">
-        <v>95.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="I45" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>24.19</v>
+        <v>6.65</v>
       </c>
       <c r="K45" t="n">
-        <v>-28.99</v>
+        <v>31.34</v>
       </c>
       <c r="L45" t="n">
-        <v>37.75</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:08:03</t>
+          <t>08:19:13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="F46" t="n">
-        <v>6.12</v>
+        <v>5.63</v>
       </c>
       <c r="G46" t="n">
-        <v>87</v>
+        <v>94.7</v>
       </c>
       <c r="H46" t="n">
-        <v>52.7</v>
+        <v>44.7</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>95.73</v>
+        <v>27.76</v>
       </c>
       <c r="K46" t="n">
-        <v>5.14</v>
+        <v>11.06</v>
       </c>
       <c r="L46" t="n">
-        <v>95.87</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:12:01</t>
+          <t>08:22:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="F47" t="n">
-        <v>2.04</v>
+        <v>3.68</v>
       </c>
       <c r="G47" t="n">
-        <v>77.3</v>
+        <v>89</v>
       </c>
       <c r="H47" t="n">
-        <v>51.7</v>
+        <v>25.2</v>
       </c>
       <c r="I47" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>9.210000000000001</v>
+        <v>28.88</v>
       </c>
       <c r="K47" t="n">
-        <v>36.21</v>
+        <v>-38.96</v>
       </c>
       <c r="L47" t="n">
-        <v>37.36</v>
+        <v>48.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:13:08</t>
+          <t>08:23:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="F48" t="n">
-        <v>2.07</v>
+        <v>3.82</v>
       </c>
       <c r="G48" t="n">
-        <v>83.3</v>
+        <v>64.2</v>
       </c>
       <c r="H48" t="n">
-        <v>21.9</v>
+        <v>60.8</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>44.14</v>
+        <v>45.68</v>
       </c>
       <c r="K48" t="n">
-        <v>-9.98</v>
+        <v>26.74</v>
       </c>
       <c r="L48" t="n">
-        <v>45.25</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:15:11</t>
+          <t>08:25:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="F49" t="n">
         <v>7.01</v>
       </c>
       <c r="G49" t="n">
-        <v>87.7</v>
+        <v>90.2</v>
       </c>
       <c r="H49" t="n">
-        <v>39.4</v>
+        <v>26.1</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>35.49</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>19.14</v>
+        <v>-43.9</v>
       </c>
       <c r="L49" t="n">
-        <v>40.32</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:19:22</t>
+          <t>08:30:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="F50" t="n">
-        <v>3.81</v>
+        <v>7.01</v>
       </c>
       <c r="G50" t="n">
-        <v>86.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="H50" t="n">
-        <v>36.7</v>
+        <v>34.5</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>65.94</v>
+        <v>69.67</v>
       </c>
       <c r="K50" t="n">
-        <v>29.87</v>
+        <v>71.7</v>
       </c>
       <c r="L50" t="n">
-        <v>72.39</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:21:29</t>
+          <t>08:32:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="F51" t="n">
         <v>7.01</v>
       </c>
       <c r="G51" t="n">
-        <v>89.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="H51" t="n">
-        <v>46.3</v>
+        <v>27.4</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.710000000000001</v>
+        <v>-54.81</v>
       </c>
       <c r="K51" t="n">
-        <v>-55.22</v>
+        <v>25.55</v>
       </c>
       <c r="L51" t="n">
-        <v>56.07</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:23:14</t>
+          <t>08:34:37</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="F52" t="n">
-        <v>2.68</v>
+        <v>3.98</v>
       </c>
       <c r="G52" t="n">
-        <v>92.90000000000001</v>
+        <v>107.3</v>
       </c>
       <c r="H52" t="n">
-        <v>43.2</v>
+        <v>47.3</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>52.56</v>
+        <v>51.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-67.2</v>
+        <v>38.28</v>
       </c>
       <c r="L52" t="n">
-        <v>85.31</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:28:09</t>
+          <t>08:38:17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="F53" t="n">
-        <v>4.86</v>
+        <v>4.96</v>
       </c>
       <c r="G53" t="n">
-        <v>114.2</v>
+        <v>84.7</v>
       </c>
       <c r="H53" t="n">
-        <v>41.3</v>
+        <v>45.4</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>112.97</v>
+        <v>88.72</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.01</v>
+        <v>-55.27</v>
       </c>
       <c r="L53" t="n">
-        <v>113.19</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:28:45</t>
+          <t>08:39:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="F54" t="n">
-        <v>5.76</v>
+        <v>6.6</v>
       </c>
       <c r="G54" t="n">
-        <v>86.3</v>
+        <v>101.6</v>
       </c>
       <c r="H54" t="n">
-        <v>33.7</v>
+        <v>39.3</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>93.79000000000001</v>
+        <v>81.81</v>
       </c>
       <c r="K54" t="n">
-        <v>17.57</v>
+        <v>-12.44</v>
       </c>
       <c r="L54" t="n">
-        <v>95.42</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:31:23</t>
+          <t>08:40:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="F55" t="n">
-        <v>3.88</v>
+        <v>4.37</v>
       </c>
       <c r="G55" t="n">
-        <v>94.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>60.9</v>
+        <v>44.3</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>112.75</v>
+        <v>97.66</v>
       </c>
       <c r="K55" t="n">
-        <v>26.73</v>
+        <v>-15.25</v>
       </c>
       <c r="L55" t="n">
-        <v>115.88</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:35:36</t>
+          <t>08:45:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="F56" t="n">
-        <v>2.23</v>
+        <v>7.01</v>
       </c>
       <c r="G56" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="H56" t="n">
-        <v>37.2</v>
+        <v>32.6</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>31.09</v>
+        <v>82.95</v>
       </c>
       <c r="K56" t="n">
-        <v>170.13</v>
+        <v>-72.87</v>
       </c>
       <c r="L56" t="n">
-        <v>172.95</v>
+        <v>110.41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:36:56</t>
+          <t>08:47:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="F57" t="n">
-        <v>7.01</v>
+        <v>3.82</v>
       </c>
       <c r="G57" t="n">
-        <v>92.3</v>
+        <v>88.3</v>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>47.3</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-141.6</v>
+        <v>-87.55</v>
       </c>
       <c r="K57" t="n">
-        <v>64.63</v>
+        <v>25.77</v>
       </c>
       <c r="L57" t="n">
-        <v>155.65</v>
+        <v>91.26000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:37:36</t>
+          <t>08:49:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="F58" t="n">
-        <v>7.01</v>
+        <v>6.74</v>
       </c>
       <c r="G58" t="n">
-        <v>89</v>
+        <v>93.7</v>
       </c>
       <c r="H58" t="n">
-        <v>27.1</v>
+        <v>52.8</v>
       </c>
       <c r="I58" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-55.71</v>
+        <v>111.93</v>
       </c>
       <c r="K58" t="n">
-        <v>28.04</v>
+        <v>104.42</v>
       </c>
       <c r="L58" t="n">
-        <v>62.37</v>
+        <v>153.07</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:49:54</t>
+          <t>08:59:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="F59" t="n">
         <v>7.01</v>
       </c>
       <c r="G59" t="n">
-        <v>93.8</v>
+        <v>86.5</v>
       </c>
       <c r="H59" t="n">
-        <v>73.09999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>26.25</v>
+        <v>-8.59</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.15</v>
+        <v>22.41</v>
       </c>
       <c r="L59" t="n">
-        <v>27.48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:51:38</t>
+          <t>09:00:37</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="F60" t="n">
-        <v>7.01</v>
+        <v>5.09</v>
       </c>
       <c r="G60" t="n">
-        <v>86.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H60" t="n">
-        <v>54.8</v>
+        <v>70.3</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.96</v>
+        <v>24.1</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.15</v>
+        <v>18.59</v>
       </c>
       <c r="L60" t="n">
-        <v>25.3</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:53:21</t>
+          <t>09:01:52</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="F61" t="n">
-        <v>6.77</v>
+        <v>4.78</v>
       </c>
       <c r="G61" t="n">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="H61" t="n">
-        <v>40.9</v>
+        <v>19.7</v>
       </c>
       <c r="I61" t="n">
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>6.32</v>
+        <v>-28.37</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.94</v>
+        <v>-5.02</v>
       </c>
       <c r="L61" t="n">
-        <v>16.22</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:57:40</t>
+          <t>09:06:12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="F62" t="n">
-        <v>7.01</v>
+        <v>5.84</v>
       </c>
       <c r="G62" t="n">
-        <v>90.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>18.7</v>
+        <v>55.6</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>27.48</v>
+        <v>-5.51</v>
       </c>
       <c r="K62" t="n">
-        <v>21.27</v>
+        <v>48.35</v>
       </c>
       <c r="L62" t="n">
-        <v>34.75</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:58:34</t>
+          <t>09:08:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="F63" t="n">
-        <v>7.01</v>
+        <v>1.88</v>
       </c>
       <c r="G63" t="n">
-        <v>84.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>40.3</v>
+        <v>32.2</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>23.77</v>
+        <v>42.46</v>
       </c>
       <c r="K63" t="n">
-        <v>-43.89</v>
+        <v>-10.92</v>
       </c>
       <c r="L63" t="n">
-        <v>49.91</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:59:45</t>
+          <t>09:10:14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="F64" t="n">
-        <v>1.92</v>
+        <v>7.01</v>
       </c>
       <c r="G64" t="n">
-        <v>92</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>51.1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.33</v>
+        <v>-38.32</v>
       </c>
       <c r="K64" t="n">
-        <v>-63.56</v>
+        <v>-22.47</v>
       </c>
       <c r="L64" t="n">
-        <v>70.86</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:04:12</t>
+          <t>09:14:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="F65" t="n">
-        <v>4.2</v>
+        <v>7.01</v>
       </c>
       <c r="G65" t="n">
-        <v>97.3</v>
+        <v>108.1</v>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>27.7</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>62.93</v>
+        <v>23.45</v>
       </c>
       <c r="K65" t="n">
-        <v>36.62</v>
+        <v>-45.22</v>
       </c>
       <c r="L65" t="n">
-        <v>72.81</v>
+        <v>50.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:06:00</t>
+          <t>09:15:59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="F66" t="n">
-        <v>6.64</v>
+        <v>4.48</v>
       </c>
       <c r="G66" t="n">
-        <v>91.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="H66" t="n">
-        <v>44.5</v>
+        <v>30.1</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>38.61</v>
+        <v>-67.39</v>
       </c>
       <c r="K66" t="n">
-        <v>19.91</v>
+        <v>10.69</v>
       </c>
       <c r="L66" t="n">
-        <v>43.44</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:07:19</t>
+          <t>09:17:52</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="F67" t="n">
-        <v>7.01</v>
+        <v>2.24</v>
       </c>
       <c r="G67" t="n">
-        <v>98.7</v>
+        <v>81.2</v>
       </c>
       <c r="H67" t="n">
-        <v>81.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>95.90000000000001</v>
+        <v>-79.16</v>
       </c>
       <c r="K67" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="L67" t="n">
-        <v>96.36</v>
+        <v>79.17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:13:37</t>
+          <t>09:22:38</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="F68" t="n">
-        <v>2.02</v>
+        <v>7.01</v>
       </c>
       <c r="G68" t="n">
-        <v>102.4</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>69.26000000000001</v>
+        <v>-77.45999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-77.45</v>
+        <v>-30.52</v>
       </c>
       <c r="L68" t="n">
-        <v>103.9</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:15:15</t>
+          <t>09:24:58</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="F69" t="n">
-        <v>3.75</v>
+        <v>7.01</v>
       </c>
       <c r="G69" t="n">
-        <v>103.9</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>60.3</v>
+        <v>45.9</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>88.39</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>4.96</v>
+        <v>47.15</v>
       </c>
       <c r="L69" t="n">
-        <v>88.53</v>
+        <v>97.94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:16:15</t>
+          <t>09:26:17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="F70" t="n">
-        <v>5.52</v>
+        <v>7.01</v>
       </c>
       <c r="G70" t="n">
-        <v>85.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="H70" t="n">
-        <v>29.9</v>
+        <v>51.7</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>31.97</v>
+        <v>-79.34999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-83.15000000000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>89.08</v>
+        <v>114.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:20:42</t>
+          <t>09:31:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="F71" t="n">
         <v>7.01</v>
       </c>
       <c r="G71" t="n">
-        <v>84.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>12.3</v>
+        <v>38</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>146.22</v>
+        <v>48.98</v>
       </c>
       <c r="K71" t="n">
-        <v>112.31</v>
+        <v>-86.11</v>
       </c>
       <c r="L71" t="n">
-        <v>184.37</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:22:02</t>
+          <t>09:33:04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="F72" t="n">
-        <v>7.01</v>
+        <v>3.69</v>
       </c>
       <c r="G72" t="n">
-        <v>98</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>53.4</v>
+        <v>9</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>11.91</v>
+        <v>-25.03</v>
       </c>
       <c r="K72" t="n">
-        <v>-119.92</v>
+        <v>-134.33</v>
       </c>
       <c r="L72" t="n">
-        <v>120.51</v>
+        <v>136.65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:23:51</t>
+          <t>09:34:28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="F73" t="n">
-        <v>1.65</v>
+        <v>6.65</v>
       </c>
       <c r="G73" t="n">
-        <v>104.4</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>28.6</v>
+        <v>21.3</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-27.05</v>
+        <v>116.93</v>
       </c>
       <c r="K73" t="n">
-        <v>110.06</v>
+        <v>83.81</v>
       </c>
       <c r="L73" t="n">
-        <v>113.34</v>
+        <v>143.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:37:36</t>
+          <t>09:45:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="F74" t="n">
-        <v>7.01</v>
+        <v>5.69</v>
       </c>
       <c r="G74" t="n">
-        <v>95.3</v>
+        <v>83.8</v>
       </c>
       <c r="H74" t="n">
-        <v>16.5</v>
+        <v>30.7</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.01</v>
+        <v>9.93</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.47</v>
+        <v>35.58</v>
       </c>
       <c r="L74" t="n">
-        <v>26.54</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:39:34</t>
+          <t>09:46:31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="F75" t="n">
-        <v>6.86</v>
+        <v>6.2</v>
       </c>
       <c r="G75" t="n">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="H75" t="n">
-        <v>60.5</v>
+        <v>12.7</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.69</v>
+        <v>15.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-28.83</v>
+        <v>27.27</v>
       </c>
       <c r="L75" t="n">
-        <v>28.96</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:40:58</t>
+          <t>09:47:56</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="F76" t="n">
-        <v>6.18</v>
+        <v>7.01</v>
       </c>
       <c r="G76" t="n">
-        <v>85.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>30.1</v>
+        <v>45.4</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>27.37</v>
+        <v>30.65</v>
       </c>
       <c r="K76" t="n">
-        <v>25.93</v>
+        <v>10.67</v>
       </c>
       <c r="L76" t="n">
-        <v>37.7</v>
+        <v>32.46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:43:48</t>
+          <t>09:52:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="F77" t="n">
-        <v>6.08</v>
+        <v>4.33</v>
       </c>
       <c r="G77" t="n">
-        <v>81.3</v>
+        <v>101.4</v>
       </c>
       <c r="H77" t="n">
-        <v>86.5</v>
+        <v>9.9</v>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-9.17</v>
+        <v>69.09</v>
       </c>
       <c r="K77" t="n">
-        <v>-44.31</v>
+        <v>25.97</v>
       </c>
       <c r="L77" t="n">
-        <v>45.25</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:45:35</t>
+          <t>09:54:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="F78" t="n">
-        <v>7.01</v>
+        <v>5.81</v>
       </c>
       <c r="G78" t="n">
-        <v>98.2</v>
+        <v>92</v>
       </c>
       <c r="H78" t="n">
-        <v>72.2</v>
+        <v>58.1</v>
       </c>
       <c r="I78" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-88.26000000000001</v>
+        <v>-32.2</v>
       </c>
       <c r="K78" t="n">
-        <v>13.57</v>
+        <v>-39.79</v>
       </c>
       <c r="L78" t="n">
-        <v>89.3</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:47:55</t>
+          <t>09:55:06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="F79" t="n">
-        <v>7.01</v>
+        <v>5.86</v>
       </c>
       <c r="G79" t="n">
-        <v>82.7</v>
+        <v>101.8</v>
       </c>
       <c r="H79" t="n">
-        <v>38.1</v>
+        <v>77</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>11.74</v>
+        <v>43.71</v>
       </c>
       <c r="K79" t="n">
-        <v>-37.3</v>
+        <v>6.07</v>
       </c>
       <c r="L79" t="n">
-        <v>39.1</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:53:26</t>
+          <t>10:00:56</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="F80" t="n">
-        <v>7.01</v>
+        <v>5.71</v>
       </c>
       <c r="G80" t="n">
-        <v>93.3</v>
+        <v>95.2</v>
       </c>
       <c r="H80" t="n">
-        <v>37.8</v>
+        <v>29</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-15.09</v>
+        <v>35.61</v>
       </c>
       <c r="K80" t="n">
-        <v>-97.70999999999999</v>
+        <v>-75.70999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>98.86</v>
+        <v>83.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:54:46</t>
+          <t>10:03:06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="F81" t="n">
         <v>7.01</v>
       </c>
       <c r="G81" t="n">
-        <v>107.1</v>
+        <v>95.5</v>
       </c>
       <c r="H81" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>39.68</v>
+        <v>47.94</v>
       </c>
       <c r="K81" t="n">
-        <v>-46.2</v>
+        <v>-68.81</v>
       </c>
       <c r="L81" t="n">
-        <v>60.9</v>
+        <v>83.86</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:57:08</t>
+          <t>10:05:23</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="F82" t="n">
-        <v>1.68</v>
+        <v>7.01</v>
       </c>
       <c r="G82" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H82" t="n">
-        <v>59.2</v>
+        <v>52.7</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>48.06</v>
+        <v>211.76</v>
       </c>
       <c r="K82" t="n">
-        <v>-35.43</v>
+        <v>11.38</v>
       </c>
       <c r="L82" t="n">
-        <v>59.71</v>
+        <v>212.07</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:01:57</t>
+          <t>10:10:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="F83" t="n">
-        <v>7.01</v>
+        <v>3.12</v>
       </c>
       <c r="G83" t="n">
-        <v>88.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="H83" t="n">
-        <v>34.6</v>
+        <v>51.7</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-61.41</v>
+        <v>11.78</v>
       </c>
       <c r="K83" t="n">
-        <v>-85.17</v>
+        <v>86.86</v>
       </c>
       <c r="L83" t="n">
-        <v>105</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:03:09</t>
+          <t>10:11:59</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="F84" t="n">
-        <v>7.01</v>
+        <v>3.12</v>
       </c>
       <c r="G84" t="n">
-        <v>87.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H84" t="n">
-        <v>72.2</v>
+        <v>21.9</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.640000000000001</v>
+        <v>100.96</v>
       </c>
       <c r="K84" t="n">
-        <v>-106.02</v>
+        <v>-27.29</v>
       </c>
       <c r="L84" t="n">
-        <v>106.37</v>
+        <v>104.59</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:03:56</t>
+          <t>10:13:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="F85" t="n">
-        <v>5.94</v>
+        <v>7.01</v>
       </c>
       <c r="G85" t="n">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
       <c r="H85" t="n">
-        <v>29.9</v>
+        <v>39.4</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-59.18</v>
+        <v>79.25</v>
       </c>
       <c r="K85" t="n">
-        <v>46.63</v>
+        <v>47.88</v>
       </c>
       <c r="L85" t="n">
-        <v>75.34</v>
+        <v>92.59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:06:59</t>
+          <t>10:16:42</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="F86" t="n">
-        <v>5.3</v>
+        <v>4.85</v>
       </c>
       <c r="G86" t="n">
-        <v>96.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>33</v>
+        <v>36.7</v>
       </c>
       <c r="I86" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-54.69</v>
+        <v>131.34</v>
       </c>
       <c r="K86" t="n">
-        <v>-123.28</v>
+        <v>66.83</v>
       </c>
       <c r="L86" t="n">
-        <v>134.87</v>
+        <v>147.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:09:26</t>
+          <t>10:18:49</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="F87" t="n">
         <v>7.01</v>
       </c>
       <c r="G87" t="n">
-        <v>101.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>13.5</v>
+        <v>46.3</v>
       </c>
       <c r="I87" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>132.64</v>
+        <v>-34.12</v>
       </c>
       <c r="K87" t="n">
-        <v>-149.46</v>
+        <v>-109.33</v>
       </c>
       <c r="L87" t="n">
-        <v>199.83</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:10:41</t>
+          <t>10:19:42</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="F88" t="n">
-        <v>5.98</v>
+        <v>3.67</v>
       </c>
       <c r="G88" t="n">
-        <v>102.6</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>39.5</v>
+        <v>43.2</v>
       </c>
       <c r="I88" t="n">
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-104.59</v>
+        <v>92.14</v>
       </c>
       <c r="K88" t="n">
-        <v>104</v>
+        <v>-140.83</v>
       </c>
       <c r="L88" t="n">
-        <v>147.5</v>
+        <v>168.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-11.xlsx
+++ b/output/2025-09-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.94</v>
+        <v>-18.44</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>27.75</v>
       </c>
       <c r="L14" t="n">
-        <v>32.42</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.2</v>
+        <v>-19.14</v>
       </c>
       <c r="K15" t="n">
-        <v>38.18</v>
+        <v>36.17</v>
       </c>
       <c r="L15" t="n">
-        <v>43.2</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>14.35</v>
+        <v>14.61</v>
       </c>
       <c r="K16" t="n">
-        <v>32.29</v>
+        <v>32.89</v>
       </c>
       <c r="L16" t="n">
-        <v>35.34</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>26.14</v>
+        <v>24.52</v>
       </c>
       <c r="K17" t="n">
-        <v>58.31</v>
+        <v>54.7</v>
       </c>
       <c r="L17" t="n">
-        <v>63.9</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>11.15</v>
+        <v>10.16</v>
       </c>
       <c r="K18" t="n">
-        <v>80.61</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>81.38</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.1</v>
+        <v>-40.47</v>
       </c>
       <c r="K19" t="n">
-        <v>-27.76</v>
+        <v>-27.34</v>
       </c>
       <c r="L19" t="n">
-        <v>49.6</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>62.24</v>
+        <v>61.51</v>
       </c>
       <c r="K20" t="n">
-        <v>66.45999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="L20" t="n">
-        <v>91.05</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-64.36</v>
+        <v>-71.63</v>
       </c>
       <c r="K21" t="n">
-        <v>33.68</v>
+        <v>37.48</v>
       </c>
       <c r="L21" t="n">
-        <v>72.64</v>
+        <v>80.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>46.67</v>
+        <v>50.86</v>
       </c>
       <c r="K22" t="n">
-        <v>43.86</v>
+        <v>47.79</v>
       </c>
       <c r="L22" t="n">
-        <v>64.04000000000001</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>6.72</v>
+        <v>6.81</v>
       </c>
       <c r="K23" t="n">
-        <v>144.63</v>
+        <v>146.53</v>
       </c>
       <c r="L23" t="n">
-        <v>144.79</v>
+        <v>146.68</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-55.28</v>
+        <v>-63.45</v>
       </c>
       <c r="K24" t="n">
-        <v>-79.3</v>
+        <v>-91.03</v>
       </c>
       <c r="L24" t="n">
-        <v>96.67</v>
+        <v>110.96</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>87.14</v>
+        <v>98.55</v>
       </c>
       <c r="K25" t="n">
-        <v>-15.91</v>
+        <v>-17.99</v>
       </c>
       <c r="L25" t="n">
-        <v>88.58</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-93.19</v>
+        <v>-102.35</v>
       </c>
       <c r="K26" t="n">
-        <v>135.76</v>
+        <v>149.1</v>
       </c>
       <c r="L26" t="n">
-        <v>164.66</v>
+        <v>180.85</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>109.85</v>
+        <v>132.79</v>
       </c>
       <c r="K27" t="n">
-        <v>12.56</v>
+        <v>15.18</v>
       </c>
       <c r="L27" t="n">
-        <v>110.57</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>76.02</v>
+        <v>85.91</v>
       </c>
       <c r="K28" t="n">
-        <v>146.32</v>
+        <v>165.37</v>
       </c>
       <c r="L28" t="n">
-        <v>164.89</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.33</v>
+        <v>-15</v>
       </c>
       <c r="K29" t="n">
-        <v>36.67</v>
+        <v>35.87</v>
       </c>
       <c r="L29" t="n">
-        <v>39.74</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-23.98</v>
+        <v>-23.41</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.24</v>
+        <v>-39.28</v>
       </c>
       <c r="L30" t="n">
-        <v>46.84</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.51</v>
+        <v>-11.02</v>
       </c>
       <c r="K31" t="n">
-        <v>42.2</v>
+        <v>40.4</v>
       </c>
       <c r="L31" t="n">
-        <v>43.74</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>60.76</v>
+        <v>57.81</v>
       </c>
       <c r="K32" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="L32" t="n">
-        <v>60.8</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-58.33</v>
+        <v>-56.13</v>
       </c>
       <c r="K33" t="n">
-        <v>18.67</v>
+        <v>17.97</v>
       </c>
       <c r="L33" t="n">
-        <v>61.25</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>47.81</v>
+        <v>44.5</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.8</v>
+        <v>-45.42</v>
       </c>
       <c r="L34" t="n">
-        <v>68.31999999999999</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>44.39</v>
+        <v>44.96</v>
       </c>
       <c r="K35" t="n">
-        <v>-80.44</v>
+        <v>-81.48999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>91.88</v>
+        <v>93.06999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>76.2</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.95999999999999</v>
+        <v>-75.08</v>
       </c>
       <c r="L36" t="n">
-        <v>109.73</v>
+        <v>104.34</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>41.52</v>
+        <v>44.74</v>
       </c>
       <c r="K37" t="n">
-        <v>-42.62</v>
+        <v>-45.91</v>
       </c>
       <c r="L37" t="n">
-        <v>59.5</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>129.68</v>
+        <v>135.56</v>
       </c>
       <c r="K38" t="n">
-        <v>57.54</v>
+        <v>60.15</v>
       </c>
       <c r="L38" t="n">
-        <v>141.88</v>
+        <v>148.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>18.75</v>
+        <v>20.93</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.86</v>
+        <v>-117.03</v>
       </c>
       <c r="L39" t="n">
-        <v>106.53</v>
+        <v>118.89</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-21.18</v>
+        <v>-23.53</v>
       </c>
       <c r="K40" t="n">
-        <v>-98.19</v>
+        <v>-109.07</v>
       </c>
       <c r="L40" t="n">
-        <v>100.44</v>
+        <v>111.58</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.35</v>
+        <v>-31.94</v>
       </c>
       <c r="K41" t="n">
-        <v>-26.85</v>
+        <v>-32.55</v>
       </c>
       <c r="L41" t="n">
-        <v>37.62</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>61.88</v>
+        <v>65.36</v>
       </c>
       <c r="K42" t="n">
-        <v>235.07</v>
+        <v>248.29</v>
       </c>
       <c r="L42" t="n">
-        <v>243.07</v>
+        <v>256.75</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>31.77</v>
+        <v>36.27</v>
       </c>
       <c r="K43" t="n">
-        <v>-148.13</v>
+        <v>-169.1</v>
       </c>
       <c r="L43" t="n">
-        <v>151.5</v>
+        <v>172.95</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-35.49</v>
+        <v>-36.14</v>
       </c>
       <c r="K44" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="L44" t="n">
-        <v>35.6</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.93</v>
+        <v>-4.6</v>
       </c>
       <c r="K45" t="n">
-        <v>-52.47</v>
+        <v>-48.99</v>
       </c>
       <c r="L45" t="n">
-        <v>52.7</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.69</v>
+        <v>-2.73</v>
       </c>
       <c r="K46" t="n">
-        <v>30.68</v>
+        <v>31.17</v>
       </c>
       <c r="L46" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-62.19</v>
+        <v>-60.13</v>
       </c>
       <c r="K47" t="n">
-        <v>-25.32</v>
+        <v>-24.48</v>
       </c>
       <c r="L47" t="n">
-        <v>67.14</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>21.04</v>
+        <v>20.37</v>
       </c>
       <c r="K48" t="n">
-        <v>58.26</v>
+        <v>56.42</v>
       </c>
       <c r="L48" t="n">
-        <v>61.94</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>64.43000000000001</v>
+        <v>61.49</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.59</v>
+        <v>-1.52</v>
       </c>
       <c r="L49" t="n">
-        <v>64.45</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>56.8</v>
+        <v>61.27</v>
       </c>
       <c r="K50" t="n">
-        <v>51.71</v>
+        <v>55.78</v>
       </c>
       <c r="L50" t="n">
-        <v>76.81</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-107.85</v>
+        <v>-108.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.59</v>
+        <v>-13.69</v>
       </c>
       <c r="L51" t="n">
-        <v>108.7</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>92.72</v>
+        <v>94.09</v>
       </c>
       <c r="K52" t="n">
-        <v>-15.45</v>
+        <v>-15.68</v>
       </c>
       <c r="L52" t="n">
-        <v>94</v>
+        <v>95.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>8.51</v>
+        <v>8.43</v>
       </c>
       <c r="K53" t="n">
-        <v>186.8</v>
+        <v>184.98</v>
       </c>
       <c r="L53" t="n">
-        <v>187</v>
+        <v>185.17</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>32.11</v>
+        <v>34.95</v>
       </c>
       <c r="K54" t="n">
-        <v>-101.31</v>
+        <v>-110.27</v>
       </c>
       <c r="L54" t="n">
-        <v>106.28</v>
+        <v>115.68</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.64</v>
+        <v>-16.42</v>
       </c>
       <c r="K55" t="n">
-        <v>-93.54000000000001</v>
+        <v>-104.93</v>
       </c>
       <c r="L55" t="n">
-        <v>94.68000000000001</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>7.71</v>
+        <v>9.48</v>
       </c>
       <c r="K56" t="n">
-        <v>-103.02</v>
+        <v>-126.64</v>
       </c>
       <c r="L56" t="n">
-        <v>103.31</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-134.1</v>
+        <v>-145.26</v>
       </c>
       <c r="K57" t="n">
-        <v>-142.58</v>
+        <v>-154.45</v>
       </c>
       <c r="L57" t="n">
-        <v>195.73</v>
+        <v>212.03</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>138.97</v>
+        <v>141.79</v>
       </c>
       <c r="K58" t="n">
-        <v>204.15</v>
+        <v>208.3</v>
       </c>
       <c r="L58" t="n">
-        <v>246.96</v>
+        <v>251.98</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>33.07</v>
+        <v>33.31</v>
       </c>
       <c r="K59" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="L59" t="n">
-        <v>34.55</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.11</v>
+        <v>-29.62</v>
       </c>
       <c r="K60" t="n">
-        <v>-36.03</v>
+        <v>-35.44</v>
       </c>
       <c r="L60" t="n">
-        <v>46.96</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>10.33</v>
+        <v>10.97</v>
       </c>
       <c r="K61" t="n">
-        <v>33.39</v>
+        <v>35.43</v>
       </c>
       <c r="L61" t="n">
-        <v>34.95</v>
+        <v>37.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-68.28</v>
+        <v>-66.01000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>29.12</v>
+        <v>28.15</v>
       </c>
       <c r="L62" t="n">
-        <v>74.23</v>
+        <v>71.76000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>36.35</v>
+        <v>35.31</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.34</v>
+        <v>-46.96</v>
       </c>
       <c r="L63" t="n">
-        <v>60.48</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>78.81999999999999</v>
+        <v>75.47</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.26</v>
+        <v>-12.69</v>
       </c>
       <c r="L64" t="n">
-        <v>79.93000000000001</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>137.64</v>
+        <v>134.41</v>
       </c>
       <c r="K65" t="n">
-        <v>38.14</v>
+        <v>37.24</v>
       </c>
       <c r="L65" t="n">
-        <v>142.82</v>
+        <v>139.47</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>94.73</v>
+        <v>94.75</v>
       </c>
       <c r="K66" t="n">
-        <v>30.73</v>
+        <v>30.74</v>
       </c>
       <c r="L66" t="n">
-        <v>99.59</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-69.59</v>
+        <v>-77.52</v>
       </c>
       <c r="K67" t="n">
-        <v>-26.48</v>
+        <v>-29.49</v>
       </c>
       <c r="L67" t="n">
-        <v>74.45999999999999</v>
+        <v>82.94</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>117.37</v>
+        <v>124.71</v>
       </c>
       <c r="K68" t="n">
-        <v>20.35</v>
+        <v>21.62</v>
       </c>
       <c r="L68" t="n">
-        <v>119.12</v>
+        <v>126.57</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-79.23</v>
+        <v>-83.84</v>
       </c>
       <c r="K69" t="n">
-        <v>-109.59</v>
+        <v>-115.96</v>
       </c>
       <c r="L69" t="n">
-        <v>135.23</v>
+        <v>143.1</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-69.45999999999999</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>109.28</v>
+        <v>113.95</v>
       </c>
       <c r="L70" t="n">
-        <v>129.49</v>
+        <v>135.02</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-150.43</v>
+        <v>-168.47</v>
       </c>
       <c r="K71" t="n">
-        <v>-72.97</v>
+        <v>-81.73</v>
       </c>
       <c r="L71" t="n">
-        <v>167.19</v>
+        <v>187.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>134.74</v>
+        <v>158.46</v>
       </c>
       <c r="K72" t="n">
-        <v>42.5</v>
+        <v>49.99</v>
       </c>
       <c r="L72" t="n">
-        <v>141.28</v>
+        <v>166.16</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>130.14</v>
+        <v>146.55</v>
       </c>
       <c r="K73" t="n">
-        <v>-125.14</v>
+        <v>-140.92</v>
       </c>
       <c r="L73" t="n">
-        <v>180.55</v>
+        <v>203.31</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-18.12</v>
+        <v>-18.99</v>
       </c>
       <c r="K74" t="n">
-        <v>29.31</v>
+        <v>30.72</v>
       </c>
       <c r="L74" t="n">
-        <v>34.46</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>36.86</v>
+        <v>34.89</v>
       </c>
       <c r="K75" t="n">
-        <v>28.57</v>
+        <v>27.05</v>
       </c>
       <c r="L75" t="n">
-        <v>46.64</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>15.24</v>
+        <v>16.49</v>
       </c>
       <c r="K76" t="n">
-        <v>23.38</v>
+        <v>25.29</v>
       </c>
       <c r="L76" t="n">
-        <v>27.9</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>19.95</v>
+        <v>21.15</v>
       </c>
       <c r="K77" t="n">
-        <v>-43.9</v>
+        <v>-46.54</v>
       </c>
       <c r="L77" t="n">
-        <v>48.22</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>10.06</v>
+        <v>9.85</v>
       </c>
       <c r="K78" t="n">
-        <v>57.29</v>
+        <v>56.09</v>
       </c>
       <c r="L78" t="n">
-        <v>58.17</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-37.03</v>
+        <v>-36.82</v>
       </c>
       <c r="K79" t="n">
-        <v>39.58</v>
+        <v>39.36</v>
       </c>
       <c r="L79" t="n">
-        <v>54.2</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>9.109999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-79.13</v>
+        <v>-82.76000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>79.66</v>
+        <v>83.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>13.19</v>
+        <v>13.94</v>
       </c>
       <c r="K81" t="n">
-        <v>73.8</v>
+        <v>78.02</v>
       </c>
       <c r="L81" t="n">
-        <v>74.97</v>
+        <v>79.26000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-60.33</v>
+        <v>-63.36</v>
       </c>
       <c r="K82" t="n">
-        <v>-54.7</v>
+        <v>-57.45</v>
       </c>
       <c r="L82" t="n">
-        <v>81.43000000000001</v>
+        <v>85.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>140.08</v>
+        <v>143.14</v>
       </c>
       <c r="K83" t="n">
-        <v>119.88</v>
+        <v>122.5</v>
       </c>
       <c r="L83" t="n">
-        <v>184.38</v>
+        <v>188.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>59.88</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>48.75</v>
+        <v>58.16</v>
       </c>
       <c r="L84" t="n">
-        <v>77.20999999999999</v>
+        <v>92.12</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-55.99</v>
+        <v>-66.44</v>
       </c>
       <c r="K85" t="n">
-        <v>64.02</v>
+        <v>75.98</v>
       </c>
       <c r="L85" t="n">
-        <v>85.05</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>215.47</v>
+        <v>224.95</v>
       </c>
       <c r="K86" t="n">
-        <v>107.1</v>
+        <v>111.81</v>
       </c>
       <c r="L86" t="n">
-        <v>240.62</v>
+        <v>251.2</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-24.3</v>
+        <v>-28.67</v>
       </c>
       <c r="K87" t="n">
-        <v>130.87</v>
+        <v>154.45</v>
       </c>
       <c r="L87" t="n">
-        <v>133.11</v>
+        <v>157.08</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>122.97</v>
+        <v>149.49</v>
       </c>
       <c r="K88" t="n">
-        <v>-45.92</v>
+        <v>-55.82</v>
       </c>
       <c r="L88" t="n">
-        <v>131.27</v>
+        <v>159.57</v>
       </c>
     </row>
   </sheetData>
